--- a/data/credit_bond_all_2026-10-09.xlsx
+++ b/data/credit_bond_all_2026-10-09.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -1007,7 +1007,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X4" s="3"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>2.27%~2.37%</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -1227,7 +1231,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X5" s="3"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>2.21%~2.31%</t>
+        </is>
+      </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -1443,7 +1451,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X6" s="3"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>1.43%~1.47%</t>
+        </is>
+      </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1572,7 +1584,7 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26锡产业SCP015</t>
+          <t>26安市淮阴MTN001</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1583,40 +1595,38 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>-1.0</v>
-      </c>
+          <t>1.30 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>25锡产业MTN005</t>
+          <t>25安市淮阴MTN003</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>271D</t>
+          <t>1.52Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.4940</t>
+          <t>1.6621</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1626,12 +1636,12 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司</t>
+          <t>淮安市淮阴区城市资产经营有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C- 21.65</t>
+          <t>C- 17.97</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1651,42 +1661,46 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X7" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额6亿元用于归还发行人本部有息债务[26锡产业SCP006]</t>
+          <t>本次发行金额5亿元,募集资金拟全部用于偿还发行人本部及下属子公司有息债务[26安市淮阴CP001]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -1701,7 +1715,7 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司2026年度第十五期超短期融资券</t>
+          <t>淮安市淮阴区城市资产经营有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1711,33 +1725,33 @@
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2027-07-07</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
@@ -1747,17 +1761,17 @@
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1785,12 +1799,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ7" s="3"/>
+      <c r="AZ7" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26安市淮阴MTN001</t>
+          <t>26镇江产投MTN008</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1805,49 +1821,49 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>25安市淮阴MTN003</t>
+          <t>26镇江产投MTN007</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>1.52Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.6621</t>
+          <t>1.6876</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/1.6600</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>淮安市淮阴区城市资产经营有限公司</t>
+          <t>镇江产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C- 17.97</t>
+          <t>C- 19.59</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1867,36 +1883,40 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X8" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本次发行金额5亿元,募集资金拟全部用于偿还发行人本部及下属子公司有息债务[26安市淮阴CP001]</t>
+          <t>发行人本次发行的3.00亿元中期票据全部用于偿还发行人存量有息债务[25镇江产投CP004]</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>中国民生银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
@@ -1917,7 +1937,7 @@
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>淮安市淮阴区城市资产经营有限公司2026年度第一期中期票据</t>
+          <t>镇江产业投资控股集团有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -1927,13 +1947,13 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2029-10-10</t>
         </is>
       </c>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM8" s="3" t="inlineStr">
@@ -1943,17 +1963,17 @@
       </c>
       <c r="AN8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
@@ -1963,17 +1983,17 @@
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2001,12 +2021,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ8" s="3"/>
+      <c r="AZ8" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26镇江产投MTN008</t>
+          <t>26海发宝诚SCP007</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2017,53 +2039,53 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.26Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.35 ~ 1.49</t>
         </is>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26镇江产投MTN007</t>
+          <t>25海租01</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>93D</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.6876</t>
+          <t>1.4726</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4600</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>镇江产业投资控股集团有限公司</t>
+          <t>海发宝诚融资租赁有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C- 19.59</t>
+          <t>C- 14.16</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2083,7 +2105,7 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U9" s="3"/>
@@ -2093,7 +2115,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X9" s="3"/>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>1.48%~1.52%</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2102,28 +2128,28 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行的3.00亿元中期票据全部用于偿还发行人存量有息债务[25镇江产投CP004]</t>
+          <t>本期超短期融资券基础发行金额0亿元，发行金额上限5亿元，拟全部用于偿还发行人即将到期的债务融资工具[26海发宝诚SCP006]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,南京银行股份有限公司</t>
+          <t>平安银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr">
@@ -2133,7 +2159,7 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>镇江产业投资控股集团有限公司2026年度第八期中期票据</t>
+          <t>海发宝诚融资租赁有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2143,53 +2169,53 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2029-10-10</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2217,12 +2243,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ9" s="3"/>
+      <c r="AZ9" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26海发宝诚SCP007</t>
+          <t>26连云港SCP004</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2233,38 +2261,38 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.26Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.49</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>25海租01</t>
+          <t>26连云港SCP003</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>93D</t>
+          <t>248D</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.4726</t>
+          <t>1.5426</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2274,12 +2302,12 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>海发宝诚融资租赁有限公司</t>
+          <t>连云港港口集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 14.16</t>
+          <t>C- 13.89</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2306,29 +2334,33 @@
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X10" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>1.59%~1.63%</t>
+        </is>
+      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-连云港市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额0亿元，发行金额上限5亿元，拟全部用于偿还发行人即将到期的债务融资工具[26海发宝诚SCP006]</t>
+          <t>本期超短期融资券发行金额4.00亿元,募集资金全部用于偿还发行人存量有息债务。</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,上海银行股份有限公司</t>
+          <t>南京银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
@@ -2339,7 +2371,7 @@
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
@@ -2349,7 +2381,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>海发宝诚融资租赁有限公司2026年度第七期超短期融资券</t>
+          <t>连云港港口集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2359,7 +2391,7 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK10" s="3"/>
@@ -2380,32 +2412,32 @@
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2433,12 +2465,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ10" s="3"/>
+      <c r="AZ10" s="4" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP004</t>
+          <t>26淮安国投MTN006</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2449,38 +2483,38 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP003</t>
+          <t>26淮安国投MTN005</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>248D</t>
+          <t>1.90Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.5426</t>
+          <t>1.6140</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2490,12 +2524,12 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司</t>
+          <t>淮安市国有联合投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C- 13.89</t>
+          <t>C 27.14</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2525,32 +2559,36 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X11" s="3"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>1.49%~1.59%</t>
+        </is>
+      </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>江苏省-连云港市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4.00亿元,募集资金全部用于偿还发行人存量有息债务。</t>
+          <t>本期发行金额2亿元，募集资金拟全部用于偿还发行人到期债券[25淮安国投MTN002]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,中国银行股份有限公司</t>
+          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -2565,7 +2603,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司2026年度第四期超短期融资券</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2575,7 +2613,7 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
@@ -2596,7 +2634,7 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
@@ -2611,17 +2649,17 @@
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2649,12 +2687,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ11" s="3"/>
+      <c r="AZ11" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN006</t>
+          <t>26广州产投SCP008</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2665,53 +2705,53 @@
       <c r="C12" s="3"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.0</v>
+        <v>10.5</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN005</t>
+          <t>26广州产投SCP007</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>1.90Y</t>
+          <t>259D</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.6140</t>
+          <t>1.4923</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/1.4900</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>广州产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C 27.14</t>
+          <t>C- 22.77</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2731,17 +2771,21 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X12" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>1.48%~1.52%</t>
+        </is>
+      </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2750,23 +2794,23 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额2亿元，募集资金拟全部用于偿还发行人到期债券[25淮安国投MTN002]</t>
+          <t>本期超短期融资券的发行规模为10.5亿元，募集资金全部用于偿还到期债务融资工具[26 广州产投SCP002 ]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
+          <t>平安银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2781,7 +2825,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年度第六期中期票据</t>
+          <t>广州产业投资控股集团有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2791,13 +2835,13 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2027-07-07</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM12" s="3" t="inlineStr">
@@ -2807,37 +2851,37 @@
       </c>
       <c r="AN12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -2865,14 +2909,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ12" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ12" s="3"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP008</t>
+          <t>26绍兴高新MTN003</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2883,53 +2925,53 @@
       <c r="C13" s="3"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.5</v>
+        <v>8.2</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP007</t>
+          <t>26绍兴高新MTN002</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>259D</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.4923</t>
+          <t>1.8213</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8400/1.8000</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司</t>
+          <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C- 22.77</t>
+          <t>C 27.17</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2939,7 +2981,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -2949,42 +2991,46 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X13" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>1.79%~1.89%</t>
+        </is>
+      </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券的发行规模为10.5亿元，募集资金全部用于偿还到期债务融资工具[26 广州产投SCP002 ]</t>
+          <t>发行人本期中期票据发行金额人民币8.20亿元,拟全部用于偿还发行人本级2026年到期的债务融资工具本金[23绍兴高新MTN002]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -2999,7 +3045,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司2026年度第八期超短期融资券</t>
+          <t>绍兴高新技术产业开发区投资发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3009,53 +3055,57 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2027-07-07</t>
-        </is>
-      </c>
-      <c r="AK13" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK13" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL13" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3088,7 +3138,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26绍兴高新MTN003</t>
+          <t>26南京公路MTN003</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3103,49 +3153,49 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>8.2</v>
+        <v>2.0</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26绍兴高新MTN002</t>
+          <t>25南京公路MTN001</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>3.83Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.8213</t>
+          <t>1.6928</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.8400/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
+          <t>南京公路发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C 27.17</t>
+          <t>C- 17.78</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3155,7 +3205,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3165,17 +3215,21 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X14" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -3184,20 +3238,24 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额人民币8.20亿元,拟全部用于偿还发行人本级2026年到期的债务融资工具本金[23绍兴高新MTN002]</t>
+          <t>本期中期票据发行金额2亿元,募集资金用于偿还发行人本级及下属子公司有息债务</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,宁波银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD14" s="3"/>
+          <t>南京银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr">
+        <is>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+        </is>
+      </c>
       <c r="AE14" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -3215,7 +3273,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>绍兴高新技术产业开发区投资发展集团有限公司2026年度第三期中期票据</t>
+          <t>南京公路发展(集团)有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3225,17 +3283,13 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK14" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-10</t>
+        </is>
+      </c>
+      <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM14" s="3" t="inlineStr">
@@ -3245,17 +3299,17 @@
       </c>
       <c r="AN14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
@@ -3265,17 +3319,17 @@
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3285,7 +3339,7 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW14" s="3" t="inlineStr">
@@ -3303,12 +3357,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ14" s="3"/>
+      <c r="AZ14" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26南京公路MTN003</t>
+          <t>26蜀道K9</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3316,56 +3372,60 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>525034.SZ</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.0</v>
+        <v>25.0</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>25南京公路MTN001</t>
+          <t>24蜀道05</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>3.83Y</t>
+          <t>5.01Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.6928</t>
+          <t>1.7316</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/1.7200</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司</t>
+          <t>蜀道投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 17.78</t>
+          <t>B- 38.80</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3375,7 +3435,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3385,46 +3445,46 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X15" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.73%</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额2亿元,募集资金用于偿还发行人本级及下属子公司有息债务</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资以及符合国家法律法规要求的其他用途。</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司,天府证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3434,12 +3494,12 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司2026年度第三期中期票据</t>
+          <t>蜀道投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第九期)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3449,33 +3509,37 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2031-10-10</t>
-        </is>
-      </c>
-      <c r="AK15" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK15" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL15" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
@@ -3485,17 +3549,17 @@
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3505,7 +3569,7 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW15" s="3" t="inlineStr">
@@ -3528,7 +3592,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26蜀道K9</t>
+          <t>26中航K5</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3538,16 +3602,16 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>525034.SZ</t>
+          <t>525028.SZ</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>25.0</v>
+        <v>7.0</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
@@ -3559,37 +3623,37 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>24蜀道05</t>
+          <t>26中航K3</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>5.01Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.7316</t>
+          <t>1.6291</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6300/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司</t>
+          <t>中航科创有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>B- 38.80</t>
+          <t>B- 40.89</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3599,7 +3663,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3609,36 +3673,44 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X16" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>1.57%~1.67%</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z16" s="3"/>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资以及符合国家法律法规要求的其他用途。</t>
+          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,天府证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司</t>
+          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
@@ -3649,7 +3721,7 @@
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
@@ -3659,7 +3731,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第九期)</t>
+          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3669,12 +3741,12 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
+          <t>2029-10-13</t>
         </is>
       </c>
       <c r="AK16" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL16" s="3" t="inlineStr">
@@ -3689,37 +3761,37 @@
       </c>
       <c r="AN16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>航空装备</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3752,7 +3824,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26中航K5</t>
+          <t>26古厝13</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3762,16 +3834,16 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>525028.SZ</t>
+          <t>520514.SZ</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
@@ -3783,37 +3855,37 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26中航K3</t>
+          <t>24古厝01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>2.63Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.6291</t>
+          <t>1.6949</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司</t>
+          <t>福州古厝集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 40.89</t>
+          <t>C 28.36</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3823,7 +3895,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -3833,7 +3905,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U17" s="3"/>
@@ -3843,30 +3915,30 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X17" s="3"/>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
+          <t>本期债券发行规模不超过5.00亿元（含），募集资金在扣除发行费用后，拟用于偿还发行人到期的公司债券本金。[25古厝D6]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>兴业证券股份有限公司,中国国际金融股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -3877,7 +3949,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -3887,24 +3959,20 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
+          <t>福州古厝集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK17" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-10-12</t>
+        </is>
+      </c>
+      <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
           <t/>
@@ -3917,37 +3985,25 @@
       </c>
       <c r="AN17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="AQ17" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR17" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3"/>
+      <c r="AR17" s="3"/>
+      <c r="AS17" s="3"/>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>航空装备</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -3980,7 +4036,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26古厝13</t>
+          <t>26中航K6</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3990,58 +4046,58 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>520514.SZ</t>
+          <t>525029.SZ</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>24古厝01</t>
+          <t>26中航K4</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2.63Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.6949</t>
+          <t>1.7137</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/1.6800</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司</t>
+          <t>中航科创有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C 28.36</t>
+          <t>B- 40.89</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4051,7 +4107,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4061,7 +4117,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U18" s="3"/>
@@ -4071,26 +4127,34 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X18" s="3"/>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>1.69%~1.79%</t>
+        </is>
+      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z18" s="3"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过5.00亿元（含），募集资金在扣除发行费用后，拟用于偿还发行人到期的公司债券本金。[25古厝D6]</t>
+          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,中国国际金融股份有限公司,天风证券股份有限公司</t>
+          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4101,7 +4165,7 @@
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
@@ -4111,17 +4175,17 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2031-10-13</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
@@ -4137,25 +4201,37 @@
       </c>
       <c r="AN18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ18" s="3"/>
-      <c r="AR18" s="3"/>
-      <c r="AS18" s="3"/>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>航空装备</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4188,7 +4264,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26中航K6</t>
+          <t>26凯建01</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4198,7 +4274,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>525029.SZ</t>
+          <t>284219.SH</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -4207,34 +4283,34 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>2.40 ~ 3.40</t>
         </is>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26中航K4</t>
+          <t>25凯建01</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>4.15Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.7137</t>
+          <t>2.8093</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4244,12 +4320,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司</t>
+          <t>凯里正源城镇建设发展有限责任公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 40.89</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4259,7 +4335,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4269,43 +4345,47 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X19" s="3"/>
+          <t>8-</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>2.79%~2.89%</t>
+        </is>
+      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>贵州省-黔东南苗族侗族自治州</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
+          <t>本期债券募集资金扣除承销费用后，拟全部用于统借统还偿还到期公司债券本金</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD19" s="3"/>
+          <t>第一创业证券承销保荐有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr">
+        <is>
+          <t>贵州省信用增进有限公司</t>
+        </is>
+      </c>
       <c r="AE19" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -4313,30 +4393,34 @@
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
+          <t>凯里正源城镇建设发展有限责任公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
-        </is>
-      </c>
-      <c r="AK19" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK19" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL19" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4349,37 +4433,37 @@
       </c>
       <c r="AN19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>航空装备</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4389,7 +4473,7 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW19" s="3" t="inlineStr">
@@ -4412,53 +4496,53 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26凯建01</t>
+          <t>26苏金04</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 17:00</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>284219.SH</t>
+          <t>284122.SH</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.0</v>
+        <v>3.6</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2.40 ~ 3.40</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>25凯建01</t>
+          <t>26苏金03</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>4.15Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>2.8093</t>
+          <t>1.7237</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4468,12 +4552,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>凯里正源城镇建设发展有限责任公司</t>
+          <t>苏州金合盛控股有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>C- 16.64</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4493,17 +4577,21 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>8-</t>
-        </is>
-      </c>
-      <c r="X20" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>1.76%~1.86%</t>
+        </is>
+      </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -4512,22 +4600,22 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>贵州省-黔东南苗族侗族自治州</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除承销费用后，拟全部用于统借统还偿还到期公司债券本金</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金。[23苏金04]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>第一创业证券承销保荐有限责任公司</t>
+          <t>东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3" t="inlineStr">
         <is>
-          <t>贵州省信用增进有限公司</t>
+          <t>苏州苏高新集团有限公司</t>
         </is>
       </c>
       <c r="AE20" s="3" t="inlineStr">
@@ -4547,7 +4635,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>凯里正源城镇建设发展有限责任公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>苏州金合盛控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4557,12 +4645,12 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
+          <t>2029-10-13</t>
         </is>
       </c>
       <c r="AK20" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL20" s="3" t="inlineStr">
@@ -4577,37 +4665,37 @@
       </c>
       <c r="AN20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4640,17 +4728,17 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26苏金04</t>
+          <t>26杭钢02</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>10-09 17:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>284122.SH</t>
+          <t>246177.SH</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -4659,34 +4747,34 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.6</v>
+        <v>10.0</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26苏金03</t>
+          <t>26杭钢01</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>2.49Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.7237</t>
+          <t>1.6479</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4696,12 +4784,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>苏州金合盛控股有限公司</t>
+          <t>杭州钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 16.64</t>
+          <t>C- 19.18</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4711,7 +4799,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4728,36 +4816,36 @@
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X21" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>1.58%~1.68%</t>
+        </is>
+      </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金。[23苏金04]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,剩余部分募集资金拟用于补充公司流动资金。</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD21" s="3" t="inlineStr">
-        <is>
-          <t>苏州苏高新集团有限公司</t>
-        </is>
-      </c>
+          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -4775,12 +4863,12 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>苏州金合盛控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>杭州钢铁集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ21" s="3" t="inlineStr">
@@ -4810,7 +4898,7 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
@@ -4820,22 +4908,22 @@
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -4845,7 +4933,7 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW21" s="3" t="inlineStr">
@@ -4868,7 +4956,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26杭钢02</t>
+          <t>26唐租01</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4878,7 +4966,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>246177.SH</t>
+          <t>246158.SH</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -4899,22 +4987,22 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26杭钢01</t>
+          <t>25大唐租赁MTN002B(绿色)</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.49Y</t>
+          <t>1.63Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.6479</t>
+          <t>1.6333</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -4924,12 +5012,12 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司</t>
+          <t>大唐融资租赁有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C- 19.18</t>
+          <t>C+ 33.74</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -4956,10 +5044,14 @@
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X22" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4968,17 +5060,17 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,剩余部分募集资金拟用于补充公司流动资金。</t>
+          <t>本期债券募集资金10.00亿元拟用于偿还发行人到期公司债券本金[24唐租04]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
@@ -4989,7 +5081,7 @@
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
@@ -4999,7 +5091,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>大唐融资租赁有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5034,32 +5126,32 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5092,7 +5184,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26唐租01</t>
+          <t>26阜阳投资PPN002</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5100,60 +5192,56 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>246158.SH</t>
-        </is>
-      </c>
+      <c r="C23" s="3"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>10.0</v>
+        <v>4.75</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.40 ~ 2.10</t>
         </is>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>25大唐租赁MTN002B(绿色)</t>
+          <t>26阜阳投资PPN001</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>1.63Y</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.6333</t>
+          <t>1.7226</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/1.7100</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司</t>
+          <t>阜阳投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.74</t>
+          <t>C 29.38</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5163,7 +5251,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5173,124 +5261,124 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X23" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>安徽省-阜阳市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金10.00亿元拟用于偿还发行人到期公司债券本金[24唐租04]</t>
+          <t>本次定向债务融资工具注册规模12.15亿元，本期发行规模4.75亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,招商证券股份有限公司</t>
+          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>阜阳投资发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK23" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2029-10-12</t>
+        </is>
+      </c>
+      <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM23" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AO23" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ23" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR23" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -5311,12 +5399,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ23" s="3"/>
+      <c r="AZ23" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN002</t>
+          <t>26鲲鹏投资02</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5324,56 +5414,60 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C24" s="3"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>525030.SZ</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1+1</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.75</v>
+        <v>16.0</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
+          <t>1.20 ~ 2.00</t>
         </is>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN001</t>
+          <t>25鲲鹏02</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>1.07Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.7226</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5400/1.5400</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司</t>
+          <t>深圳市鲲鹏股权投资管理有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C 29.38</t>
+          <t>B- 40.21</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5383,7 +5477,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5400,35 +5494,39 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X24" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>1.51%~1.55%</t>
+        </is>
+      </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>安徽省-阜阳市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具注册规模12.15亿元，本期发行规模4.75亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004]</t>
+          <t>本期债券发行规模为不超过16亿元(含16亿元),募集资金扣除发行费用后,拟使用不超过15亿元用于偿还到期的公司债券本金,剩余募集资金用于补充流动资金。[24鲲鹏04]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5438,28 +5536,28 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>深圳市鲲鹏股权投资管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t/>
         </is>
       </c>
       <c r="AM24" s="3" t="inlineStr">
@@ -5474,37 +5572,33 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP24" s="3"/>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-10-12</t>
         </is>
       </c>
       <c r="AV24" s="3" t="inlineStr">
@@ -5514,7 +5608,7 @@
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
@@ -5532,7 +5626,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26鲲鹏投资02</t>
+          <t>26榕水02</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5542,58 +5636,58 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>525030.SZ</t>
+          <t>525031.SZ</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>1+1</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>16.0</v>
+        <v>7.0</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.00</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>25鲲鹏02</t>
+          <t>24榕水04</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>1.07Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.7405</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7900/1.7600</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>深圳市鲲鹏股权投资管理有限公司</t>
+          <t>福州水务集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>B- 40.21</t>
+          <t>D+ 8.33</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5603,7 +5697,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5613,17 +5707,21 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X25" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5632,17 +5730,17 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过16亿元(含16亿元),募集资金扣除发行费用后,拟使用不超过15亿元用于偿还到期的公司债券本金,剩余募集资金用于补充流动资金。[24鲲鹏04]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务。[23榕水01]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
+          <t>中信证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
@@ -5663,7 +5761,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>深圳市鲲鹏股权投资管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>福州水务集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5673,7 +5771,7 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2031-10-13</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
@@ -5684,43 +5782,47 @@
       </c>
       <c r="AM25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP25" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
         <is>
-          <t>2027-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AV25" s="3" t="inlineStr">
@@ -5730,7 +5832,7 @@
       </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX25" s="3" t="inlineStr">
@@ -5748,7 +5850,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26榕水02</t>
+          <t>26通新01</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5758,7 +5860,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>525031.SZ</t>
+          <t>284151.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -5767,34 +5869,34 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>24榕水04</t>
+          <t>24通新03</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>3.05Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.7405</t>
+          <t>1.7084</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -5804,12 +5906,12 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>福州水务集团有限公司</t>
+          <t>南通高新控股集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.33</t>
+          <t>C- 24.10</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -5819,7 +5921,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -5836,33 +5938,33 @@
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务。[23榕水01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换偿还到期公司债券本金的自有资金[21通新01]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华福证券股份有限公司</t>
+          <t>东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
@@ -5878,17 +5980,17 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>福州水务集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>南通高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
@@ -5914,32 +6016,32 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -5972,7 +6074,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26通新01</t>
+          <t>26创星PPN002(科创债)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -5980,60 +6082,56 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>284151.SH</t>
-        </is>
-      </c>
+      <c r="C27" s="3"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.20 ~ 2.60</t>
         </is>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>24通新03</t>
+          <t>25创星PPN001(科创债)</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>3.05Y</t>
+          <t>3.69Y+5.00Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.7084</t>
+          <t>1.7809</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>南通高新控股集团有限公司</t>
+          <t>中科创星科技投资有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 24.10</t>
+          <t>D+ 6.86</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6043,7 +6141,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6053,61 +6151,61 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>2.45%~2.55%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换偿还到期公司债券本金的自有资金[21通新01]</t>
+          <t>本次定向债务融资工具发行拟募集资金1亿元,所募集资金拟用于置换前期出资、新增基金出资以及补充流动资金</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>南通高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>中科创星科技投资有限公司2026年度第二期定向科技创新债券</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6117,13 +6215,13 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
+          <t>2029-10-10</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6133,37 +6231,33 @@
       </c>
       <c r="AN27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP27" s="3"/>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6196,7 +6290,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26创星PPN002(科创债)</t>
+          <t>26皖投集MTN006</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6211,49 +6305,49 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.60</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>25创星PPN001(科创债)</t>
+          <t>24皖投03</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>3.69Y+5.00Y</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.7809</t>
+          <t>1.5936</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6300/1.5900</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>中科创星科技投资有限公司</t>
+          <t>安徽省投资集团控股有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.86</t>
+          <t>C- 20.19</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6273,47 +6367,51 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X28" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>1.59%~1.69%</t>
+        </is>
+      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具发行拟募集资金1亿元,所募集资金拟用于置换前期出资、新增基金出资以及补充流动资金</t>
+          <t>本期中期票据募集资金5亿元人民币，全部用于偿还发行人即将到期的债券[25皖投集CP003]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,国家开发银行</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
@@ -6323,54 +6421,58 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>中科创星科技投资有限公司2026年度第二期定向科技创新债券</t>
+          <t>安徽省投资集团控股有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-10-10</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP28" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
@@ -6408,7 +6510,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26皖投集MTN006</t>
+          <t>26吴中经发MTN003</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6419,53 +6521,53 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.0</v>
+        <v>5.7</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>24皖投03</t>
+          <t>26吴中经发MTN002</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>2.85Y+2.00Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.5936</t>
+          <t>1.6622</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司</t>
+          <t>江苏省吴中经济技术发展集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 20.19</t>
+          <t>C- 15.92</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6492,29 +6594,33 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X29" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>1.57%~1.67%</t>
+        </is>
+      </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金5亿元人民币，全部用于偿还发行人即将到期的债券[25皖投集CP003]</t>
+          <t>本期中期票据发行金额5.70亿元,募集资金用于偿还债券[26吴中经发SCP001,26吴中经发SCP002,26吴中经发SCP003]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,国家开发银行</t>
+          <t>苏州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6535,7 +6641,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司2026年度第六期中期票据</t>
+          <t>江苏省吴中经济技术发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6545,60 +6651,64 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
           <t>2029-10-12</t>
         </is>
       </c>
-      <c r="AK29" s="3"/>
-      <c r="AL29" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AM29" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO29" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ29" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR29" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS29" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU29" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV29" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6606,7 +6716,7 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
@@ -6624,7 +6734,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26吴中经发MTN003</t>
+          <t>26广州地铁SCP015</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6635,38 +6745,38 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.7</v>
+        <v>14.0</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.26 ~ 1.55</t>
         </is>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26吴中经发MTN002</t>
+          <t>17广州地铁专项债01(柜台)</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.85Y+2.00Y</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.6622</t>
+          <t>1.4941</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -6676,12 +6786,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>江苏省吴中经济技术发展集团有限公司</t>
+          <t>广州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 15.92</t>
+          <t>B- 36.89</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6708,35 +6818,39 @@
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="X30" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>1.47%~1.51%</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额5.70亿元,募集资金用于偿还债券[26吴中经发SCP001,26吴中经发SCP002,26吴中经发SCP003]</t>
+          <t>本期超短期融资券金额14亿元，其中5亿元用于归还发行人存量债券，9亿元用于归还发行人金融机构借款。[26广州地铁SCP001]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>苏州银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -6751,7 +6865,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>江苏省吴中经济技术发展集团有限公司2026年度第三期中期票据</t>
+          <t>广州地铁集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -6761,14 +6875,10 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-07-09</t>
+        </is>
+      </c>
+      <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -6786,12 +6896,12 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
@@ -6801,22 +6911,22 @@
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AV30" s="3" t="inlineStr">
@@ -6826,7 +6936,7 @@
       </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX30" s="3" t="inlineStr">
@@ -6844,7 +6954,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26广州地铁SCP015</t>
+          <t>26广州地铁SCP014</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6859,7 +6969,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>14.0</v>
+        <v>20.0</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
@@ -6931,7 +7041,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X31" s="3"/>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>1.47%~1.51%</t>
+        </is>
+      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6945,7 +7059,7 @@
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券金额14亿元，其中5亿元用于归还发行人存量债券，9亿元用于归还发行人金融机构借款。[26广州地铁SCP001]</t>
+          <t>本期超短期融资券金额20亿元，全部用于归还发行人的债务融资工具。[26广州地铁SCP001]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
@@ -6971,7 +7085,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司2026年度第十五期超短期融资券</t>
+          <t>广州地铁集团有限公司2026年度第十四期超短期融资券</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7060,7 +7174,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26广州地铁SCP014</t>
+          <t>26宿迁新城MTN001</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7071,38 +7185,38 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>20.0</v>
+        <v>6.88</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.55</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>17广州地铁专项债01(柜台)</t>
+          <t>26宿迁新城CP001</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>159D</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.4941</t>
+          <t>1.5334</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7112,12 +7226,12 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司</t>
+          <t>宿迁市新城控股集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>B- 36.89</t>
+          <t>B- 39.74</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7144,35 +7258,39 @@
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X32" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>1.56%~1.66%</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券金额20亿元，全部用于归还发行人的债务融资工具。[26广州地铁SCP001]</t>
+          <t>首期拟发行金额6.88亿元募集资金拟用于偿还发行人存量债务融资工具本金[25宿迁新城CP002]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
+          <t>南京银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
@@ -7187,7 +7305,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司2026年度第十四期超短期融资券</t>
+          <t>宿迁市新城控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7197,7 +7315,7 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
@@ -7218,12 +7336,12 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
@@ -7233,17 +7351,17 @@
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7271,12 +7389,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ32" s="3"/>
+      <c r="AZ32" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城MTN001</t>
+          <t>26天长01</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7284,41 +7404,45 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C33" s="3"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>284203.SH</t>
+        </is>
+      </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.88</v>
+        <v>8.0</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城CP001</t>
+          <t>25滁高01</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>159D</t>
+          <t>1.64Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.5334</t>
+          <t>1.6291</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -7328,12 +7452,12 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司</t>
+          <t>天长市科技工业发展有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>B- 39.74</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7343,7 +7467,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7360,35 +7484,47 @@
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X33" s="3"/>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z33" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>安徽省-滁州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>首期拟发行金额6.88亿元募集资金拟用于偿还发行人存量债务融资工具本金[25宿迁新城CP002]</t>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还“23天长02”公司债券本金。[23天长02]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,交通银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD33" s="3"/>
+          <t>五矿证券有限公司,川财证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr">
+        <is>
+          <t>安徽省信用融资担保集团有限公司</t>
+        </is>
+      </c>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7398,28 +7534,28 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司2026年度第一期中期票据</t>
+          <t>天长市科技工业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t/>
         </is>
       </c>
       <c r="AM33" s="3" t="inlineStr">
@@ -7439,7 +7575,7 @@
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
@@ -7449,17 +7585,17 @@
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7469,7 +7605,7 @@
       </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW33" s="3" t="inlineStr">
@@ -7492,7 +7628,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26天长01</t>
+          <t>26杭金投MTN004</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7500,60 +7636,56 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>284203.SH</t>
-        </is>
-      </c>
+      <c r="C34" s="3"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1.5Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>25滁高01</t>
+          <t>26杭金投MTN001</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>1.64Y</t>
+          <t>1.69Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.6291</t>
+          <t>1.6154</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>天长市科技工业发展有限公司</t>
+          <t>杭州市金融投资集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 17.14</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7563,7 +7695,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7573,50 +7705,46 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X34" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>1.53%~1.63%</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>安徽省-滁州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,全部用于偿还“23天长02”公司债券本金。[23天长02]</t>
+          <t>本次中期票据募集资金10亿元，拟全部用于偿还发行人即将到期的债务融资工具【26 杭金投SCP001】</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司,川财证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD34" s="3" t="inlineStr">
-        <is>
-          <t>安徽省信用融资担保集团有限公司</t>
-        </is>
-      </c>
+          <t>浙商银行股份有限公司,中国工商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -7626,78 +7754,78 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>天长市科技工业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>杭州市金融投资集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2028-04-10</t>
         </is>
       </c>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO34" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ34" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR34" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW34" s="3" t="inlineStr">
@@ -7720,7 +7848,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26杭金投MTN004</t>
+          <t>26莆田国资MTN002</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -7731,7 +7859,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
@@ -7740,29 +7868,29 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26杭金投MTN001</t>
+          <t>26莆田国资MTN001</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>1.69Y</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.6154</t>
+          <t>1.6718</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -7772,12 +7900,12 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>杭州市金融投资集团有限公司</t>
+          <t>莆田市国有资产投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 17.14</t>
+          <t>B- 35.44</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -7787,7 +7915,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -7797,36 +7925,40 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X35" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>福建省-莆田市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据募集资金10亿元，拟全部用于偿还发行人即将到期的债务融资工具【26 杭金投SCP001】</t>
+          <t>发行人本期中期票据发行金额为10亿元,拟用于偿还发行人本部接续债务融资工具的专项贷款。[21莆田国资PPN003]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -7847,7 +7979,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>杭州市金融投资集团有限公司2026年度第四期中期票据</t>
+          <t>莆田市国有资产投资集团有限责任公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -7857,53 +7989,53 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2028-04-10</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -7936,7 +8068,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26莆田国资MTN002</t>
+          <t>26云能04</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -7944,56 +8076,60 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C36" s="3"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>246167.SH</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26莆田国资MTN001</t>
+          <t>25云能投MTN003</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>3.89Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.6718</t>
+          <t>1.8363</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8500/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>莆田市国有资产投资集团有限责任公司</t>
+          <t>云南省能源集团有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>B- 35.44</t>
+          <t>C 26.08</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8003,7 +8139,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8020,35 +8156,39 @@
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X36" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>1.84%~1.94%</t>
+        </is>
+      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>福建省-莆田市</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为10亿元,拟用于偿还发行人本部接续债务融资工具的专项贷款。[21莆田国资PPN003]</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,太平洋证券股份有限公司,平安证券股份有限公司,五矿证券有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8058,12 +8198,12 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>莆田市国有资产投资集团有限责任公司2026年度第二期中期票据</t>
+          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8073,13 +8213,17 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK36" s="3"/>
+          <t>2030-10-12</t>
+        </is>
+      </c>
+      <c r="AK36" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t/>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
@@ -8094,12 +8238,12 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
@@ -8109,17 +8253,17 @@
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8152,7 +8296,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26云能04</t>
+          <t>26左海02</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8162,58 +8306,58 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>246167.SH</t>
+          <t>284143.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>25云能投MTN003</t>
+          <t>25左海01</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>3.89Y</t>
+          <t>3.26Y+5.00Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.8363</t>
+          <t>1.7185</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司</t>
+          <t>福州左海控股集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C 26.08</t>
+          <t>C+ 31.87</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8240,10 +8384,14 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X37" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>1.73%~1.83%</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8252,17 +8400,17 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还有息债务</t>
+          <t>本期公司债券拟发行5亿元，募集资金扣除发行费用后，拟全部用于偿还公司债券本金【23左海03 】</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,太平洋证券股份有限公司,平安证券股份有限公司,五矿证券有限公司</t>
+          <t>中信建投证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8283,22 +8431,22 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>福州左海控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2030-10-12</t>
+          <t>2031-10-12</t>
         </is>
       </c>
       <c r="AK37" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL37" s="3" t="inlineStr">
@@ -8318,37 +8466,37 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AV37" s="3" t="inlineStr">
@@ -8358,7 +8506,7 @@
       </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX37" s="3" t="inlineStr">
@@ -8376,7 +8524,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26左海02</t>
+          <t>26常城建PPN002</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8384,45 +8532,41 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>284143.SH</t>
-        </is>
-      </c>
+      <c r="C38" s="3"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>5.0</v>
+        <v>6.64</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.55 ~ 2.05</t>
         </is>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>25左海01</t>
+          <t>26常城05</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>3.26Y+5.00Y</t>
+          <t>4.85Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.7185</t>
+          <t>1.8288</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -8432,12 +8576,12 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>福州左海控股集团有限公司</t>
+          <t>常州市城市建设(集团)有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.87</t>
+          <t>C+ 31.26</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8447,7 +8591,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8457,17 +8601,21 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X38" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>1.69%~1.79%</t>
+        </is>
+      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8476,23 +8624,23 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券拟发行5亿元，募集资金扣除发行费用后，拟全部用于偿还公司债券本金【23左海03 】</t>
+          <t>发行人本期定向债务融资工具发行金额为6.64亿元,拟用于偿还发行人本部存量债务融资工具本金[21常城建MTN003,26常城建SCP001]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,华福证券股份有限公司</t>
+          <t>南京银行股份有限公司,江苏银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8502,12 +8650,12 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>福州左海控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>常州市城市建设(集团)有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8517,64 +8665,60 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK38" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-10</t>
+        </is>
+      </c>
+      <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>燃气</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO38" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ38" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR38" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>高速公路</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
-        <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8582,7 +8726,7 @@
       </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX38" s="3" t="inlineStr">
@@ -8595,12 +8739,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ38" s="3"/>
+      <c r="AZ38" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26常城建PPN002</t>
+          <t>26兴化城投PPN009</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8611,53 +8757,53 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>6.64</v>
+        <v>4.0</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.55 ~ 2.05</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26常城05</t>
+          <t>26兴化城投PPN008</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>4.85Y</t>
+          <t>1.88Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.8288</t>
+          <t>1.6847</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>常州市城市建设(集团)有限公司</t>
+          <t>兴化市城市建设投资有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.26</t>
+          <t>C- 12.27</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8684,29 +8830,33 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X39" s="3"/>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>1.65%~1.75%</t>
+        </is>
+      </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行金额为6.64亿元,拟用于偿还发行人本部存量债务融资工具本金[21常城建MTN003,26常城建SCP001]</t>
+          <t>本期定向债务融资工具发行金额4亿元,拟用于偿还发行人有息债务[26兴化城投PPN002]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,江苏银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>江苏江南农村商业银行股份有限公司,苏州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
@@ -8727,7 +8877,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>常州市城市建设(集团)有限公司2026年度第二期定向债务融资工具</t>
+          <t>兴化市城市建设投资有限公司2026年度第九期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -8737,7 +8887,7 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2031-10-10</t>
+          <t>2028-10-10</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
@@ -8758,12 +8908,12 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
@@ -8783,7 +8933,7 @@
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>农产品加工</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -8816,7 +8966,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26兴化城投PPN009</t>
+          <t>26锡产业SCP015</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8827,53 +8977,53 @@
       <c r="C40" s="3"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.31 ~ 1.51</t>
         </is>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26兴化城投PPN008</t>
+          <t>25锡产业MTN005</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>1.88Y</t>
+          <t>271D</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.6847</t>
+          <t>1.4940</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>--/1.4800</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>兴化市城市建设投资有限公司</t>
+          <t>无锡产业发展集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 12.27</t>
+          <t>C- 21.65</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -8900,35 +9050,39 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X40" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>1.49%~1.53%</t>
+        </is>
+      </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额4亿元,拟用于偿还发行人有息债务[26兴化城投PPN002]</t>
+          <t>本期超短期融资券发行金额6亿元用于归还发行人本部有息债务[26锡产业SCP006]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>江苏江南农村商业银行股份有限公司,苏州银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -8943,17 +9097,17 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>兴化市城市建设投资有限公司2026年度第九期定向债务融资工具</t>
+          <t>无锡产业发展集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2028-10-10</t>
+          <t>2027-07-07</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
@@ -8979,7 +9133,7 @@
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
@@ -8989,17 +9143,17 @@
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>农产品加工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-10-09.xlsx
+++ b/data/credit_bond_all_2026-10-09.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-09" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-12" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -719,8 +719,12 @@
           <t>1.40 ~ 2.40</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>49.84</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.75</t>
@@ -753,7 +757,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.80</t>
+          <t>C+ 33.03</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -852,7 +856,7 @@
       </c>
       <c r="AM3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN3" s="3" t="inlineStr">
@@ -928,7 +932,11 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>102690061.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>10Y</t>
@@ -937,14 +945,20 @@
       <c r="E4" s="4" t="n">
         <v>7.0</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>7.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>61.36</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -977,7 +991,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C 25.88</t>
+          <t>C- 24.60</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1000,7 +1014,9 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>2.7</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
@@ -1152,7 +1168,11 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>102690060.IB</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>7Y</t>
@@ -1161,7 +1181,9 @@
       <c r="E5" s="4" t="n">
         <v>3.0</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>1.70 ~ 2.70</t>
@@ -1201,7 +1223,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C 25.88</t>
+          <t>C- 24.60</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1364,7 +1386,7 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26鲁高速SCP004</t>
+          <t>26安市淮阴MTN001</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1372,41 +1394,51 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>102683884.IB</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>0.66Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
-        </is>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+          <t>1.30 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>46.84</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>24鲁高K3</t>
+          <t>25安市淮阴MTN003</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>290D</t>
+          <t>1.52Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.4688</t>
+          <t>1.6621</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1416,12 +1448,12 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司</t>
+          <t>淮安市淮阴区城市资产经营有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>B- 43.44</t>
+          <t>C- 17.97</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1431,56 +1463,60 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>10-09 10:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>4.67</v>
+      </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.43%~1.47%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额20亿元，发行金额上限30亿元，募集资金用于偿还发行人本部及子公司有息负债及补充流动资金</t>
+          <t>本次发行金额5亿元,募集资金拟全部用于偿还发行人本部及下属子公司有息债务[26安市淮阴CP001]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司,北京银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
@@ -1495,7 +1531,7 @@
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司2026年度第四期超短期融资券</t>
+          <t>淮安市淮阴区城市资产经营有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
@@ -1505,53 +1541,53 @@
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2027-06-07</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK6" s="3"/>
       <c r="AL6" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1579,12 +1615,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ6" s="3"/>
+      <c r="AZ6" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26安市淮阴MTN001</t>
+          <t>26镇江产投MTN008</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1592,56 +1630,66 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>102683874.IB</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>30.84</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>25安市淮阴MTN003</t>
+          <t>26镇江产投MTN007</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>1.52Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.6621</t>
+          <t>1.6876</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6900/1.6600</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>淮安市淮阴区城市资产经营有限公司</t>
+          <t>镇江产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C- 17.97</t>
+          <t>C- 13.33</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1656,45 +1704,49 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本次发行金额5亿元,募集资金拟全部用于偿还发行人本部及下属子公司有息债务[26安市淮阴CP001]</t>
+          <t>发行人本次发行的3.00亿元中期票据全部用于偿还发行人存量有息债务[25镇江产投CP004]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>中国民生银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
@@ -1715,7 +1767,7 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>淮安市淮阴区城市资产经营有限公司2026年度第一期中期票据</t>
+          <t>镇江产业投资控股集团有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1725,13 +1777,13 @@
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2029-10-10</t>
         </is>
       </c>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM7" s="3" t="inlineStr">
@@ -1741,17 +1793,17 @@
       </c>
       <c r="AN7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
@@ -1761,17 +1813,17 @@
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1800,13 +1852,13 @@
         </is>
       </c>
       <c r="AZ7" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26镇江产投MTN008</t>
+          <t>26海发宝诚SCP007</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1814,56 +1866,66 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>012682380.IB</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.26Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+          <t>1.35 ~ 1.49</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>30.32</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26镇江产投MTN007</t>
+          <t>25海租01</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>93D</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.6876</t>
+          <t>1.4631</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.8000/1.6600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>镇江产业投资控股集团有限公司</t>
+          <t>海发宝诚融资租赁有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C- 19.59</t>
+          <t>C- 16.02</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1883,7 +1945,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U8" s="3"/>
@@ -1895,7 +1957,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1906,28 +1968,28 @@
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行的3.00亿元中期票据全部用于偿还发行人存量有息债务[25镇江产投CP004]</t>
+          <t>本期超短期融资券基础发行金额0亿元，发行金额上限5亿元，拟全部用于偿还发行人即将到期的债务融资工具[26海发宝诚SCP006]</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,南京银行股份有限公司</t>
+          <t>平安银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG8" s="3" t="inlineStr">
@@ -1937,7 +1999,7 @@
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>镇江产业投资控股集团有限公司2026年度第八期中期票据</t>
+          <t>海发宝诚融资租赁有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -1947,53 +2009,53 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2029-10-10</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2028,7 +2090,7 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26海发宝诚SCP007</t>
+          <t>26连云港SCP004</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2036,56 +2098,66 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>012682382.IB</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>0.26Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.49</t>
-        </is>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+          <t>1.30 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>30.25</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>25海租01</t>
+          <t>26连云港SCP003</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>93D</t>
+          <t>248D</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.4726</t>
+          <t>1.5426</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/1.4600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>海发宝诚融资租赁有限公司</t>
+          <t>连云港港口集团有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C- 14.16</t>
+          <t>C- 13.46</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2108,37 +2180,41 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
+      <c r="U9" s="4" t="n">
+        <v>3.475</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.59%~1.63%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-连云港市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额0亿元，发行金额上限5亿元，拟全部用于偿还发行人即将到期的债务融资工具[26海发宝诚SCP006]</t>
+          <t>本期超短期融资券发行金额4.00亿元,募集资金全部用于偿还发行人存量有息债务。</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,上海银行股份有限公司</t>
+          <t>南京银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
@@ -2149,7 +2225,7 @@
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr">
@@ -2159,7 +2235,7 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>海发宝诚融资租赁有限公司2026年度第七期超短期融资券</t>
+          <t>连云港港口集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2169,7 +2245,7 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
@@ -2190,32 +2266,32 @@
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2244,13 +2320,13 @@
         </is>
       </c>
       <c r="AZ9" s="4" t="n">
-        <v>0.0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP004</t>
+          <t>26淮安国投MTN006</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2258,41 +2334,51 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>102683878.IB</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F10" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+          <t>1.30 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>32.81</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP003</t>
+          <t>26淮安国投MTN005</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>248D</t>
+          <t>1.90Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.5426</t>
+          <t>1.6140</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2302,12 +2388,12 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司</t>
+          <t>淮安市国有联合投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 13.89</t>
+          <t>C 25.65</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2322,7 +2408,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2330,8 +2416,12 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
+      <c r="U10" s="4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>2.33</v>
+      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -2339,34 +2429,34 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.63%</t>
+          <t>1.49%~1.59%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>江苏省-连云港市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4.00亿元,募集资金全部用于偿还发行人存量有息债务。</t>
+          <t>本期发行金额2亿元，募集资金拟全部用于偿还发行人到期债券[25淮安国投MTN002]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,中国银行股份有限公司</t>
+          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
@@ -2381,7 +2471,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司2026年度第四期超短期融资券</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2391,7 +2481,7 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK10" s="3"/>
@@ -2412,7 +2502,7 @@
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
@@ -2427,17 +2517,17 @@
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2466,13 +2556,13 @@
         </is>
       </c>
       <c r="AZ10" s="4" t="n">
-        <v>0.005</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN006</t>
+          <t>26绍兴高新MTN003</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2480,41 +2570,51 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>102683883.IB</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>8.2</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>8.2</v>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
-        </is>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>41.11</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN005</t>
+          <t>26绍兴高新MTN002</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>1.90Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.6140</t>
+          <t>1.8213</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2524,12 +2624,12 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C 27.14</t>
+          <t>C- 23.35</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2539,12 +2639,12 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2552,37 +2652,39 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U11" s="3"/>
+      <c r="U11" s="4" t="n">
+        <v>5.04</v>
+      </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.59%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额2亿元，募集资金拟全部用于偿还发行人到期债券[25淮安国投MTN002]</t>
+          <t>发行人本期中期票据发行金额人民币8.20亿元,拟全部用于偿还发行人本级2026年到期的债务融资工具本金[23绍兴高新MTN002]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
@@ -2603,7 +2705,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年度第六期中期票据</t>
+          <t>绍兴高新技术产业开发区投资发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2613,10 +2715,14 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
-        </is>
-      </c>
-      <c r="AK11" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK11" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL11" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2634,12 +2740,12 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
@@ -2649,12 +2755,12 @@
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
@@ -2687,14 +2793,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ11" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ11" s="3"/>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP008</t>
+          <t>26阜阳投资PPN002</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2705,53 +2809,57 @@
       <c r="C12" s="3"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>10.5</v>
+        <v>4.75</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
-        </is>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+          <t>1.40 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>41.84</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP007</t>
+          <t>26阜阳投资PPN001</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>259D</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.4923</t>
+          <t>1.7226</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1.5000/1.4900</t>
+          <t>1.7500/1.7000</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司</t>
+          <t>阜阳投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 22.77</t>
+          <t>C- 23.56</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2766,51 +2874,55 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>22.85</v>
+      </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>安徽省-阜阳市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券的发行规模为10.5亿元，募集资金全部用于偿还到期债务融资工具[26 广州产投SCP002 ]</t>
+          <t>本次定向债务融资工具注册规模12.15亿元，本期发行规模4.75亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,中信银行股份有限公司</t>
+          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2825,43 +2937,43 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司2026年度第八期超短期融资券</t>
+          <t>阜阳投资发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2027-07-07</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
@@ -2871,17 +2983,17 @@
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -2909,69 +3021,79 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ12" s="3"/>
+      <c r="AZ12" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26绍兴高新MTN003</t>
+          <t>26苏金04</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
-        </is>
-      </c>
-      <c r="C13" s="3"/>
+          <t>10-09 19:00</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>284122.SH</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>8.2</v>
+        <v>3.6</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>46.84</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26绍兴高新MTN002</t>
+          <t>26苏金03</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.8213</t>
+          <t>1.7214</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>1.8400/1.8000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
+          <t>苏州金合盛控股有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C 27.17</t>
+          <t>C- 16.64</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2981,7 +3103,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -2991,46 +3113,50 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额人民币8.20亿元,拟全部用于偿还发行人本级2026年到期的债务融资工具本金[23绍兴高新MTN002]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金。[23苏金04]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,宁波银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD13" s="3"/>
+          <t>东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr">
+        <is>
+          <t>苏州苏高新集团有限公司</t>
+        </is>
+      </c>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3040,72 +3166,72 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>绍兴高新技术产业开发区投资发展集团有限公司2026年度第三期中期票据</t>
+          <t>苏州金合盛控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
+          <t>2029-10-13</t>
         </is>
       </c>
       <c r="AK13" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL13" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AM13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3115,7 +3241,7 @@
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW13" s="3" t="inlineStr">
@@ -3138,64 +3264,72 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26南京公路MTN003</t>
+          <t>26通新01</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
-        </is>
-      </c>
-      <c r="C14" s="3"/>
+          <t>10-09 19:00</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>284151.SH</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>41.11</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>25南京公路MTN001</t>
+          <t>24通新03</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>3.83Y</t>
+          <t>3.05Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.6928</t>
+          <t>1.7098</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.7100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司</t>
+          <t>南通高新控股集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 17.78</t>
+          <t>C- 19.83</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3205,7 +3339,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3215,7 +3349,7 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U14" s="3"/>
@@ -3227,7 +3361,7 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3238,27 +3372,23 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额2亿元,募集资金用于偿还发行人本级及下属子公司有息债务</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换偿还到期公司债券本金的自有资金[21通新01]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
-        </is>
-      </c>
+          <t>东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3268,38 +3398,38 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司2026年度第三期中期票据</t>
+          <t>南通高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-10-10</t>
+          <t>2031-10-13</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AM14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO14" s="3" t="inlineStr">
@@ -3309,7 +3439,7 @@
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
@@ -3319,17 +3449,17 @@
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3339,7 +3469,7 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW14" s="3" t="inlineStr">
@@ -3357,24 +3487,22 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ14" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ14" s="3"/>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26蜀道K9</t>
+          <t>26榕水02</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>525034.SZ</t>
+          <t>525031.SZ</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3383,7 +3511,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>25.0</v>
+        <v>7.0</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="inlineStr">
@@ -3391,41 +3519,45 @@
           <t>1.20 ~ 2.20</t>
         </is>
       </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="H15" s="4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>33.11</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>24蜀道05</t>
+          <t>24榕水04</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>5.01Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.7316</t>
+          <t>1.7324</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.7200</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司</t>
+          <t>福州水务集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>B- 38.80</t>
+          <t>D+ 8.33</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3435,7 +3567,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3445,19 +3577,21 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U15" s="3"/>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>4.86</v>
+      </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3468,17 +3602,17 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资以及符合国家法律法规要求的其他用途。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务。[23榕水01]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,天府证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司</t>
+          <t>中信证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
@@ -3499,7 +3633,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第九期)</t>
+          <t>福州水务集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3509,14 +3643,10 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK15" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-13</t>
+        </is>
+      </c>
+      <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
           <t/>
@@ -3524,12 +3654,12 @@
       </c>
       <c r="AM15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO15" s="3" t="inlineStr">
@@ -3539,27 +3669,27 @@
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3592,26 +3722,26 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26中航K5</t>
+          <t>26古厝13</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>525028.SZ</t>
+          <t>520514.SZ</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
@@ -3619,41 +3749,45 @@
           <t>1.20 ~ 2.20</t>
         </is>
       </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="H16" s="4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>34.81</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26中航K3</t>
+          <t>24古厝01</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>2.63Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.6291</t>
+          <t>1.6920</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.6300/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司</t>
+          <t>福州古厝集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>B- 40.89</t>
+          <t>C- 24.13</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3663,7 +3797,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3673,10 +3807,12 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U16" s="3"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>3.2</v>
+      </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
@@ -3685,7 +3821,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3693,24 +3829,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z16" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
+          <t>本期债券发行规模不超过5.00亿元（含），募集资金在扣除发行费用后，拟用于偿还发行人到期的公司债券本金。[25古厝D6]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>兴业证券股份有限公司,中国国际金融股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
@@ -3721,7 +3853,7 @@
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
@@ -3731,24 +3863,20 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
+          <t>福州古厝集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK16" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-10-12</t>
+        </is>
+      </c>
+      <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
           <t/>
@@ -3761,37 +3889,25 @@
       </c>
       <c r="AN16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="AQ16" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR16" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS16" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3"/>
+      <c r="AR16" s="3"/>
+      <c r="AS16" s="3"/>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>航空装备</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3824,68 +3940,72 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26古厝13</t>
+          <t>26凯建01</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>520514.SZ</t>
+          <t>284219.SH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+          <t>2.40 ~ 3.40</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>124.11</v>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>24古厝01</t>
+          <t>25凯建01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>2.63Y</t>
+          <t>4.15Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.6949</t>
+          <t>2.8084</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司</t>
+          <t>凯里正源城镇建设发展有限责任公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C 28.36</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3912,36 +4032,40 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>2.79%~2.89%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>贵州省-黔东南苗族侗族自治州</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过5.00亿元（含），募集资金在扣除发行费用后，拟用于偿还发行人到期的公司债券本金。[25古厝D6]</t>
+          <t>本期债券募集资金扣除承销费用后，拟全部用于统借统还偿还到期公司债券本金</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,中国国际金融股份有限公司,天风证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD17" s="3"/>
+          <t>第一创业证券承销保荐有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr">
+        <is>
+          <t>贵州省信用增进有限公司</t>
+        </is>
+      </c>
       <c r="AE17" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -3954,12 +4078,12 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>凯里正源城镇建设发展有限责任公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -3969,10 +4093,14 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
-        </is>
-      </c>
-      <c r="AK17" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK17" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL17" s="3" t="inlineStr">
         <is>
           <t/>
@@ -3995,12 +4123,24 @@
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ17" s="3"/>
-      <c r="AR17" s="3"/>
-      <c r="AS17" s="3"/>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -4013,7 +4153,7 @@
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW17" s="3" t="inlineStr">
@@ -4036,26 +4176,26 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26中航K6</t>
+          <t>26左海02</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>525029.SZ</t>
+          <t>284143.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="inlineStr">
@@ -4063,41 +4203,45 @@
           <t>1.30 ~ 2.30</t>
         </is>
       </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="H18" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>28.11</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26中航K4</t>
+          <t>25左海01</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>3.26Y+5.00Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.7137</t>
+          <t>1.7199</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.6800</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司</t>
+          <t>福州左海控股集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 40.89</t>
+          <t>C- 21.87</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4107,7 +4251,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4117,19 +4261,19 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4137,24 +4281,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
+          <t>本期公司债券拟发行5亿元，募集资金扣除发行费用后，拟全部用于偿还公司债券本金【23左海03 】</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4165,30 +4305,34 @@
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
+          <t>福州左海控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
-        </is>
-      </c>
-      <c r="AK18" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK18" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4201,42 +4345,42 @@
       </c>
       <c r="AN18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>航空装备</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AV18" s="3" t="inlineStr">
@@ -4246,7 +4390,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4264,53 +4408,57 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26凯建01</t>
+          <t>26唐租01</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>284219.SH</t>
+          <t>246158.SH</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2.40 ~ 3.40</t>
-        </is>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>39.84</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>25凯建01</t>
+          <t>25大唐租赁MTN002B(绿色)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>4.15Y</t>
+          <t>1.63Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>2.8093</t>
+          <t>1.6333</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4320,12 +4468,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>凯里正源城镇建设发展有限责任公司</t>
+          <t>大唐融资租赁有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>C 27.94</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4335,7 +4483,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4345,47 +4493,43 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>8-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>2.79%~2.89%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>贵州省-黔东南苗族侗族自治州</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除承销费用后，拟全部用于统借统还偿还到期公司债券本金</t>
+          <t>本期债券募集资金10.00亿元拟用于偿还发行人到期公司债券本金[24唐租04]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>第一创业证券承销保荐有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD19" s="3" t="inlineStr">
-        <is>
-          <t>贵州省信用增进有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,招商证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -4393,7 +4537,7 @@
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
@@ -4403,22 +4547,22 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>凯里正源城镇建设发展有限责任公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>大唐融资租赁有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
+          <t>2029-10-13</t>
         </is>
       </c>
       <c r="AK19" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL19" s="3" t="inlineStr">
@@ -4433,37 +4577,37 @@
       </c>
       <c r="AN19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4473,7 +4617,7 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW19" s="3" t="inlineStr">
@@ -4496,68 +4640,72 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26苏金04</t>
+          <t>26鲲鹏投资02</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>10-09 17:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>284122.SH</t>
+          <t>525030.SZ</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1+1</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.6</v>
+        <v>16.0</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+          <t>1.20 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>20.81</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26苏金03</t>
+          <t>25鲲鹏02</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>1.07Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.7237</t>
+          <t>1.5373</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>苏州金合盛控股有限公司</t>
+          <t>深圳市鲲鹏股权投资管理有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C- 16.64</t>
+          <t>B- 43.09</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4577,47 +4725,43 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金。[23苏金04]</t>
+          <t>本期债券发行规模为不超过16亿元(含16亿元),募集资金扣除发行费用后,拟使用不超过15亿元用于偿还到期的公司债券本金,剩余募集资金用于补充流动资金。[24鲲鹏04]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD20" s="3" t="inlineStr">
-        <is>
-          <t>苏州苏高新集团有限公司</t>
-        </is>
-      </c>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -4630,29 +4774,25 @@
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>苏州金合盛控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>深圳市鲲鹏股权投资管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK20" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-10-12</t>
+        </is>
+      </c>
+      <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4660,12 +4800,12 @@
       </c>
       <c r="AM20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO20" s="3" t="inlineStr">
@@ -4673,11 +4813,7 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+      <c r="AP20" s="3"/>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
           <t>非银</t>
@@ -4685,32 +4821,32 @@
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-10-12</t>
         </is>
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX20" s="3" t="inlineStr">
@@ -4728,7 +4864,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26杭钢02</t>
+          <t>26锡产业SCP015</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4738,58 +4874,64 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>246177.SH</t>
+          <t>012682379.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F21" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+          <t>1.31 ~ 1.51</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>31.25</v>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26杭钢01</t>
+          <t>25锡产业MTN005</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2.49Y</t>
+          <t>271D</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.6479</t>
+          <t>1.4940</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4800</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司</t>
+          <t>无锡产业发展集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 19.18</t>
+          <t>C- 18.23</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4799,7 +4941,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4809,19 +4951,23 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>1.82</v>
+      </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -4832,23 +4978,23 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,剩余部分募集资金拟用于补充公司流动资金。</t>
+          <t>本期超短期融资券发行金额6亿元用于归还发行人本部有息债务[26锡产业SCP006]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -4858,12 +5004,12 @@
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>无锡产业发展集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4873,17 +5019,13 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK21" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-07-07</t>
+        </is>
+      </c>
+      <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM21" s="3" t="inlineStr">
@@ -4893,7 +5035,7 @@
       </c>
       <c r="AN21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO21" s="3" t="inlineStr">
@@ -4903,27 +5045,27 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -4956,7 +5098,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26唐租01</t>
+          <t>26创星PPN002(科创债)</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4966,7 +5108,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>246158.SH</t>
+          <t>032680550.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -4975,49 +5117,55 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+          <t>2.20 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>126.84</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>25大唐租赁MTN002B(绿色)</t>
+          <t>25创星PPN001(科创债)</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>1.63Y</t>
+          <t>3.69Y+5.00Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.6333</t>
+          <t>1.7809</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司</t>
+          <t>中科创星科技投资有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.74</t>
+          <t>D+ 6.00</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5027,7 +5175,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5037,128 +5185,124 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>2.45%~2.55%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金10.00亿元拟用于偿还发行人到期公司债券本金[24唐租04]</t>
+          <t>本次定向债务融资工具发行拟募集资金1亿元,所募集资金拟用于置换前期出资、新增基金出资以及补充流动资金</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,招商证券股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>中科创星科技投资有限公司2026年度第二期定向科技创新债券</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK22" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2029-10-10</t>
+        </is>
+      </c>
+      <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP22" s="3"/>
+      <c r="AQ22" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM22" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AO22" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ22" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR22" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AS22" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AT22" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU22" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -5179,12 +5323,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ22" s="3"/>
+      <c r="AZ22" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN002</t>
+          <t>26广州产投SCP008</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5192,56 +5338,66 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C23" s="3"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>012682378.IB</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F23" s="3"/>
+        <v>10.5</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>10.5</v>
+      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+          <t>1.30 ~ 1.50</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>24.25</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN001</t>
+          <t>26广州产投SCP007</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>259D</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.7226</t>
+          <t>1.4923</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>1.7400/1.7100</t>
+          <t>1.5000/1.4900</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司</t>
+          <t>广州产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C 29.38</t>
+          <t>C- 19.95</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5261,46 +5417,48 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U23" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>1.3</v>
+      </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>安徽省-阜阳市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具注册规模12.15亿元，本期发行规模4.75亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004]</t>
+          <t>本期超短期融资券的发行规模为10.5亿元，募集资金全部用于偿还到期债务融资工具[26 广州产投SCP002 ]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
+          <t>平安银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5315,23 +5473,23 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>广州产业投资控股集团有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2027-07-07</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM23" s="3" t="inlineStr">
@@ -5341,17 +5499,17 @@
       </c>
       <c r="AN23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
@@ -5361,17 +5519,17 @@
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5399,14 +5557,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ23" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ23" s="3"/>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26鲲鹏投资02</t>
+          <t>26鲁高速SCP004</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5416,58 +5572,64 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>525030.SZ</t>
+          <t>012682377.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>1+1</t>
+          <t>0.66Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>20.0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>30.0</v>
+      </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+          <t>1.30 ~ 1.50</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>17.25</v>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>25鲲鹏02</t>
+          <t>24鲁高K3</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>1.07Y</t>
+          <t>290D</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.4600</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1.5400/1.5400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>深圳市鲲鹏股权投资管理有限公司</t>
+          <t>山东高速集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B- 40.21</t>
+          <t>B- 41.63</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5477,21 +5639,25 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 10:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>1.5667</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>9.0</v>
+      </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
           <t>4+</t>
@@ -5499,7 +5665,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>1.43%~1.47%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -5510,23 +5676,23 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过16亿元(含16亿元),募集资金扣除发行费用后,拟使用不超过15亿元用于偿还到期的公司债券本金,剩余募集资金用于补充流动资金。[24鲲鹏04]</t>
+          <t>本期超短期融资券基础发行金额20亿元，发行金额上限30亿元，募集资金用于偿还发行人本部及子公司有息负债及补充流动资金</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
+          <t>广发银行股份有限公司,北京银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5536,12 +5702,12 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>深圳市鲲鹏股权投资管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>山东高速集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5551,56 +5717,60 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2027-06-07</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>高速公路</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM24" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO24" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP24" s="3"/>
-      <c r="AQ24" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR24" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AS24" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AT24" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU24" s="3" t="inlineStr">
-        <is>
-          <t>2027-10-12</t>
-        </is>
-      </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -5608,7 +5778,7 @@
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
@@ -5626,7 +5796,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26榕水02</t>
+          <t>26南京公路MTN003</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5636,7 +5806,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>525031.SZ</t>
+          <t>102683875.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5645,49 +5815,55 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F25" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+          <t>1.60 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>24.11</v>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>24榕水04</t>
+          <t>25南京公路MTN001</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>3.83Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7405</t>
+          <t>1.6928</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.7900/1.7600</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>福州水务集团有限公司</t>
+          <t>南京公路发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.33</t>
+          <t>C- 13.95</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5697,56 +5873,64 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U25" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务。[23榕水01]</t>
+          <t>本期中期票据发行金额2亿元,募集资金用于偿还发行人本级及下属子公司有息债务</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华福证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD25" s="3"/>
+          <t>南京银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr">
+        <is>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+        </is>
+      </c>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -5756,12 +5940,12 @@
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>福州水务集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>南京公路发展(集团)有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5771,63 +5955,63 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
+          <t>2031-10-10</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>高速公路</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AO25" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ25" s="3" t="inlineStr">
-        <is>
-          <t>公用事业</t>
-        </is>
-      </c>
-      <c r="AR25" s="3" t="inlineStr">
-        <is>
-          <t>水务</t>
-        </is>
-      </c>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>水务</t>
-        </is>
-      </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>水务</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW25" s="3" t="inlineStr">
@@ -5845,12 +6029,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ25" s="3"/>
+      <c r="AZ25" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26通新01</t>
+          <t>26皖投集MTN006</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5860,58 +6046,64 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>284151.SH</t>
+          <t>102683882.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F26" s="3"/>
+      <c r="F26" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+          <t>1.40 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>22.84</v>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>24通新03</t>
+          <t>24皖投03</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>3.05Y</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.7084</t>
+          <t>1.6119</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5900</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>南通高新控股集团有限公司</t>
+          <t>安徽省投资集团控股有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 24.10</t>
+          <t>C- 16.98</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -5921,56 +6113,60 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>3.08</v>
+      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换偿还到期公司债券本金的自有资金[21通新01]</t>
+          <t>本期中期票据募集资金5亿元人民币，全部用于偿还发行人即将到期的债券[25皖投集CP003]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,国家开发银行</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -5980,68 +6176,68 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>南通高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>安徽省投资集团控股有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AM26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6074,7 +6270,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26创星PPN002(科创债)</t>
+          <t>26吴中经发MTN003</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6082,56 +6278,66 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>102683881.IB</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F27" s="3"/>
+        <v>5.7</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>5.7</v>
+      </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+          <t>1.50 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>26.11</v>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>25创星PPN001(科创债)</t>
+          <t>26吴中经发MTN002</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>3.69Y+5.00Y</t>
+          <t>2.85Y+2.00Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.7809</t>
+          <t>1.6622</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/1.7600</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>中科创星科技投资有限公司</t>
+          <t>江苏省吴中经济技术发展集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.86</t>
+          <t>C- 15.92</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6151,51 +6357,53 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="U27" s="3"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>5.49</v>
+      </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>2.45%~2.55%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具发行拟募集资金1亿元,所募集资金拟用于置换前期出资、新增基金出资以及补充流动资金</t>
+          <t>本期中期票据发行金额5.70亿元,募集资金用于偿还债券[26吴中经发SCP001,26吴中经发SCP002,26吴中经发SCP003]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司</t>
+          <t>苏州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr">
@@ -6205,54 +6413,62 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>中科创星科技投资有限公司2026年度第二期定向科技创新债券</t>
+          <t>江苏省吴中经济技术发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2029-10-10</t>
-        </is>
-      </c>
-      <c r="AK27" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL27" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP27" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
@@ -6262,7 +6478,7 @@
       </c>
       <c r="AU27" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AV27" s="3" t="inlineStr">
@@ -6272,7 +6488,7 @@
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">
@@ -6290,7 +6506,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26皖投集MTN006</t>
+          <t>26广州地铁SCP015</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6298,56 +6514,66 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C28" s="3"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>012682381.IB</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F28" s="3"/>
+        <v>14.0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>14.0</v>
+      </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+          <t>1.26 ~ 1.55</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>15.25</v>
+      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>24皖投03</t>
+          <t>17广州地铁专项债01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.5936</t>
+          <t>1.4941</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>1.6300/1.5900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司</t>
+          <t>广州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C- 20.19</t>
+          <t>C+ 33.99</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6370,7 +6596,9 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U28" s="3"/>
+      <c r="U28" s="4" t="n">
+        <v>3.89</v>
+      </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
@@ -6379,7 +6607,7 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6390,23 +6618,23 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金5亿元人民币，全部用于偿还发行人即将到期的债券[25皖投集CP003]</t>
+          <t>本期超短期融资券金额14亿元，其中5亿元用于归还发行人存量债券，9亿元用于归还发行人金融机构借款。[26广州地铁SCP001]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,国家开发银行</t>
+          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
@@ -6421,7 +6649,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司2026年度第六期中期票据</t>
+          <t>广州地铁集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6431,7 +6659,7 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
@@ -6457,27 +6685,27 @@
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6510,7 +6738,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26吴中经发MTN003</t>
+          <t>26广州地铁SCP014</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6518,56 +6746,66 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C29" s="3"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>012682383.IB</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F29" s="3"/>
+        <v>20.0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+          <t>1.26 ~ 1.55</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>15.25</v>
+      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26吴中经发MTN002</t>
+          <t>17广州地铁专项债01</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.85Y+2.00Y</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.6622</t>
+          <t>1.4941</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>江苏省吴中经济技术发展集团有限公司</t>
+          <t>广州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 15.92</t>
+          <t>C+ 33.99</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6590,43 +6828,45 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U29" s="3"/>
+      <c r="U29" s="4" t="n">
+        <v>3.79</v>
+      </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额5.70亿元,募集资金用于偿还债券[26吴中经发SCP001,26吴中经发SCP002,26吴中经发SCP003]</t>
+          <t>本期超短期融资券金额20亿元，全部用于归还发行人的债务融资工具。[26广州地铁SCP001]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>苏州银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6641,7 +6881,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>江苏省吴中经济技术发展集团有限公司2026年度第三期中期票据</t>
+          <t>广州地铁集团有限公司2026年度第十四期超短期融资券</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6651,14 +6891,10 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK29" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-07-09</t>
+        </is>
+      </c>
+      <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -6676,12 +6912,12 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
@@ -6691,22 +6927,22 @@
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AV29" s="3" t="inlineStr">
@@ -6716,7 +6952,7 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
@@ -6734,7 +6970,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26广州地铁SCP015</t>
+          <t>26宿迁新城MTN001</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6742,41 +6978,51 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C30" s="3"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>102683877.IB</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="F30" s="3"/>
+        <v>6.88</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>6.88</v>
+      </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.55</t>
-        </is>
-      </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>36.81</v>
+      </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>17广州地铁专项债01(柜台)</t>
+          <t>26宿迁新城CP001</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>159D</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.4941</t>
+          <t>1.5334</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -6786,12 +7032,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司</t>
+          <t>宿迁市新城控股集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B- 36.89</t>
+          <t>B- 37.23</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6806,7 +7052,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -6814,43 +7060,47 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
+      <c r="U30" s="4" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>1.8</v>
+      </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券金额14亿元，其中5亿元用于归还发行人存量债券，9亿元用于归还发行人金融机构借款。[26广州地铁SCP001]</t>
+          <t>首期拟发行金额6.88亿元募集资金拟用于偿还发行人存量债务融资工具本金[25宿迁新城CP002]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
+          <t>南京银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -6865,7 +7115,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司2026年度第十五期超短期融资券</t>
+          <t>宿迁市新城控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -6875,7 +7125,7 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
@@ -6896,12 +7146,12 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
@@ -6911,17 +7161,17 @@
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -6949,54 +7199,64 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ30" s="3"/>
+      <c r="AZ30" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26广州地铁SCP014</t>
+          <t>26天长01</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
-        </is>
-      </c>
-      <c r="C31" s="3"/>
+          <t>10-09 19:00</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>284203.SH</t>
+        </is>
+      </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>20.0</v>
+        <v>8.0</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.55</t>
-        </is>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>46.84</v>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>17广州地铁专项债01(柜台)</t>
+          <t>25滁高01</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>1.64Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.4941</t>
+          <t>1.6256</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -7006,12 +7266,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司</t>
+          <t>天长市科技工业发展有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>B- 36.89</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7021,7 +7281,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7038,39 +7298,47 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>安徽省-滁州市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券金额20亿元，全部用于归还发行人的债务融资工具。[26广州地铁SCP001]</t>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还“23天长02”公司债券本金。[23天长02]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD31" s="3"/>
+          <t>五矿证券有限公司,川财证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr">
+        <is>
+          <t>安徽省信用融资担保集团有限公司</t>
+        </is>
+      </c>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7080,28 +7348,28 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司2026年度第十四期超短期融资券</t>
+          <t>天长市科技工业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t/>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
@@ -7116,12 +7384,12 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
@@ -7131,17 +7399,17 @@
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7151,7 +7419,7 @@
       </c>
       <c r="AV31" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW31" s="3" t="inlineStr">
@@ -7174,7 +7442,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城MTN001</t>
+          <t>26杭金投MTN004</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7182,56 +7450,66 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C32" s="3"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>102683873.IB</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>1.5Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="F32" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+          <t>1.40 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>17.85</v>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城CP001</t>
+          <t>26杭金投MTN001</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>159D</t>
+          <t>1.69Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.5334</t>
+          <t>1.6154</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司</t>
+          <t>杭州市金融投资集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>B- 39.74</t>
+          <t>C- 17.41</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7246,45 +7524,49 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>1.54</v>
+      </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.53%~1.63%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>首期拟发行金额6.88亿元募集资金拟用于偿还发行人存量债务融资工具本金[25宿迁新城CP002]</t>
+          <t>本次中期票据募集资金10亿元，拟全部用于偿还发行人即将到期的债务融资工具【26 杭金投SCP001】</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,交通银行股份有限公司</t>
+          <t>浙商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
@@ -7305,7 +7587,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司2026年度第一期中期票据</t>
+          <t>杭州市金融投资集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7315,13 +7597,13 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2028-04-10</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM32" s="3" t="inlineStr">
@@ -7331,37 +7613,37 @@
       </c>
       <c r="AN32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7389,14 +7671,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ32" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ32" s="3"/>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26天长01</t>
+          <t>26莆田国资MTN002</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7406,7 +7686,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>284203.SH</t>
+          <t>102683876.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -7415,34 +7695,40 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F33" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+          <t>1.50 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>40.84</v>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>25滁高01</t>
+          <t>26莆田国资MTN001</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>1.64Y</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.6291</t>
+          <t>1.6718</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -7452,12 +7738,12 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>天长市科技工业发展有限公司</t>
+          <t>莆田市国有资产投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C+ 33.96</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7472,7 +7758,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -7480,51 +7766,45 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U33" s="3"/>
+      <c r="U33" s="4" t="n">
+        <v>5.26</v>
+      </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>安徽省-滁州市</t>
+          <t>福建省-莆田市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,全部用于偿还“23天长02”公司债券本金。[23天长02]</t>
+          <t>发行人本期中期票据发行金额为10亿元,拟用于偿还发行人本部接续债务融资工具的专项贷款。[21莆田国资PPN003]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司,川财证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD33" s="3" t="inlineStr">
-        <is>
-          <t>安徽省信用融资担保集团有限公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7534,17 +7814,17 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>天长市科技工业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>莆田市国有资产投资集团有限责任公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
@@ -7555,57 +7835,57 @@
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO33" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ33" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR33" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW33" s="3" t="inlineStr">
@@ -7628,64 +7908,72 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26杭金投MTN004</t>
+          <t>26蜀道K9</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
-        </is>
-      </c>
-      <c r="C34" s="3"/>
+          <t>10-09 19:00</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>525034.SZ</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>21.11</v>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26杭金投MTN001</t>
+          <t>24蜀道05</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>1.69Y</t>
+          <t>5.01Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.6154</t>
+          <t>1.7267</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.6400/--</t>
+          <t>--/1.7200</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>杭州市金融投资集团有限公司</t>
+          <t>蜀道投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 17.14</t>
+          <t>B- 36.12</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7695,7 +7983,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7705,19 +7993,21 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="U34" s="3"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>4.26</v>
+      </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.63%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -7728,23 +8018,23 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据募集资金10亿元，拟全部用于偿还发行人即将到期的债务融资工具【26 杭金投SCP001】</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资以及符合国家法律法规要求的其他用途。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,天府证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -7754,12 +8044,12 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>杭州市金融投资集团有限公司2026年度第四期中期票据</t>
+          <t>蜀道投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第九期)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7769,28 +8059,32 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2028-04-10</t>
-        </is>
-      </c>
-      <c r="AK34" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK34" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
@@ -7800,22 +8094,22 @@
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -7848,64 +8142,72 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26莆田国资MTN002</t>
+          <t>26中航K5</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
-        </is>
-      </c>
-      <c r="C35" s="3"/>
+          <t>10-09 19:00</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>525028.SZ</t>
+        </is>
+      </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>24.84</v>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26莆田国资MTN001</t>
+          <t>26中航K3</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.6718</t>
+          <t>1.6223</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6500/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>莆田市国有资产投资集团有限责任公司</t>
+          <t>中航科创有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>B- 35.44</t>
+          <t>C+ 34.11</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -7915,7 +8217,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -7925,61 +8227,65 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z35" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>福建省-莆田市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为10亿元,拟用于偿还发行人本部接续债务融资工具的专项贷款。[21莆田国资PPN003]</t>
+          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
+          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>莆田市国有资产投资集团有限责任公司2026年度第二期中期票据</t>
+          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -7989,33 +8295,37 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK35" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK35" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
@@ -8025,17 +8335,17 @@
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>航空装备</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8068,68 +8378,72 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26云能04</t>
+          <t>26中航K6</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>246167.SH</t>
+          <t>525029.SZ</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>26.11</v>
+      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>25云能投MTN003</t>
+          <t>26中航K4</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>3.89Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.8363</t>
+          <t>1.7088</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.8500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司</t>
+          <t>中航科创有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C 26.08</t>
+          <t>C+ 34.11</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8139,7 +8453,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8149,19 +8463,19 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8169,20 +8483,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z36" s="3"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还有息债务</t>
+          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,太平洋证券股份有限公司,平安证券股份有限公司,五矿证券有限公司</t>
+          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
@@ -8193,17 +8511,17 @@
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8213,14 +8531,10 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2030-10-12</t>
-        </is>
-      </c>
-      <c r="AK36" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-13</t>
+        </is>
+      </c>
+      <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8228,12 +8542,12 @@
       </c>
       <c r="AM36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO36" s="3" t="inlineStr">
@@ -8243,7 +8557,7 @@
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
@@ -8253,17 +8567,17 @@
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>航空装备</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8296,68 +8610,72 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26左海02</t>
+          <t>26杭钢02</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>284143.SH</t>
+          <t>246177.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>31.84</v>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>25左海01</t>
+          <t>26杭钢01</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>3.26Y+5.00Y</t>
+          <t>2.49Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.7185</t>
+          <t>1.6419</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>1.7600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>福州左海控股集团有限公司</t>
+          <t>杭州钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.87</t>
+          <t>C- 20.35</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8377,19 +8695,19 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8400,17 +8718,17 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券拟发行5亿元，募集资金扣除发行费用后，拟全部用于偿还公司债券本金【23左海03 】</t>
+          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,剩余部分募集资金拟用于补充公司流动资金。</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,华福证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8431,22 +8749,22 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>福州左海控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>杭州钢铁集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
+          <t>2029-10-13</t>
         </is>
       </c>
       <c r="AK37" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL37" s="3" t="inlineStr">
@@ -8461,42 +8779,42 @@
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AV37" s="3" t="inlineStr">
@@ -8506,7 +8824,7 @@
       </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX37" s="3" t="inlineStr">
@@ -8524,64 +8842,72 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26常城建PPN002</t>
+          <t>26云能04</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
-        </is>
-      </c>
-      <c r="C38" s="3"/>
+          <t>10-09 19:00</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>246167.SH</t>
+        </is>
+      </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>6.64</v>
+        <v>15.0</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.55 ~ 2.05</t>
-        </is>
-      </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+          <t>1.60 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>48.22</v>
+      </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26常城05</t>
+          <t>25云能投MTN003</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>4.85Y</t>
+          <t>3.89Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.8288</t>
+          <t>1.8363</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8600/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>常州市城市建设(集团)有限公司</t>
+          <t>云南省能源集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.26</t>
+          <t>C- 23.42</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8591,7 +8917,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8601,19 +8927,19 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -8624,23 +8950,23 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行金额为6.64亿元,拟用于偿还发行人本部存量债务融资工具本金[21常城建MTN003,26常城建SCP001]</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,江苏银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,太平洋证券股份有限公司,平安证券股份有限公司,五矿证券有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8650,48 +8976,52 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>常州市城市建设(集团)有限公司2026年度第二期定向债务融资工具</t>
+          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-10-10</t>
-        </is>
-      </c>
-      <c r="AK38" s="3"/>
+          <t>2030-10-12</t>
+        </is>
+      </c>
+      <c r="AK38" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
@@ -8701,17 +9031,17 @@
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8739,9 +9069,7 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ38" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ38" s="3"/>
     </row>
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
@@ -8754,7 +9082,11 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C39" s="3"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>032680552.IB</t>
+        </is>
+      </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -8763,14 +9095,20 @@
       <c r="E39" s="4" t="n">
         <v>4.0</v>
       </c>
-      <c r="F39" s="3"/>
+      <c r="F39" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.10</t>
         </is>
       </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+      <c r="H39" s="4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>39.81</v>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
           <t>1.67</t>
@@ -8793,7 +9131,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -8803,7 +9141,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 12.27</t>
+          <t>C- 12.83</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8826,8 +9164,12 @@
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
+      <c r="U39" s="4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>1.26</v>
+      </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
           <t>7+</t>
@@ -8966,7 +9308,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26锡产业SCP015</t>
+          <t>26常城建PPN002</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8974,56 +9316,66 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C40" s="3"/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>032690031.IB</t>
+        </is>
+      </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F40" s="3"/>
+        <v>6.64</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>6.64</v>
+      </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
-        </is>
-      </c>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
+          <t>1.55 ~ 2.05</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>32.11</v>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>25锡产业MTN005</t>
+          <t>26常城05</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>271D</t>
+          <t>4.85Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.4940</t>
+          <t>1.8215</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/1.4800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司</t>
+          <t>常州市城市建设(集团)有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 21.65</t>
+          <t>C 29.73</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9038,7 +9390,7 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
@@ -9046,8 +9398,12 @@
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
+      <c r="U40" s="4" t="n">
+        <v>4.2377</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>1.19</v>
+      </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -9055,7 +9411,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -9066,23 +9422,23 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额6亿元用于归还发行人本部有息债务[26锡产业SCP006]</t>
+          <t>发行人本期定向债务融资工具发行金额为6.64亿元,拟用于偿还发行人本部存量债务融资工具本金[21常城建MTN003,26常城建SCP001]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>南京银行股份有限公司,江苏银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9097,17 +9453,17 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司2026年度第十五期超短期融资券</t>
+          <t>常州市城市建设(集团)有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2027-07-07</t>
+          <t>2031-10-10</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
@@ -9128,12 +9484,12 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
@@ -9143,17 +9499,17 @@
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9181,7 +9537,9 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ40" s="3"/>
+      <c r="AZ40" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-10-09.xlsx
+++ b/data/credit_bond_all_2026-10-09.xlsx
@@ -1679,7 +1679,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>1.6900/1.6600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="U7" s="4" t="n">
-        <v>3.57</v>
+        <v>3.5667</v>
       </c>
       <c r="V7" s="4" t="n">
         <v>1.0</v>
@@ -1858,7 +1858,7 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26海发宝诚SCP007</t>
+          <t>26连云港SCP004</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1868,49 +1868,49 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>012682380.IB</t>
+          <t>012682382.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>0.26Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.49</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>30.32</v>
+        <v>30.25</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>25海租01</t>
+          <t>26连云港SCP003</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>93D</t>
+          <t>248D</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.4631</t>
+          <t>1.5426</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>海发宝诚融资租赁有限公司</t>
+          <t>连云港港口集团有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C- 16.02</t>
+          <t>C- 13.46</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1948,37 +1948,41 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
+      <c r="U8" s="4" t="n">
+        <v>3.475</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.59%~1.63%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-连云港市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额0亿元，发行金额上限5亿元，拟全部用于偿还发行人即将到期的债务融资工具[26海发宝诚SCP006]</t>
+          <t>本期超短期融资券发行金额4.00亿元,募集资金全部用于偿还发行人存量有息债务。</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,上海银行股份有限公司</t>
+          <t>南京银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
@@ -1989,7 +1993,7 @@
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG8" s="3" t="inlineStr">
@@ -1999,7 +2003,7 @@
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>海发宝诚融资租赁有限公司2026年度第七期超短期融资券</t>
+          <t>连云港港口集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -2009,7 +2013,7 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK8" s="3"/>
@@ -2030,32 +2034,32 @@
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2084,13 +2088,13 @@
         </is>
       </c>
       <c r="AZ8" s="4" t="n">
-        <v>0.0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP004</t>
+          <t>26淮安国投MTN006</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2100,49 +2104,49 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>012682382.IB</t>
+          <t>102683878.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>30.25</v>
+        <v>32.81</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP003</t>
+          <t>26淮安国投MTN005</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>248D</t>
+          <t>1.90Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.5426</t>
+          <t>1.6140</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -2152,12 +2156,12 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司</t>
+          <t>淮安市国有联合投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C- 13.46</t>
+          <t>C 25.65</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2172,7 +2176,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -2181,10 +2185,10 @@
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>3.475</v>
+        <v>3.8</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.0</v>
+        <v>2.33</v>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
@@ -2193,34 +2197,34 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.63%</t>
+          <t>1.49%~1.59%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>江苏省-连云港市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4.00亿元,募集资金全部用于偿还发行人存量有息债务。</t>
+          <t>本期发行金额2亿元，募集资金拟全部用于偿还发行人到期债券[25淮安国投MTN002]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,中国银行股份有限公司</t>
+          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -2235,7 +2239,7 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司2026年度第四期超短期融资券</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2245,7 +2249,7 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
@@ -2266,7 +2270,7 @@
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
@@ -2281,17 +2285,17 @@
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2320,13 +2324,13 @@
         </is>
       </c>
       <c r="AZ9" s="4" t="n">
-        <v>0.005</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN006</t>
+          <t>26绍兴高新MTN003</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2336,49 +2340,49 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683878.IB</t>
+          <t>102683883.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.0</v>
+        <v>8.2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.0</v>
+        <v>8.2</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>32.81</v>
+        <v>41.11</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN005</t>
+          <t>26绍兴高新MTN002</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>1.90Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.6140</t>
+          <t>1.8213</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2388,12 +2392,12 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C 25.65</t>
+          <t>C- 23.35</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2403,12 +2407,12 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2417,40 +2421,38 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V10" s="4" t="n">
-        <v>2.33</v>
-      </c>
+        <v>5.04</v>
+      </c>
+      <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.59%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额2亿元，募集资金拟全部用于偿还发行人到期债券[25淮安国投MTN002]</t>
+          <t>发行人本期中期票据发行金额人民币8.20亿元,拟全部用于偿还发行人本级2026年到期的债务融资工具本金[23绍兴高新MTN002]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
@@ -2471,7 +2473,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年度第六期中期票据</t>
+          <t>绍兴高新技术产业开发区投资发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2481,10 +2483,14 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
-        </is>
-      </c>
-      <c r="AK10" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK10" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL10" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2502,12 +2508,12 @@
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
@@ -2517,12 +2523,12 @@
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
@@ -2555,14 +2561,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ10" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ10" s="3"/>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26绍兴高新MTN003</t>
+          <t>26阜阳投资PPN002</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2570,66 +2574,60 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>102683883.IB</t>
-        </is>
-      </c>
+      <c r="C11" s="3"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>8.2</v>
-      </c>
+        <v>4.75</v>
+      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.10</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>41.11</v>
+        <v>41.84</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26绍兴高新MTN002</t>
+          <t>26阜阳投资PPN001</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.8213</t>
+          <t>1.7226</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/1.7000</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
+          <t>阜阳投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C- 23.35</t>
+          <t>C- 23.56</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2639,12 +2637,12 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2653,17 +2651,19 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="V11" s="3"/>
+        <v>1.6</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>22.85</v>
+      </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -2674,23 +2674,23 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>安徽省-阜阳市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额人民币8.20亿元,拟全部用于偿还发行人本级2026年到期的债务融资工具本金[23绍兴高新MTN002]</t>
+          <t>本次定向债务融资工具注册规模12.15亿元，本期发行规模4.75亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,宁波银行股份有限公司</t>
+          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -2705,24 +2705,20 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>绍兴高新技术产业开发区投资发展集团有限公司2026年度第三期中期票据</t>
+          <t>阜阳投资发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK11" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-12</t>
+        </is>
+      </c>
+      <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2740,7 +2736,7 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
@@ -2750,17 +2746,17 @@
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
@@ -2793,73 +2789,79 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ11" s="3"/>
+      <c r="AZ11" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN002</t>
+          <t>26苏金04</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
-        </is>
-      </c>
-      <c r="C12" s="3"/>
+          <t>10-09 19:00</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>284122.SH</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>41.84</v>
+        <v>46.84</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN001</t>
+          <t>26苏金03</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.7226</t>
+          <t>1.7214</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1.7500/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司</t>
+          <t>苏州金合盛控股有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 23.56</t>
+          <t>C- 16.64</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2869,60 +2871,60 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>22.85</v>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>安徽省-阜阳市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具注册规模12.15亿元，本期发行规模4.75亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金。[23苏金04]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3"/>
+          <t>东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>苏州苏高新集团有限公司</t>
+        </is>
+      </c>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2932,12 +2934,12 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>苏州金合盛控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2947,55 +2949,59 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK12" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK12" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL12" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AM12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR12" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
       <c r="AU12" s="3" t="inlineStr">
         <is>
           <t/>
@@ -3003,7 +3009,7 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
@@ -3021,14 +3027,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ12" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ12" s="3"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26苏金04</t>
+          <t>26通新01</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3038,47 +3042,47 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>284122.SH</t>
+          <t>284151.SH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.6</v>
+        <v>5.0</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>46.84</v>
+        <v>41.11</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26苏金03</t>
+          <t>24通新03</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>3.05Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.7214</t>
+          <t>1.7098</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3088,12 +3092,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>苏州金合盛控股有限公司</t>
+          <t>南通高新控股集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C- 16.64</t>
+          <t>C- 19.83</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3120,28 +3124,28 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金。[23苏金04]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换偿还到期公司债券本金的自有资金[21通新01]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
@@ -3149,11 +3153,7 @@
           <t>东吴证券股份有限公司</t>
         </is>
       </c>
-      <c r="AD13" s="3" t="inlineStr">
-        <is>
-          <t>苏州苏高新集团有限公司</t>
-        </is>
-      </c>
+      <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>苏州金合盛控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>南通高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3181,14 +3181,10 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK13" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-13</t>
+        </is>
+      </c>
+      <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
           <t/>
@@ -3196,7 +3192,7 @@
       </c>
       <c r="AM13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN13" s="3" t="inlineStr">
@@ -3206,32 +3202,32 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3241,7 +3237,7 @@
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW13" s="3" t="inlineStr">
@@ -3264,7 +3260,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26通新01</t>
+          <t>26榕水02</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3274,7 +3270,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>284151.SH</t>
+          <t>525031.SZ</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3283,53 +3279,53 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>41.11</v>
+        <v>33.11</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>24通新03</t>
+          <t>24榕水04</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>3.05Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7098</t>
+          <t>1.7324</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>南通高新控股集团有限公司</t>
+          <t>福州水务集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 19.83</t>
+          <t>D+ 8.33</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3339,7 +3335,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3352,37 +3348,39 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="U14" s="3"/>
+      <c r="U14" s="4" t="n">
+        <v>4.86</v>
+      </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换偿还到期公司债券本金的自有资金[21通新01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务。[23榕水01]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>中信证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3398,17 +3396,17 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>南通高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>福州水务集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr">
@@ -3434,32 +3432,32 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3492,7 +3490,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26榕水02</t>
+          <t>26古厝13</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3502,16 +3500,16 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>525031.SZ</t>
+          <t>520514.SZ</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="inlineStr">
@@ -3520,44 +3518,44 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>33.11</v>
+        <v>34.81</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>24榕水04</t>
+          <t>24古厝01</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>2.63Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.7324</t>
+          <t>1.6920</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/1.7600</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>福州水务集团有限公司</t>
+          <t>福州古厝集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.33</t>
+          <t>C- 24.13</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3567,7 +3565,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3577,21 +3575,21 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.86</v>
+        <v>3.2</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3607,12 +3605,12 @@
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务。[23榕水01]</t>
+          <t>本期债券发行规模不超过5.00亿元（含），募集资金在扣除发行费用后，拟用于偿还发行人到期的公司债券本金。[25古厝D6]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华福证券股份有限公司</t>
+          <t>兴业证券股份有限公司,中国国际金融股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
@@ -3633,17 +3631,17 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>福州水务集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>福州古厝集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
@@ -3654,17 +3652,17 @@
       </c>
       <c r="AM15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
@@ -3672,24 +3670,12 @@
           <t>5.5</t>
         </is>
       </c>
-      <c r="AQ15" s="3" t="inlineStr">
-        <is>
-          <t>公用事业</t>
-        </is>
-      </c>
-      <c r="AR15" s="3" t="inlineStr">
-        <is>
-          <t>水务</t>
-        </is>
-      </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>水务</t>
-        </is>
-      </c>
+      <c r="AQ15" s="3"/>
+      <c r="AR15" s="3"/>
+      <c r="AS15" s="3"/>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3722,7 +3708,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26古厝13</t>
+          <t>26凯建01</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3732,62 +3718,62 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>520514.SZ</t>
+          <t>284219.SH</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>2.40 ~ 3.40</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.62</v>
+        <v>2.65</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>34.81</v>
+        <v>124.11</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>24古厝01</t>
+          <t>25凯建01</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.63Y</t>
+          <t>4.15Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.6920</t>
+          <t>2.8084</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司</t>
+          <t>凯里正源城镇建设发展有限责任公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 24.13</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3810,42 +3796,44 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U16" s="4" t="n">
-        <v>3.2</v>
-      </c>
+      <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>2.79%~2.89%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>贵州省-黔东南苗族侗族自治州</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过5.00亿元（含），募集资金在扣除发行费用后，拟用于偿还发行人到期的公司债券本金。[25古厝D6]</t>
+          <t>本期债券募集资金扣除承销费用后，拟全部用于统借统还偿还到期公司债券本金</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,中国国际金融股份有限公司,天风证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3"/>
+          <t>第一创业证券承销保荐有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>贵州省信用增进有限公司</t>
+        </is>
+      </c>
       <c r="AE16" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -3858,12 +3846,12 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>凯里正源城镇建设发展有限责任公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3873,10 +3861,14 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
-        </is>
-      </c>
-      <c r="AK16" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK16" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL16" s="3" t="inlineStr">
         <is>
           <t/>
@@ -3899,12 +3891,24 @@
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ16" s="3"/>
-      <c r="AR16" s="3"/>
-      <c r="AS16" s="3"/>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -3917,7 +3921,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
@@ -3940,7 +3944,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26凯建01</t>
+          <t>26左海02</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3950,62 +3954,62 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>284219.SH</t>
+          <t>284143.SH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2.40 ~ 3.40</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.65</v>
+        <v>1.69</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>124.11</v>
+        <v>28.11</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>25凯建01</t>
+          <t>25左海01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>4.15Y</t>
+          <t>3.26Y+5.00Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2.8084</t>
+          <t>1.7199</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>凯里正源城镇建设发展有限责任公司</t>
+          <t>福州左海控股集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>C- 21.87</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4015,7 +4019,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -4032,40 +4036,36 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>8-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>2.79%~2.89%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>贵州省-黔东南苗族侗族自治州</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除承销费用后，拟全部用于统借统还偿还到期公司债券本金</t>
+          <t>本期公司债券拟发行5亿元，募集资金扣除发行费用后，拟全部用于偿还公司债券本金【23左海03 】</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>第一创业证券承销保荐有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD17" s="3" t="inlineStr">
-        <is>
-          <t>贵州省信用增进有限公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,华福证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>凯里正源城镇建设发展有限责任公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>福州左海控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4118,12 +4118,12 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
@@ -4133,32 +4133,32 @@
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4176,7 +4176,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26左海02</t>
+          <t>26唐租01</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4186,62 +4186,62 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>284143.SH</t>
+          <t>246158.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>28.11</v>
+        <v>39.84</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>25左海01</t>
+          <t>25大唐租赁MTN002B(绿色)</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>3.26Y+5.00Y</t>
+          <t>1.63Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.7199</t>
+          <t>1.6333</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>福州左海控股集团有限公司</t>
+          <t>大唐融资租赁有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C- 21.87</t>
+          <t>C 27.94</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4261,19 +4261,19 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4284,17 +4284,17 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券拟发行5亿元，募集资金扣除发行费用后，拟全部用于偿还公司债券本金【23左海03 】</t>
+          <t>本期债券募集资金10.00亿元拟用于偿还发行人到期公司债券本金[24唐租04]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,华福证券股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
@@ -4315,22 +4315,22 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>福州左海控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>大唐融资租赁有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
+          <t>2029-10-13</t>
         </is>
       </c>
       <c r="AK18" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL18" s="3" t="inlineStr">
@@ -4345,42 +4345,42 @@
       </c>
       <c r="AN18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AV18" s="3" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4408,7 +4408,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26唐租01</t>
+          <t>26鲲鹏投资02</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4418,62 +4418,62 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>246158.SH</t>
+          <t>525030.SZ</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1+1</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.20 ~ 2.00</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>39.84</v>
+        <v>20.81</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>25大唐租赁MTN002B(绿色)</t>
+          <t>25鲲鹏02</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>1.63Y</t>
+          <t>1.07Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.6333</t>
+          <t>1.5373</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司</t>
+          <t>深圳市鲲鹏股权投资管理有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C 27.94</t>
+          <t>B- 43.09</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4493,19 +4493,19 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4516,17 +4516,17 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金10.00亿元拟用于偿还发行人到期公司债券本金[24唐租04]</t>
+          <t>本期债券发行规模为不超过16亿元(含16亿元),募集资金扣除发行费用后,拟使用不超过15亿元用于偿还到期的公司债券本金,剩余募集资金用于补充流动资金。[24鲲鹏04]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,招商证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
@@ -4537,17 +4537,17 @@
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>深圳市鲲鹏股权投资管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4557,14 +4557,10 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK19" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-10-12</t>
+        </is>
+      </c>
+      <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4572,12 +4568,12 @@
       </c>
       <c r="AM19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr">
@@ -4585,11 +4581,7 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP19" s="3"/>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
           <t>非银</t>
@@ -4597,12 +4589,12 @@
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
@@ -4612,7 +4604,7 @@
       </c>
       <c r="AU19" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-10-12</t>
         </is>
       </c>
       <c r="AV19" s="3" t="inlineStr">
@@ -4622,7 +4614,7 @@
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX19" s="3" t="inlineStr">
@@ -4640,72 +4632,74 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26鲲鹏投资02</t>
+          <t>26创星PPN002(科创债)</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>525030.SZ</t>
+          <t>032680550.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>1+1</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="F20" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.00</t>
+          <t>2.20 ~ 2.60</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.48</v>
+        <v>2.55</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>20.81</v>
+        <v>126.84</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>25鲲鹏02</t>
+          <t>25创星PPN001(科创债)</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>1.07Y</t>
+          <t>3.69Y+5.00Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.5373</t>
+          <t>1.7809</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>1.5500/--</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>深圳市鲲鹏股权投资管理有限公司</t>
+          <t>中科创星科技投资有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 43.09</t>
+          <t>D+ 6.00</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4715,7 +4709,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -4725,87 +4719,91 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U20" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>2.45%~2.55%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过16亿元(含16亿元),募集资金扣除发行费用后,拟使用不超过15亿元用于偿还到期的公司债券本金,剩余募集资金用于补充流动资金。[24鲲鹏04]</t>
+          <t>本次定向债务融资工具发行拟募集资金1亿元,所募集资金拟用于置换前期出资、新增基金出资以及补充流动资金</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>深圳市鲲鹏股权投资管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>中科创星科技投资有限公司2026年度第二期定向科技创新债券</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2029-10-10</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO20" s="3" t="inlineStr">
@@ -4831,12 +4829,12 @@
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
         <is>
-          <t>2027-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AV20" s="3" t="inlineStr">
@@ -4846,7 +4844,7 @@
       </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX20" s="3" t="inlineStr">
@@ -4859,12 +4857,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ20" s="3"/>
+      <c r="AZ20" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26锡产业SCP015</t>
+          <t>26广州产投SCP008</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>012682379.IB</t>
+          <t>012682378.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -4883,55 +4883,55 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>6.0</v>
+        <v>10.5</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6.0</v>
+        <v>10.5</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>31.25</v>
+        <v>24.25</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>25锡产业MTN005</t>
+          <t>26广州产投SCP007</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>271D</t>
+          <t>259D</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.4940</t>
+          <t>1.4923</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/1.4800</t>
+          <t>1.5000/1.4900</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司</t>
+          <t>广州产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 18.23</t>
+          <t>C- 19.95</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4955,19 +4955,19 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.82</v>
+        <v>1.06</v>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -4978,17 +4978,17 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额6亿元用于归还发行人本部有息债务[26锡产业SCP006]</t>
+          <t>本期超短期融资券的发行规模为10.5亿元，募集资金全部用于偿还到期债务融资工具[26 广州产投SCP002 ]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>平安银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司2026年度第十五期超短期融资券</t>
+          <t>广州产业投资控股集团有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5098,7 +5098,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26创星PPN002(科创债)</t>
+          <t>26鲁高速SCP004</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5108,64 +5108,64 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>032680550.IB</t>
+          <t>012682377.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.66Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.0</v>
+        <v>20.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.0</v>
+        <v>30.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.60</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.55</v>
+        <v>1.37</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>126.84</v>
+        <v>17.25</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>25创星PPN001(科创债)</t>
+          <t>24鲁高K3</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>3.69Y+5.00Y</t>
+          <t>290D</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.7809</t>
+          <t>1.4600</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/1.7600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>中科创星科技投资有限公司</t>
+          <t>山东高速集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.00</t>
+          <t>B- 41.63</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 10:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
@@ -5189,51 +5189,51 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1.5</v>
+        <v>1.5667</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>2.45%~2.55%</t>
+          <t>1.43%~1.47%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具发行拟募集资金1亿元,所募集资金拟用于置换前期出资、新增基金出资以及补充流动资金</t>
+          <t>本期超短期融资券基础发行金额20亿元，发行金额上限30亿元，募集资金用于偿还发行人本部及子公司有息负债及补充流动资金</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司</t>
+          <t>广发银行股份有限公司,北京银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
@@ -5243,17 +5243,17 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>中科创星科技投资有限公司2026年度第二期定向科技创新债券</t>
+          <t>山东高速集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2029-10-10</t>
+          <t>2027-06-07</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="AM22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN22" s="3" t="inlineStr">
@@ -5274,28 +5274,32 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP22" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5323,14 +5327,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ22" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ22" s="3"/>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP008</t>
+          <t>26南京公路MTN003</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5340,64 +5342,64 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>012682378.IB</t>
+          <t>102683875.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>10.5</v>
+        <v>2.0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>10.5</v>
+        <v>2.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>24.25</v>
+        <v>24.11</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP007</t>
+          <t>25南京公路MTN001</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>259D</t>
+          <t>3.83Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.4923</t>
+          <t>1.6928</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>1.5000/1.4900</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司</t>
+          <t>南京公路发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 19.95</t>
+          <t>C- 13.95</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5412,7 +5414,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -5421,44 +5423,50 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V23" s="3"/>
+        <v>2.5</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券的发行规模为10.5亿元，募集资金全部用于偿还到期债务融资工具[26 广州产投SCP002 ]</t>
+          <t>本期中期票据发行金额2亿元,募集资金用于偿还发行人本级及下属子公司有息债务</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,中信银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD23" s="3"/>
+          <t>南京银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr">
+        <is>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+        </is>
+      </c>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5473,7 +5481,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司2026年度第八期超短期融资券</t>
+          <t>南京公路发展(集团)有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5483,7 +5491,7 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2027-07-07</t>
+          <t>2031-10-10</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
@@ -5504,32 +5512,32 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5539,7 +5547,7 @@
       </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW23" s="3" t="inlineStr">
@@ -5557,12 +5565,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ23" s="3"/>
+      <c r="AZ23" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26鲁高速SCP004</t>
+          <t>26皖投集MTN006</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5572,49 +5582,49 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>012682377.IB</t>
+          <t>102683882.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>0.66Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>30.0</v>
+        <v>5.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>17.25</v>
+        <v>22.84</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>24鲁高K3</t>
+          <t>24皖投03</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>290D</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.4600</t>
+          <t>1.6119</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5624,12 +5634,12 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司</t>
+          <t>安徽省投资集团控股有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B- 41.63</t>
+          <t>C- 16.98</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5639,33 +5649,33 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>10-09 10:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.5667</v>
+        <v>5.16</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>9.0</v>
+        <v>3.08</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.43%~1.47%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -5676,23 +5686,23 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额20亿元，发行金额上限30亿元，募集资金用于偿还发行人本部及子公司有息负债及补充流动资金</t>
+          <t>本期中期票据募集资金5亿元人民币，全部用于偿还发行人即将到期的债券[25皖投集CP003]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司,北京银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,国家开发银行</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5707,7 +5717,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司2026年度第四期超短期融资券</t>
+          <t>安徽省投资集团控股有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5717,25 +5727,25 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2027-06-07</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM24" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>类城投</t>
@@ -5743,27 +5753,27 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5796,7 +5806,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26南京公路MTN003</t>
+          <t>26吴中经发MTN003</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5806,64 +5816,64 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>102683875.IB</t>
+          <t>102683881.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.0</v>
+        <v>5.7</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.0</v>
+        <v>5.7</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>24.11</v>
+        <v>26.11</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>25南京公路MTN001</t>
+          <t>26吴中经发MTN002</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>3.83Y</t>
+          <t>2.85Y+2.00Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.6928</t>
+          <t>1.6622</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.7100/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司</t>
+          <t>江苏省吴中经济技术发展集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 13.95</t>
+          <t>C- 15.92</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5878,28 +5888,26 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V25" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>5.49</v>
+      </c>
+      <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5910,24 +5918,20 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额2亿元,募集资金用于偿还发行人本级及下属子公司有息债务</t>
+          <t>本期中期票据发行金额5.70亿元,募集资金用于偿还债券[26吴中经发SCP001,26吴中经发SCP002,26吴中经发SCP003]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD25" s="3" t="inlineStr">
-        <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
-        </is>
-      </c>
+          <t>苏州银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -5945,7 +5949,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司2026年度第三期中期票据</t>
+          <t>江苏省吴中经济技术发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5955,25 +5959,29 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2031-10-10</t>
-        </is>
-      </c>
-      <c r="AK25" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK25" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL25" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM25" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>城投</t>
@@ -5981,7 +5989,7 @@
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
@@ -5991,32 +5999,32 @@
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX25" s="3" t="inlineStr">
@@ -6029,14 +6037,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ25" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ25" s="3"/>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26皖投集MTN006</t>
+          <t>26广州地铁SCP015</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6046,64 +6052,64 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>102683882.IB</t>
+          <t>012682381.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.0</v>
+        <v>14.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.0</v>
+        <v>14.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.26 ~ 1.55</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>22.84</v>
+        <v>15.25</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>24皖投03</t>
+          <t>17广州地铁专项债01</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.6119</t>
+          <t>1.4941</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/1.5900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司</t>
+          <t>广州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 16.98</t>
+          <t>C+ 33.99</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6118,7 +6124,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -6127,11 +6133,9 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>3.08</v>
-      </c>
+        <v>3.89</v>
+      </c>
+      <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -6139,7 +6143,7 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -6150,23 +6154,23 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金5亿元人民币，全部用于偿还发行人即将到期的债券[25皖投集CP003]</t>
+          <t>本期超短期融资券金额14亿元，其中5亿元用于归还发行人存量债券，9亿元用于归还发行人金融机构借款。[26广州地铁SCP001]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,国家开发银行</t>
+          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6181,7 +6185,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司2026年度第六期中期票据</t>
+          <t>广州地铁集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6191,7 +6195,7 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
@@ -6217,27 +6221,27 @@
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6270,7 +6274,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26吴中经发MTN003</t>
+          <t>26广州地铁SCP014</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6280,64 +6284,64 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>102683881.IB</t>
+          <t>012682383.IB</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.7</v>
+        <v>20.0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.7</v>
+        <v>20.0</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.26 ~ 1.55</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>26.11</v>
+        <v>15.25</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26吴中经发MTN002</t>
+          <t>17广州地铁专项债01</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2.85Y+2.00Y</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.6622</t>
+          <t>1.4941</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>江苏省吴中经济技术发展集团有限公司</t>
+          <t>广州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 15.92</t>
+          <t>C+ 33.99</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6361,44 +6365,44 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>5.49</v>
+        <v>3.79</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额5.70亿元,募集资金用于偿还债券[26吴中经发SCP001,26吴中经发SCP002,26吴中经发SCP003]</t>
+          <t>本期超短期融资券金额20亿元，全部用于归还发行人的债务融资工具。[26广州地铁SCP001]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>苏州银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6413,7 +6417,7 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>江苏省吴中经济技术发展集团有限公司2026年度第三期中期票据</t>
+          <t>广州地铁集团有限公司2026年度第十四期超短期融资券</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6423,14 +6427,10 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK27" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-07-09</t>
+        </is>
+      </c>
+      <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
@@ -6463,22 +6463,22 @@
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AV27" s="3" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">
@@ -6506,59 +6506,57 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26广州地铁SCP015</t>
+          <t>26天长01</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>012682381.IB</t>
+          <t>284203.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>14.0</v>
-      </c>
+        <v>8.0</v>
+      </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.55</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>15.25</v>
+        <v>46.84</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>17广州地铁专项债01</t>
+          <t>25滁高01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>1.64Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.4941</t>
+          <t>1.6256</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6568,12 +6566,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司</t>
+          <t>天长市科技工业发展有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.99</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6583,7 +6581,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6596,45 +6594,51 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U28" s="4" t="n">
-        <v>3.89</v>
-      </c>
+      <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>安徽省-滁州市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券金额14亿元，其中5亿元用于归还发行人存量债券，9亿元用于归还发行人金融机构借款。[26广州地铁SCP001]</t>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还“23天长02”公司债券本金。[23天长02]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD28" s="3"/>
+          <t>五矿证券有限公司,川财证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr">
+        <is>
+          <t>安徽省信用融资担保集团有限公司</t>
+        </is>
+      </c>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
@@ -6644,28 +6648,28 @@
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司2026年度第十五期超短期融资券</t>
+          <t>天长市科技工业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t/>
         </is>
       </c>
       <c r="AM28" s="3" t="inlineStr">
@@ -6680,12 +6684,12 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
@@ -6695,17 +6699,17 @@
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6715,7 +6719,7 @@
       </c>
       <c r="AV28" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW28" s="3" t="inlineStr">
@@ -6738,7 +6742,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26广州地铁SCP014</t>
+          <t>26杭金投MTN004</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6748,64 +6752,64 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>012682383.IB</t>
+          <t>102683873.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>1.5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.55</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>15.25</v>
+        <v>17.85</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>17广州地铁专项债01</t>
+          <t>26杭金投MTN001</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>1.69Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.4941</t>
+          <t>1.6154</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司</t>
+          <t>杭州市金融投资集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.99</t>
+          <t>C- 17.41</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6820,26 +6824,28 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="V29" s="3"/>
+        <v>3.3</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>1.54</v>
+      </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.53%~1.63%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6850,23 +6856,23 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券金额20亿元，全部用于归还发行人的债务融资工具。[26广州地铁SCP001]</t>
+          <t>本次中期票据募集资金10亿元，拟全部用于偿还发行人即将到期的债务融资工具【26 杭金投SCP001】</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
+          <t>浙商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6881,7 +6887,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司2026年度第十四期超短期融资券</t>
+          <t>杭州市金融投资集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6891,13 +6897,13 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2028-04-10</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
@@ -6907,37 +6913,37 @@
       </c>
       <c r="AN29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6970,7 +6976,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城MTN001</t>
+          <t>26莆田国资MTN002</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6980,49 +6986,49 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>102683877.IB</t>
+          <t>102683876.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.88</v>
+        <v>10.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.88</v>
+        <v>10.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>36.81</v>
+        <v>40.84</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城CP001</t>
+          <t>26莆田国资MTN001</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>159D</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.5334</t>
+          <t>1.6718</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -7032,12 +7038,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司</t>
+          <t>莆田市国有资产投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B- 37.23</t>
+          <t>C+ 33.96</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7047,12 +7053,12 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -7061,19 +7067,17 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>1.8</v>
-      </c>
+        <v>5.26</v>
+      </c>
+      <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -7084,17 +7088,17 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>福建省-莆田市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>首期拟发行金额6.88亿元募集资金拟用于偿还发行人存量债务融资工具本金[25宿迁新城CP002]</t>
+          <t>发行人本期中期票据发行金额为10亿元,拟用于偿还发行人本部接续债务融资工具的专项贷款。[21莆田国资PPN003]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,交通银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -7115,7 +7119,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司2026年度第一期中期票据</t>
+          <t>莆田市国有资产投资集团有限责任公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7125,7 +7129,7 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
@@ -7146,27 +7150,27 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
@@ -7199,14 +7203,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ30" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ30" s="3"/>
     </row>
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26天长01</t>
+          <t>26蜀道K9</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7216,62 +7218,62 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>284203.SH</t>
+          <t>525034.SZ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.0</v>
+        <v>25.0</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>46.84</v>
+        <v>21.11</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>25滁高01</t>
+          <t>24蜀道05</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>1.64Y</t>
+          <t>5.01Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.6256</t>
+          <t>1.7267</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7200</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>天长市科技工业发展有限公司</t>
+          <t>蜀道投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B- 36.12</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7294,48 +7296,42 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U31" s="3"/>
+      <c r="U31" s="4" t="n">
+        <v>4.26</v>
+      </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>安徽省-滁州市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,全部用于偿还“23天长02”公司债券本金。[23天长02]</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资以及符合国家法律法规要求的其他用途。</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司,川财证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD31" s="3" t="inlineStr">
-        <is>
-          <t>安徽省信用融资担保集团有限公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司,天府证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -7348,25 +7344,29 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>天长市科技工业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>蜀道投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第九期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK31" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK31" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7384,12 +7384,12 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="AV31" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW31" s="3" t="inlineStr">
@@ -7442,74 +7442,72 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26杭金投MTN004</t>
+          <t>26中航K5</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>102683873.IB</t>
+          <t>525028.SZ</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>7.0</v>
+      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>17.85</v>
+        <v>24.84</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26杭金投MTN001</t>
+          <t>26中航K3</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>1.69Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.6154</t>
+          <t>1.6223</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>1.6400/--</t>
+          <t>1.6500/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>杭州市金融投资集团有限公司</t>
+          <t>中航科创有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 17.41</t>
+          <t>C+ 34.11</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7519,25 +7517,21 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>1.54</v>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -7545,7 +7539,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.63%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7553,41 +7547,45 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z32" s="3"/>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据募集资金10亿元，拟全部用于偿还发行人即将到期的债务融资工具【26 杭金投SCP001】</t>
+          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>杭州市金融投资集团有限公司2026年度第四期中期票据</t>
+          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7597,53 +7595,57 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2028-04-10</t>
-        </is>
-      </c>
-      <c r="AK32" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK32" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AM32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>航空装备</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7676,59 +7678,57 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26莆田国资MTN002</t>
+          <t>26中航K6</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>102683876.IB</t>
+          <t>525029.SZ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>7.0</v>
+      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>40.84</v>
+        <v>26.11</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26莆田国资MTN001</t>
+          <t>26中航K4</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.6718</t>
+          <t>1.7088</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>莆田市国有资产投资集团有限责任公司</t>
+          <t>中航科创有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.96</t>
+          <t>C+ 34.11</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7753,73 +7753,75 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U33" s="4" t="n">
-        <v>5.26</v>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z33" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>福建省-莆田市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为10亿元,拟用于偿还发行人本部接续债务融资工具的专项贷款。[21莆田国资PPN003]</t>
+          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
+          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>莆田市国有资产投资集团有限责任公司2026年度第二期中期票据</t>
+          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7829,33 +7831,33 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2031-10-13</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
@@ -7865,17 +7867,17 @@
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>航空装备</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7908,7 +7910,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26蜀道K9</t>
+          <t>26杭钢02</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7918,16 +7920,16 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>525034.SZ</t>
+          <t>246177.SH</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
@@ -7936,44 +7938,44 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>21.11</v>
+        <v>31.84</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>24蜀道05</t>
+          <t>26杭钢01</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>5.01Y</t>
+          <t>2.49Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.7267</t>
+          <t>1.6419</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/1.7200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司</t>
+          <t>杭州钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>B- 36.12</t>
+          <t>C- 20.35</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7983,7 +7985,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7993,21 +7995,19 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="n">
-        <v>4.26</v>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -8018,17 +8018,17 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资以及符合国家法律法规要求的其他用途。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,剩余部分募集资金拟用于补充公司流动资金。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,天府证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
@@ -8044,12 +8044,12 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第九期)</t>
+          <t>杭州钢铁集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
+          <t>2029-10-13</t>
         </is>
       </c>
       <c r="AK34" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL34" s="3" t="inlineStr">
@@ -8079,37 +8079,37 @@
       </c>
       <c r="AN34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8142,7 +8142,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26中航K5</t>
+          <t>26云能04</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8152,62 +8152,62 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>525028.SZ</t>
+          <t>246167.SH</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>24.84</v>
+        <v>48.22</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26中航K3</t>
+          <t>25云能投MTN003</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>3.89Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.6223</t>
+          <t>1.8363</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1.6500/--</t>
+          <t>1.8600/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司</t>
+          <t>云南省能源集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.11</t>
+          <t>C- 23.42</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8227,19 +8227,19 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8247,24 +8247,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,太平洋证券股份有限公司,平安证券股份有限公司,五矿证券有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -8275,17 +8271,17 @@
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
+          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8295,7 +8291,7 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
+          <t>2030-10-12</t>
         </is>
       </c>
       <c r="AK35" s="3" t="inlineStr">
@@ -8315,7 +8311,7 @@
       </c>
       <c r="AN35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO35" s="3" t="inlineStr">
@@ -8325,7 +8321,7 @@
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
@@ -8335,17 +8331,17 @@
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>航空装备</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8378,72 +8374,74 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26中航K6</t>
+          <t>26兴化城投PPN009</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>525029.SZ</t>
+          <t>032680552.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
         <v>1.67</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>26.11</v>
+        <v>39.81</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26中航K4</t>
+          <t>26兴化城投PPN008</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>1.88Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.7088</t>
+          <t>1.6847</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司</t>
+          <t>兴化市城市建设投资有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.11</t>
+          <t>C- 12.83</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8453,7 +8451,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8463,91 +8461,91 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>1.26</v>
+      </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
+          <t>本期定向债务融资工具发行金额4亿元,拟用于偿还发行人有息债务[26兴化城投PPN002]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>江苏江南农村商业银行股份有限公司,苏州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
+          <t>兴化市城市建设投资有限公司2026年度第九期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
+          <t>2028-10-10</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO36" s="3" t="inlineStr">
@@ -8557,7 +8555,7 @@
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
@@ -8567,17 +8565,17 @@
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>航空装备</t>
+          <t>农产品加工</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8610,57 +8608,59 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26杭钢02</t>
+          <t>26常城建PPN002</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>246177.SH</t>
+          <t>032690031.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>6.64</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>6.64</v>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.55 ~ 2.05</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>31.84</v>
+        <v>32.11</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26杭钢01</t>
+          <t>26常城05</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>2.49Y</t>
+          <t>4.85Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.6419</t>
+          <t>1.8215</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -8670,12 +8670,12 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司</t>
+          <t>常州市城市建设(集团)有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C- 20.35</t>
+          <t>C 29.73</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8685,29 +8685,33 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U37" s="4" t="n">
+        <v>4.2377</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>1.19</v>
+      </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8718,23 +8722,23 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,剩余部分募集资金拟用于补充公司流动资金。</t>
+          <t>发行人本期定向债务融资工具发行金额为6.64亿元,拟用于偿还发行人本部存量债务融资工具本金[21常城建MTN003,26常城建SCP001]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>南京银行股份有限公司,江苏银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8744,79 +8748,75 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>常州市城市建设(集团)有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK37" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-10</t>
+        </is>
+      </c>
+      <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>燃气</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM37" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AO37" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ37" s="3" t="inlineStr">
-        <is>
-          <t>金属和非金属矿产</t>
-        </is>
-      </c>
-      <c r="AR37" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>普钢</t>
-        </is>
-      </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV37" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8837,109 +8837,117 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ37" s="3"/>
+      <c r="AZ37" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26云能04</t>
+          <t>26锡产业SCP015</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>246167.SH</t>
+          <t>012682379.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.31 ~ 1.51</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>25锡产业MTN005</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>271D</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>1.4940</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>无锡产业发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>C- 18.23</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>10-09 09:00</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>1.2333</v>
+      </c>
+      <c r="V38" s="4" t="n">
         <v>1.82</v>
       </c>
-      <c r="I38" s="4" t="n">
-        <v>48.22</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>25云能投MTN003</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>3.89Y</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>1.8363</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>1.8600/--</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>云南省能源集团有限公司</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t>C- 23.42</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>10-09 16:00</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -8950,23 +8958,23 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还有息债务</t>
+          <t>本期超短期融资券发行金额6亿元用于归还发行人本部有息债务[26锡产业SCP006]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,太平洋证券股份有限公司,平安证券股份有限公司,五矿证券有限公司</t>
+          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8976,12 +8984,12 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>无锡产业发展集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8991,27 +8999,23 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2030-10-12</t>
-        </is>
-      </c>
-      <c r="AK38" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-07-07</t>
+        </is>
+      </c>
+      <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO38" s="3" t="inlineStr">
@@ -9021,7 +9025,7 @@
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
@@ -9031,12 +9035,12 @@
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
@@ -9074,7 +9078,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26兴化城投PPN009</t>
+          <t>26海发宝诚SCP007</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -9084,64 +9088,64 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>032680552.IB</t>
+          <t>012682380.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.26Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.35 ~ 1.49</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>39.81</v>
+        <v>30.32</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26兴化城投PPN008</t>
+          <t>25海租01</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>1.88Y</t>
+          <t>93D</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.6847</t>
+          <t>1.4631</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.7100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>兴化市城市建设投资有限公司</t>
+          <t>海发宝诚融资租赁有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 12.83</t>
+          <t>C- 16.02</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9161,55 +9165,55 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>3.6</v>
+        <v>1.0</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>1.26</v>
+        <v>1.0</v>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额4亿元,拟用于偿还发行人有息债务[26兴化城投PPN002]</t>
+          <t>本期超短期融资券基础发行金额0亿元，发行金额上限5亿元，拟全部用于偿还发行人即将到期的债务融资工具[26海发宝诚SCP006]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>江苏江南农村商业银行股份有限公司,苏州银行股份有限公司</t>
+          <t>平安银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG39" s="3" t="inlineStr">
@@ -9219,63 +9223,63 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>兴化市城市建设投资有限公司2026年度第九期定向债务融资工具</t>
+          <t>海发宝诚融资租赁有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2028-10-10</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>农产品加工</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9303,12 +9307,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ39" s="3"/>
+      <c r="AZ39" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26常城建PPN002</t>
+          <t>26宿迁新城MTN001</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9318,49 +9324,49 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>032690031.IB</t>
+          <t>102683877.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>6.64</v>
+        <v>6.88</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>6.64</v>
+        <v>6.88</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.55 ~ 2.05</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>32.11</v>
+        <v>36.81</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26常城05</t>
+          <t>26宿迁新城CP001</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.85Y</t>
+          <t>159D</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.8215</t>
+          <t>1.5334</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -9370,12 +9376,12 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>常州市城市建设(集团)有限公司</t>
+          <t>宿迁市新城控股集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C 29.73</t>
+          <t>B- 37.23</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9390,55 +9396,55 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>4.2377</v>
+        <v>4.6584</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>1.19</v>
+        <v>1.8</v>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行金额为6.64亿元,拟用于偿还发行人本部存量债务融资工具本金[21常城建MTN003,26常城建SCP001]</t>
+          <t>首期拟发行金额6.88亿元募集资金拟用于偿还发行人存量债务融资工具本金[25宿迁新城CP002]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,江苏银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>南京银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9453,35 +9459,35 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>常州市城市建设(集团)有限公司2026年度第二期定向债务融资工具</t>
+          <t>宿迁市新城控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-10-10</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM40" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>城投</t>
@@ -9489,27 +9495,27 @@
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-10-09.xlsx
+++ b/data/credit_bond_all_2026-10-09.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-12" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-13" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.03</t>
+          <t>C+ 32.87</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN003B</t>
+          <t>26安市淮阴MTN001</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -934,49 +934,49 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>102690061.IB</t>
+          <t>102683884.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>61.36</v>
+        <v>46.84</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN002B</t>
+          <t>25安市淮阴MTN003</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>6.86Y</t>
+          <t>1.52Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.0881</t>
+          <t>1.6621</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
+          <t>淮安市淮阴区城市资产经营有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 24.60</t>
+          <t>C- 15.83</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -1015,17 +1015,19 @@
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V4" s="3"/>
+        <v>1.46</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>4.67</v>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>2.27%~2.37%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1036,17 +1038,17 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期债券基础发行规模为0亿元,发行金额上限为10亿元,募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN003]</t>
+          <t>本次发行金额5亿元,募集资金拟全部用于偿还发行人本部及下属子公司有息债务[26安市淮阴CP001]</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
@@ -1067,7 +1069,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据(品种二)</t>
+          <t>淮安市淮阴区城市资产经营有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1077,14 +1079,10 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2036-10-12</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-12</t>
+        </is>
+      </c>
+      <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -1102,12 +1100,12 @@
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
@@ -1127,7 +1125,7 @@
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>食品加工</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
@@ -1155,12 +1153,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ4" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN003A</t>
+          <t>26镇江产投MTN008</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>102690060.IB</t>
+          <t>102683874.IB</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
@@ -1186,44 +1186,48 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>30.84</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN002B</t>
+          <t>26镇江产投MTN007</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>6.86Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>2.0881</t>
+          <t>1.6876</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6900/1.6600</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
+          <t>镇江产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 24.60</t>
+          <t>C- 13.22</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1233,50 +1237,54 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>3.5667</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>2.21%~2.31%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期债券基础发行规模为0亿元,发行金额上限为10亿元,募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN003]</t>
+          <t>发行人本次发行的3.00亿元中期票据全部用于偿还发行人存量有息债务[25镇江产投CP004]</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>中国民生银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD5" s="3"/>
@@ -1297,7 +1305,7 @@
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据(品种一)</t>
+          <t>镇江产业投资控股集团有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
@@ -1307,13 +1315,13 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2033-10-12</t>
+          <t>2029-10-10</t>
         </is>
       </c>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
@@ -1323,12 +1331,12 @@
       </c>
       <c r="AN5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr">
@@ -1343,17 +1351,17 @@
       </c>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>食品加工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr">
@@ -1381,22 +1389,24 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ5" s="3"/>
+      <c r="AZ5" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26安市淮阴MTN001</t>
+          <t>26苏金04</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>102683884.IB</t>
+          <t>284122.SH</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1405,14 +1415,12 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
@@ -1423,22 +1431,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>25安市淮阴MTN003</t>
+          <t>26苏金03</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>1.52Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.6621</t>
+          <t>1.7214</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1448,12 +1456,12 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>淮安市淮阴区城市资产经营有限公司</t>
+          <t>苏州金合盛控股有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C- 17.97</t>
+          <t>C- 19.19</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1463,60 +1471,60 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>4.67</v>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本次发行金额5亿元,募集资金拟全部用于偿还发行人本部及下属子公司有息债务[26安市淮阴CP001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金。[23苏金04]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD6" s="3"/>
+          <t>东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>苏州苏高新集团有限公司</t>
+        </is>
+      </c>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
@@ -1526,70 +1534,74 @@
       </c>
       <c r="AG6" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>淮安市淮阴区城市资产经营有限公司2026年度第一期中期票据</t>
+          <t>苏州金合盛控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK6" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL6" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AM6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR6" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
       <c r="AU6" s="3" t="inlineStr">
         <is>
           <t/>
@@ -1597,7 +1609,7 @@
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW6" s="3" t="inlineStr">
@@ -1615,66 +1627,62 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ6" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ6" s="3"/>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26镇江产投MTN008</t>
+          <t>26通新01</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>102683874.IB</t>
+          <t>284151.SH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>3.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>30.84</v>
+        <v>41.11</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>26镇江产投MTN007</t>
+          <t>24通新03</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>3.05Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.6876</t>
+          <t>1.7098</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1684,12 +1692,12 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>镇江产业投资控股集团有限公司</t>
+          <t>南通高新控股集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C- 13.33</t>
+          <t>C- 18.24</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1699,60 +1707,56 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>3.5667</v>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>1.0</v>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行的3.00亿元中期票据全部用于偿还发行人存量有息债务[25镇江产投CP004]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换偿还到期公司债券本金的自有资金[21通新01]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,南京银行股份有限公司</t>
+          <t>东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -1762,68 +1766,68 @@
       </c>
       <c r="AG7" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>镇江产业投资控股集团有限公司2026年度第八期中期票据</t>
+          <t>南通高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2029-10-10</t>
+          <t>2031-10-13</t>
         </is>
       </c>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AM7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1851,81 +1855,77 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ7" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ7" s="3"/>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP004</t>
+          <t>26榕水02</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>012682382.IB</t>
+          <t>525031.SZ</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>4.0</v>
-      </c>
+        <v>7.0</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>30.25</v>
+        <v>33.11</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP003</t>
+          <t>24榕水04</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>248D</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.5426</t>
+          <t>1.7324</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司</t>
+          <t>福州水务集团有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C- 13.46</t>
+          <t>D+ 8.33</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -1945,50 +1945,48 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U8" s="4" t="n">
-        <v>3.475</v>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>4.86</v>
+      </c>
+      <c r="V8" s="3"/>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.63%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>江苏省-连云港市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4.00亿元,募集资金全部用于偿还发行人存量有息债务。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务。[23榕水01]</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,中国银行股份有限公司</t>
+          <t>中信证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
@@ -1998,12 +1996,12 @@
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司2026年度第四期超短期融资券</t>
+          <t>福州水务集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -2013,28 +2011,28 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2031-10-13</t>
         </is>
       </c>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AM8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
@@ -2044,22 +2042,22 @@
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2087,81 +2085,79 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ8" s="4" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="AZ8" s="3"/>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN006</t>
+          <t>26左海02</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>102683878.IB</t>
+          <t>284143.SH</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>32.81</v>
+        <v>28.11</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN005</t>
+          <t>25左海01</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>1.90Y</t>
+          <t>3.26Y+5.00Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.6140</t>
+          <t>1.7199</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>福州左海控股集团有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C 25.65</t>
+          <t>C 27.65</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2171,12 +2167,12 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -2185,19 +2181,17 @@
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>2.33</v>
-      </c>
+        <v>4.56</v>
+      </c>
+      <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.59%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -2208,23 +2202,23 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额2亿元，募集资金拟全部用于偿还发行人到期债券[25淮安国投MTN002]</t>
+          <t>本期公司债券拟发行5亿元，募集资金扣除发行费用后，拟全部用于偿还公司债券本金【23左海03 】</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -2234,28 +2228,32 @@
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年度第六期中期票据</t>
+          <t>福州左海控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
-        </is>
-      </c>
-      <c r="AK9" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK9" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t/>
         </is>
       </c>
       <c r="AM9" s="3" t="inlineStr">
@@ -2270,12 +2268,12 @@
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
@@ -2285,22 +2283,22 @@
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AV9" s="3" t="inlineStr">
@@ -2310,7 +2308,7 @@
       </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX9" s="3" t="inlineStr">
@@ -2323,66 +2321,62 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ9" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ9" s="3"/>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26绍兴高新MTN003</t>
+          <t>26唐租01</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683883.IB</t>
+          <t>246158.SH</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>8.2</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>41.11</v>
+        <v>39.84</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26绍兴高新MTN002</t>
+          <t>25大唐租赁MTN002B(绿色)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>1.63Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.8213</t>
+          <t>1.6333</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2392,12 +2386,12 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
+          <t>大唐融资租赁有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 23.35</t>
+          <t>C+ 33.38</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2407,22 +2401,20 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="n">
-        <v>5.04</v>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
@@ -2431,49 +2423,49 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额人民币8.20亿元,拟全部用于偿还发行人本级2026年到期的债务融资工具本金[23绍兴高新MTN002]</t>
+          <t>本期债券募集资金10.00亿元拟用于偿还发行人到期公司债券本金[24唐租04]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,宁波银行股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>绍兴高新技术产业开发区投资发展集团有限公司2026年度第三期中期票据</t>
+          <t>大唐融资租赁有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2483,57 +2475,57 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
+          <t>2029-10-13</t>
         </is>
       </c>
       <c r="AK10" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL10" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AM10" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2566,7 +2558,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN002</t>
+          <t>26创星PPN002(科创债)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2574,60 +2566,66 @@
           <t>10-09 18:00</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>032680550.IB</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
+          <t>2.20 ~ 2.60</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>41.84</v>
+        <v>126.84</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN001</t>
+          <t>25创星PPN001(科创债)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>3.69Y+5.00Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.7226</t>
+          <t>1.7809</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>1.7500/1.7000</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司</t>
+          <t>中科创星科技投资有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C- 23.56</t>
+          <t>D+ 9.13</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2642,49 +2640,49 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>22.85</v>
+        <v>1.0</v>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>2.45%~2.55%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>安徽省-阜阳市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具注册规模12.15亿元，本期发行规模4.75亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004]</t>
+          <t>本次定向债务融资工具发行拟募集资金1亿元,所募集资金拟用于置换前期出资、新增基金出资以及补充流动资金</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
@@ -2695,7 +2693,7 @@
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
@@ -2705,7 +2703,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>中科创星科技投资有限公司2026年度第二期定向科技创新债券</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2715,53 +2713,49 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2029-10-10</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP11" s="3"/>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
-        </is>
-      </c>
-      <c r="AR11" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS11" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2796,72 +2790,74 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26苏金04</t>
+          <t>26广州产投SCP008</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>284122.SH</t>
+          <t>012682378.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>10.5</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>10.5</v>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>46.84</v>
+        <v>24.25</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26苏金03</t>
+          <t>26广州产投SCP007</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>259D</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.7214</t>
+          <t>1.4923</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/1.4900</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>苏州金合盛控股有限公司</t>
+          <t>广州产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 16.64</t>
+          <t>C- 23.54</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2871,7 +2867,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2881,50 +2877,50 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>1.06</v>
+      </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金。[23苏金04]</t>
+          <t>本期超短期融资券的发行规模为10.5亿元，募集资金全部用于偿还到期债务融资工具[26 广州产投SCP002 ]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>苏州苏高新集团有限公司</t>
-        </is>
-      </c>
+          <t>平安银行股份有限公司,中信银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2934,82 +2930,78 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>苏州金合盛控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>广州产业投资控股集团有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK12" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-07-07</t>
+        </is>
+      </c>
+      <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AO12" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ12" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR12" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
@@ -3032,57 +3024,59 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26通新01</t>
+          <t>26鲁高速SCP004</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>284151.SH</t>
+          <t>012682377.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.66Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F13" s="3"/>
+        <v>20.0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>30.0</v>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.82</v>
+        <v>1.37</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>41.11</v>
+        <v>17.25</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>24通新03</t>
+          <t>24鲁高K3</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>3.05Y</t>
+          <t>290D</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.7098</t>
+          <t>1.4600</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3092,12 +3086,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>南通高新控股集团有限公司</t>
+          <t>山东高速集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C- 19.83</t>
+          <t>B- 43.18</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3107,56 +3101,60 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 10:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>1.5667</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>9.0</v>
+      </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.43%~1.47%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换偿还到期公司债券本金的自有资金[21通新01]</t>
+          <t>本期超短期融资券基础发行金额20亿元，发行金额上限30亿元，募集资金用于偿还发行人本部及子公司有息负债及补充流动资金</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>广发银行股份有限公司,北京银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3166,48 +3164,48 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>南通高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>山东高速集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
+          <t>2027-06-07</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
@@ -3217,17 +3215,17 @@
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3260,17 +3258,17 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26榕水02</t>
+          <t>26南京公路MTN003</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>525031.SZ</t>
+          <t>102683875.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3279,53 +3277,55 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F14" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>33.11</v>
+        <v>24.11</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>24榕水04</t>
+          <t>25南京公路MTN001</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>3.83Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7324</t>
+          <t>1.6928</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/1.7600</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>福州水务集团有限公司</t>
+          <t>南京公路发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.33</t>
+          <t>C- 11.53</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3335,58 +3335,64 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="V14" s="3"/>
+        <v>2.5</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务。[23榕水01]</t>
+          <t>本期中期票据发行金额2亿元,募集资金用于偿还发行人本级及下属子公司有息债务</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华福证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD14" s="3"/>
+          <t>南京银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr">
+        <is>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+        </is>
+      </c>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3396,12 +3402,12 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>福州水务集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>南京公路发展(集团)有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3411,63 +3417,63 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
+          <t>2031-10-10</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>高速公路</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AO14" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ14" s="3" t="inlineStr">
-        <is>
-          <t>公用事业</t>
-        </is>
-      </c>
-      <c r="AR14" s="3" t="inlineStr">
-        <is>
-          <t>水务</t>
-        </is>
-      </c>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>水务</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>水务</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW14" s="3" t="inlineStr">
@@ -3485,77 +3491,81 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ14" s="3"/>
+      <c r="AZ14" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26古厝13</t>
+          <t>26皖投集MTN006</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>520514.SZ</t>
+          <t>102683882.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>34.81</v>
+        <v>22.84</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>24古厝01</t>
+          <t>24皖投03</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>2.63Y</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.6920</t>
+          <t>1.6119</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/1.5900</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司</t>
+          <t>安徽省投资集团控股有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 24.13</t>
+          <t>C- 16.85</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3565,12 +3575,12 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -3579,17 +3589,19 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V15" s="3"/>
+        <v>5.16</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>3.08</v>
+      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3600,23 +3612,23 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过5.00亿元（含），募集资金在扣除发行费用后，拟用于偿还发行人到期的公司债券本金。[25古厝D6]</t>
+          <t>本期中期票据募集资金5亿元人民币，全部用于偿还发行人即将到期的债券[25皖投集CP003]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,中国国际金融股份有限公司,天风证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,国家开发银行</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3626,28 +3638,28 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>安徽省投资集团控股有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AM15" s="3" t="inlineStr">
@@ -3662,7 +3674,7 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
@@ -3670,12 +3682,24 @@
           <t>5.5</t>
         </is>
       </c>
-      <c r="AQ15" s="3"/>
-      <c r="AR15" s="3"/>
-      <c r="AS15" s="3"/>
+      <c r="AQ15" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3708,57 +3732,59 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26凯建01</t>
+          <t>26涪陵国资MTN003</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>284219.SH</t>
+          <t>102690061.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F16" s="3"/>
+        <v>7.0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2.40 ~ 3.40</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>124.11</v>
+        <v>61.36</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>25凯建01</t>
+          <t>26涪陵国资MTN002B</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.15Y</t>
+          <t>6.86Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>2.8084</t>
+          <t>2.0881</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3768,12 +3794,12 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>凯里正源城镇建设发展有限责任公司</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>C- 24.65</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3783,7 +3809,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3796,47 +3822,45 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U16" s="3"/>
+      <c r="U16" s="4" t="n">
+        <v>2.7</v>
+      </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>8-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>2.79%~2.89%</t>
+          <t>2.27%~2.37%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>贵州省-黔东南苗族侗族自治州</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除承销费用后，拟全部用于统借统还偿还到期公司债券本金</t>
+          <t>本期债券基础发行规模为0亿元,发行金额上限为10亿元,募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN003]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>第一创业证券承销保荐有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3" t="inlineStr">
-        <is>
-          <t>贵州省信用增进有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3846,22 +3870,22 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>凯里正源城镇建设发展有限责任公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
+          <t>2036-10-12</t>
         </is>
       </c>
       <c r="AK16" s="3" t="inlineStr">
@@ -3871,57 +3895,57 @@
       </c>
       <c r="AL16" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>食品加工</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO16" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="AQ16" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR16" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS16" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
@@ -3944,72 +3968,68 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26左海02</t>
+          <t>26涪陵国资MTN003A(取消发行)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>284143.SH</t>
+          <t>DY102690060.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>28.11</v>
-      </c>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>25左海01</t>
+          <t>26涪陵国资MTN002B</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>3.26Y+5.00Y</t>
+          <t>6.86Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.7199</t>
+          <t>2.0881</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>福州左海控股集团有限公司</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 21.87</t>
+          <t>C- 24.65</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4019,7 +4039,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -4036,39 +4056,39 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>2.21%~2.31%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券拟发行5亿元，募集资金扣除发行费用后，拟全部用于偿还公司债券本金【23左海03 】</t>
+          <t>本期债券基础发行规模为0亿元,发行金额上限为10亿元,募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN003]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,华福证券股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4078,79 +4098,75 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>福州左海控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK17" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2033-10-12</t>
+        </is>
+      </c>
+      <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>食品加工</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM17" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO17" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ17" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR17" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>高速公路</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
-        <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4158,7 +4174,7 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4176,7 +4192,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26唐租01</t>
+          <t>26云能04</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4186,62 +4202,64 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>246158.SH</t>
+          <t>246167.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F18" s="3"/>
+        <v>15.0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>15.0</v>
+      </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>39.84</v>
+        <v>48.22</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>25大唐租赁MTN002B(绿色)</t>
+          <t>25云能投MTN003</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>1.63Y</t>
+          <t>3.89Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.6333</t>
+          <t>1.8363</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8600/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司</t>
+          <t>云南省能源集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C 27.94</t>
+          <t>C- 23.68</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4261,10 +4279,12 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U18" s="3"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>3.19</v>
+      </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
@@ -4273,7 +4293,7 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4284,17 +4304,17 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金10.00亿元拟用于偿还发行人到期公司债券本金[24唐租04]</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,招商证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,太平洋证券股份有限公司,平安证券股份有限公司,五矿证券有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4305,7 +4325,7 @@
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
@@ -4315,7 +4335,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4325,7 +4345,7 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
+          <t>2030-10-12</t>
         </is>
       </c>
       <c r="AK18" s="3" t="inlineStr">
@@ -4340,42 +4360,42 @@
       </c>
       <c r="AM18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4429,7 +4449,9 @@
       <c r="E19" s="4" t="n">
         <v>16.0</v>
       </c>
-      <c r="F19" s="3"/>
+      <c r="F19" s="4" t="n">
+        <v>16.0</v>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
           <t>1.20 ~ 2.00</t>
@@ -4473,7 +4495,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 43.09</t>
+          <t>C+ 33.56</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4496,7 +4518,9 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U19" s="3"/>
+      <c r="U19" s="4" t="n">
+        <v>3.06</v>
+      </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
@@ -4632,7 +4656,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26创星PPN002(科创债)</t>
+          <t>26淮安国投MTN006</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4642,64 +4666,64 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>032680550.IB</t>
+          <t>102683878.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.60</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>126.84</v>
+        <v>32.81</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>25创星PPN001(科创债)</t>
+          <t>26淮安国投MTN005</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>3.69Y+5.00Y</t>
+          <t>1.90Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.7809</t>
+          <t>1.6140</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/1.7600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>中科创星科技投资有限公司</t>
+          <t>淮安市国有联合投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.00</t>
+          <t>C 25.84</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4714,60 +4738,60 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.0</v>
+        <v>2.33</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>2.45%~2.55%</t>
+          <t>1.49%~1.59%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具发行拟募集资金1亿元,所募集资金拟用于置换前期出资、新增基金出资以及补充流动资金</t>
+          <t>本期发行金额2亿元，募集资金拟全部用于偿还发行人到期债券[25淮安国投MTN002]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司</t>
+          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr">
@@ -4777,59 +4801,63 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>中科创星科技投资有限公司2026年度第二期定向科技创新债券</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2029-10-10</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP20" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4858,13 +4886,13 @@
         </is>
       </c>
       <c r="AZ20" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP008</t>
+          <t>26绍兴高新MTN003</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4874,64 +4902,64 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>012682378.IB</t>
+          <t>102683883.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>10.5</v>
+        <v>8.2</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>10.5</v>
+        <v>8.2</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24.25</v>
+        <v>41.11</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP007</t>
+          <t>26绍兴高新MTN002</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>259D</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.4923</t>
+          <t>1.8213</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1.5000/1.4900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司</t>
+          <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 19.95</t>
+          <t>C- 20.62</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4941,60 +4969,58 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>1.06</v>
-      </c>
+        <v>5.04</v>
+      </c>
+      <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券的发行规模为10.5亿元，募集资金全部用于偿还到期债务融资工具[26 广州产投SCP002 ]</t>
+          <t>发行人本期中期票据发行金额人民币8.20亿元,拟全部用于偿还发行人本级2026年到期的债务融资工具本金[23绍兴高新MTN002]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -5009,7 +5035,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司2026年度第八期超短期融资券</t>
+          <t>绍兴高新技术产业开发区投资发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5019,53 +5045,57 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2027-07-07</t>
-        </is>
-      </c>
-      <c r="AK21" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK21" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL21" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM21" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5098,7 +5128,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26鲁高速SCP004</t>
+          <t>26广州地铁SCP014</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5108,49 +5138,49 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>012682377.IB</t>
+          <t>012682383.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>0.66Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
         <v>20.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.26 ~ 1.55</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>17.25</v>
+        <v>15.25</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>24鲁高K3</t>
+          <t>17广州地铁专项债01</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>290D</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.4600</t>
+          <t>1.4941</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -5160,12 +5190,12 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司</t>
+          <t>广州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 41.63</t>
+          <t>C+ 32.28</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5175,33 +5205,31 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>10-09 10:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1.5667</v>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>9.0</v>
-      </c>
+        <v>3.79</v>
+      </c>
+      <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.43%~1.47%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5212,17 +5240,17 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额20亿元，发行金额上限30亿元，募集资金用于偿还发行人本部及子公司有息负债及补充流动资金</t>
+          <t>本期超短期融资券金额20亿元，全部用于归还发行人的债务融资工具。[26广州地铁SCP001]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司,北京银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
@@ -5243,7 +5271,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司2026年度第四期超短期融资券</t>
+          <t>广州地铁集团有限公司2026年度第十四期超短期融资券</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5253,25 +5281,25 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2027-06-07</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM22" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>类城投</t>
@@ -5279,7 +5307,7 @@
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
@@ -5289,17 +5317,17 @@
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5332,7 +5360,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26南京公路MTN003</t>
+          <t>26宿迁新城MTN001</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5342,64 +5370,64 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>102683875.IB</t>
+          <t>102683877.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.0</v>
+        <v>6.88</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.0</v>
+        <v>6.88</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>24.11</v>
+        <v>36.81</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>25南京公路MTN001</t>
+          <t>26宿迁新城CP001</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>3.83Y</t>
+          <t>159D</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.6928</t>
+          <t>1.5334</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>1.7100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司</t>
+          <t>宿迁市新城控股集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 13.95</t>
+          <t>C+ 34.88</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5419,23 +5447,23 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.5</v>
+        <v>4.6584</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.0</v>
+        <v>1.8</v>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5446,24 +5474,20 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额2亿元,募集资金用于偿还发行人本级及下属子公司有息债务</t>
+          <t>首期拟发行金额6.88亿元募集资金拟用于偿还发行人存量债务融资工具本金[25宿迁新城CP002]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD23" s="3" t="inlineStr">
-        <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
-        </is>
-      </c>
+          <t>南京银行股份有限公司,交通银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -5481,7 +5505,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司2026年度第三期中期票据</t>
+          <t>宿迁市新城控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5491,25 +5515,25 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-10-10</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM23" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>城投</t>
@@ -5517,7 +5541,7 @@
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
@@ -5527,17 +5551,17 @@
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5547,7 +5571,7 @@
       </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW23" s="3" t="inlineStr">
@@ -5572,7 +5596,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26皖投集MTN006</t>
+          <t>26连云港SCP004</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5582,49 +5606,49 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102683882.IB</t>
+          <t>012682382.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>22.84</v>
+        <v>30.25</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>24皖投03</t>
+          <t>26连云港SCP003</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>248D</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.6119</t>
+          <t>1.5426</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5634,12 +5658,12 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司</t>
+          <t>连云港港口集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C- 16.98</t>
+          <t>C- 12.75</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5654,7 +5678,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -5663,46 +5687,46 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>5.16</v>
+        <v>3.475</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.08</v>
+        <v>1.0</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.59%~1.63%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>江苏省-连云港市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金5亿元人民币，全部用于偿还发行人即将到期的债券[25皖投集CP003]</t>
+          <t>本期超短期融资券发行金额4.00亿元,募集资金全部用于偿还发行人存量有息债务。</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,国家开发银行</t>
+          <t>南京银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5717,7 +5741,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司2026年度第六期中期票据</t>
+          <t>连云港港口集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5727,7 +5751,7 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
@@ -5748,7 +5772,7 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
@@ -5758,22 +5782,22 @@
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5801,12 +5825,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ24" s="3"/>
+      <c r="AZ24" s="4" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26吴中经发MTN003</t>
+          <t>26莆田国资MTN002</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5816,64 +5842,64 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>102683881.IB</t>
+          <t>102683876.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.7</v>
+        <v>10.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.7</v>
+        <v>10.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>26.11</v>
+        <v>40.84</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26吴中经发MTN002</t>
+          <t>26莆田国资MTN001</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>2.85Y+2.00Y</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.6622</t>
+          <t>1.6718</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>江苏省吴中经济技术发展集团有限公司</t>
+          <t>莆田市国有资产投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 15.92</t>
+          <t>C- 22.97</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5883,12 +5909,12 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -5897,17 +5923,17 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>5.49</v>
+        <v>5.26</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5918,17 +5944,17 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>福建省-莆田市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额5.70亿元,募集资金用于偿还债券[26吴中经发SCP001,26吴中经发SCP002,26吴中经发SCP003]</t>
+          <t>发行人本期中期票据发行金额为10亿元,拟用于偿还发行人本部接续债务融资工具的专项贷款。[21莆田国资PPN003]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>苏州银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
@@ -5949,7 +5975,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>江苏省吴中经济技术发展集团有限公司2026年度第三期中期票据</t>
+          <t>莆田市国有资产投资集团有限责任公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5959,14 +5985,10 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK25" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-12</t>
+        </is>
+      </c>
+      <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -5984,37 +6006,37 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AV25" s="3" t="inlineStr">
@@ -6024,7 +6046,7 @@
       </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX25" s="3" t="inlineStr">
@@ -6042,7 +6064,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26广州地铁SCP015</t>
+          <t>26吴中经发MTN003</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6052,64 +6074,64 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>012682381.IB</t>
+          <t>102683881.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>14.0</v>
+        <v>5.7</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>14.0</v>
+        <v>5.7</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.55</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>15.25</v>
+        <v>26.11</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>17广州地铁专项债01</t>
+          <t>26吴中经发MTN002</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>2.85Y+2.00Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.4941</t>
+          <t>1.6622</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司</t>
+          <t>江苏省吴中经济技术发展集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.99</t>
+          <t>C- 16.95</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6133,44 +6155,44 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.89</v>
+        <v>5.4912</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券金额14亿元，其中5亿元用于归还发行人存量债券，9亿元用于归还发行人金融机构借款。[26广州地铁SCP001]</t>
+          <t>本期中期票据发行金额5.70亿元,募集资金用于偿还债券[26吴中经发SCP001,26吴中经发SCP002,26吴中经发SCP003]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
+          <t>苏州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6185,7 +6207,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司2026年度第十五期超短期融资券</t>
+          <t>江苏省吴中经济技术发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6195,10 +6217,14 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
-        </is>
-      </c>
-      <c r="AK26" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK26" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL26" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -6216,12 +6242,12 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
@@ -6231,22 +6257,22 @@
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AV26" s="3" t="inlineStr">
@@ -6256,7 +6282,7 @@
       </c>
       <c r="AW26" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX26" s="3" t="inlineStr">
@@ -6274,7 +6300,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26广州地铁SCP014</t>
+          <t>26阜阳投资PPN002</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6284,64 +6310,64 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>012682383.IB</t>
+          <t>032680548.IB</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>20.0</v>
+        <v>4.75</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>20.0</v>
+        <v>4.75</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.55</t>
+          <t>1.40 ~ 2.10</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>15.25</v>
+        <v>41.84</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>17广州地铁专项债01</t>
+          <t>26阜阳投资PPN001</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.4941</t>
+          <t>1.7226</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/1.7000</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司</t>
+          <t>阜阳投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.99</t>
+          <t>C- 22.00</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6356,7 +6382,7 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
@@ -6365,44 +6391,46 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="V27" s="3"/>
+        <v>4.8632</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>22.85</v>
+      </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>安徽省-阜阳市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券金额20亿元，全部用于归还发行人的债务融资工具。[26广州地铁SCP001]</t>
+          <t>本次定向债务融资工具注册规模12.15亿元，本期发行规模4.75亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
+          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6417,17 +6445,17 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司2026年度第十四期超短期融资券</t>
+          <t>阜阳投资发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
@@ -6448,32 +6476,32 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6501,77 +6529,81 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ27" s="3"/>
+      <c r="AZ27" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26天长01</t>
+          <t>26杭金投MTN004</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>284203.SH</t>
+          <t>102683873.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1.5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F28" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>46.84</v>
+        <v>17.85</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>25滁高01</t>
+          <t>26杭金投MTN001</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>1.64Y</t>
+          <t>1.69Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.6256</t>
+          <t>1.6154</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>天长市科技工业发展有限公司</t>
+          <t>杭州市金融投资集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 19.13</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6581,64 +6613,60 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>1.54</v>
+      </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.53%~1.63%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>安徽省-滁州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,全部用于偿还“23天长02”公司债券本金。[23天长02]</t>
+          <t>本次中期票据募集资金10亿元，拟全部用于偿还发行人即将到期的债务融资工具【26 杭金投SCP001】</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司,川财证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD28" s="3" t="inlineStr">
-        <is>
-          <t>安徽省信用融资担保集团有限公司</t>
-        </is>
-      </c>
+          <t>浙商银行股份有限公司,中国工商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
@@ -6648,78 +6676,78 @@
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>天长市科技工业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>杭州市金融投资集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2028-04-10</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO28" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ28" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR28" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV28" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW28" s="3" t="inlineStr">
@@ -6742,74 +6770,74 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26杭金投MTN004</t>
+          <t>26蜀道K9</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>102683873.IB</t>
+          <t>525034.SZ</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>17.85</v>
+        <v>21.11</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26杭金投MTN001</t>
+          <t>24蜀道05</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>1.69Y</t>
+          <t>5.01Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.6154</t>
+          <t>1.7267</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.6400/--</t>
+          <t>--/1.7200</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>杭州市金融投资集团有限公司</t>
+          <t>蜀道投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 17.41</t>
+          <t>C+ 34.43</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6819,33 +6847,31 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V29" s="4" t="n">
-        <v>1.54</v>
-      </c>
+        <v>4.26</v>
+      </c>
+      <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.63%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6856,23 +6882,23 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据募集资金10亿元，拟全部用于偿还发行人即将到期的债务融资工具【26 杭金投SCP001】</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资以及符合国家法律法规要求的其他用途。</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,天府证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6882,12 +6908,12 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>杭州市金融投资集团有限公司2026年度第四期中期票据</t>
+          <t>蜀道投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第九期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6897,28 +6923,32 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2028-04-10</t>
-        </is>
-      </c>
-      <c r="AK29" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL29" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM29" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
@@ -6928,22 +6958,22 @@
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6976,17 +7006,17 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26莆田国资MTN002</t>
+          <t>26中航K5</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>102683876.IB</t>
+          <t>525028.SZ</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -6995,55 +7025,53 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>7.0</v>
+      </c>
+      <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>40.84</v>
+        <v>24.84</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26莆田国资MTN001</t>
+          <t>26中航K3</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.6718</t>
+          <t>1.6223</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6500/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>莆田市国有资产投资集团有限责任公司</t>
+          <t>中航科创有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.96</t>
+          <t>C+ 31.30</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7053,73 +7081,75 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="n">
-        <v>5.26</v>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z30" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>福建省-莆田市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为10亿元,拟用于偿还发行人本部接续债务融资工具的专项贷款。[21莆田国资PPN003]</t>
+          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
+          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>莆田市国有资产投资集团有限责任公司2026年度第二期中期票据</t>
+          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7129,33 +7159,37 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK30" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK30" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AM30" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
@@ -7165,17 +7199,17 @@
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>航空装备</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7208,7 +7242,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26蜀道K9</t>
+          <t>26中航K6</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7218,7 +7252,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>525034.SZ</t>
+          <t>525029.SZ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -7227,53 +7261,53 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>25.0</v>
+        <v>7.0</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>21.11</v>
+        <v>26.11</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>24蜀道05</t>
+          <t>26中航K4</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>5.01Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7267</t>
+          <t>1.7088</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/1.7200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司</t>
+          <t>中航科创有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>B- 36.12</t>
+          <t>C+ 31.30</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7283,7 +7317,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7293,21 +7327,19 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U31" s="4" t="n">
-        <v>4.26</v>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7315,20 +7347,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z31" s="3"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资以及符合国家法律法规要求的其他用途。</t>
+          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,天府证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司</t>
+          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
@@ -7339,7 +7375,7 @@
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -7349,7 +7385,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第九期)</t>
+          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7359,14 +7395,10 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK31" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-13</t>
+        </is>
+      </c>
+      <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7374,42 +7406,42 @@
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>航空装备</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7442,7 +7474,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26中航K5</t>
+          <t>26杭钢02</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7452,7 +7484,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>525028.SZ</t>
+          <t>246177.SH</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -7461,7 +7493,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
@@ -7470,44 +7502,44 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>24.84</v>
+        <v>31.84</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26中航K3</t>
+          <t>26杭钢01</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>2.49Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.6223</t>
+          <t>1.6419</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>1.6500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司</t>
+          <t>杭州钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.11</t>
+          <t>C- 20.59</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7517,7 +7549,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7534,12 +7566,12 @@
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7547,24 +7579,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,剩余部分募集资金拟用于补充公司流动资金。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
@@ -7575,17 +7603,17 @@
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
+          <t>杭州钢铁集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7610,7 +7638,7 @@
       </c>
       <c r="AM32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN32" s="3" t="inlineStr">
@@ -7625,27 +7653,27 @@
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>航空装备</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7678,17 +7706,17 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26中航K6</t>
+          <t>26常城建PPN002</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>525029.SZ</t>
+          <t>032690031.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -7697,38 +7725,40 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F33" s="3"/>
+        <v>6.64</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>6.64</v>
+      </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.55 ~ 2.05</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>26.11</v>
+        <v>32.11</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26中航K4</t>
+          <t>26常城05</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>4.85Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.7088</t>
+          <t>1.8215</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -7738,12 +7768,12 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司</t>
+          <t>常州市城市建设(集团)有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.11</t>
+          <t>C 27.12</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7753,21 +7783,25 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>4.2377</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>1.19</v>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -7783,199 +7817,199 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
+          <t>发行人本期定向债务融资工具发行金额为6.64亿元,拟用于偿还发行人本部存量债务融资工具本金[21常城建MTN003,26常城建SCP001]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>南京银行股份有限公司,江苏银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
+          <t>常州市城市建设(集团)有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
+          <t>2031-10-10</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>燃气</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY33" s="3" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AO33" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="AQ33" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR33" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>航空装备</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV33" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW33" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX33" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AZ33" s="3"/>
+      <c r="AZ33" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26杭钢02</t>
+          <t>26锡产业SCP015</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>246177.SH</t>
+          <t>012682379.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.31 ~ 1.51</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>31.84</v>
+        <v>31.25</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26杭钢01</t>
+          <t>25锡产业MTN005</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.49Y</t>
+          <t>271D</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.6419</t>
+          <t>1.4940</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4800</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司</t>
+          <t>无锡产业发展集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 20.35</t>
+          <t>C- 18.79</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7985,7 +8019,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7995,19 +8029,23 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>1.2333</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>1.82</v>
+      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -8018,23 +8056,23 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,剩余部分募集资金拟用于补充公司流动资金。</t>
+          <t>本期超短期融资券发行金额6亿元用于归还发行人本部有息债务[26锡产业SCP006]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -8044,12 +8082,12 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>无锡产业发展集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -8059,17 +8097,13 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-07-07</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
@@ -8079,7 +8113,7 @@
       </c>
       <c r="AN34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO34" s="3" t="inlineStr">
@@ -8089,27 +8123,27 @@
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8142,7 +8176,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26云能04</t>
+          <t>26古厝13</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8152,62 +8186,64 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>246167.SH</t>
+          <t>520514.SZ</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="F35" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>48.22</v>
+        <v>34.81</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>25云能投MTN003</t>
+          <t>24古厝01</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>3.89Y</t>
+          <t>2.63Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.8363</t>
+          <t>1.6920</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1.8600/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司</t>
+          <t>福州古厝集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 23.42</t>
+          <t>C- 21.71</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8217,7 +8253,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8230,16 +8266,18 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U35" s="3"/>
+      <c r="U35" s="4" t="n">
+        <v>3.2</v>
+      </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8250,17 +8288,17 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还有息债务</t>
+          <t>本期债券发行规模不超过5.00亿元（含），募集资金在扣除发行费用后，拟用于偿还发行人到期的公司债券本金。[25古厝D6]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,太平洋证券股份有限公司,平安证券股份有限公司,五矿证券有限公司</t>
+          <t>兴业证券股份有限公司,中国国际金融股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -8276,29 +8314,25 @@
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>福州古厝集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2030-10-12</t>
-        </is>
-      </c>
-      <c r="AK35" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-10-12</t>
+        </is>
+      </c>
+      <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8306,7 +8340,7 @@
       </c>
       <c r="AM35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN35" s="3" t="inlineStr">
@@ -8316,32 +8350,20 @@
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ35" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR35" s="3" t="inlineStr">
-        <is>
-          <t>产业集团</t>
-        </is>
-      </c>
-      <c r="AS35" s="3" t="inlineStr">
-        <is>
-          <t>产业集团</t>
-        </is>
-      </c>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3"/>
+      <c r="AR35" s="3"/>
+      <c r="AS35" s="3"/>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8374,7 +8396,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26兴化城投PPN009</t>
+          <t>26海发宝诚SCP007</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8384,64 +8406,64 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>032680552.IB</t>
+          <t>012682380.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.26Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.35 ~ 1.49</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>39.81</v>
+        <v>30.32</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26兴化城投PPN008</t>
+          <t>25海租01</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>1.88Y</t>
+          <t>93D</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.6847</t>
+          <t>1.4631</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.7100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>兴化市城市建设投资有限公司</t>
+          <t>海发宝诚融资租赁有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 12.83</t>
+          <t>C- 14.76</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8461,55 +8483,55 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>3.6</v>
+        <v>1.0</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>1.26</v>
+        <v>1.0</v>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额4亿元,拟用于偿还发行人有息债务[26兴化城投PPN002]</t>
+          <t>本期超短期融资券基础发行金额0亿元，发行金额上限5亿元，拟全部用于偿还发行人即将到期的债务融资工具[26海发宝诚SCP006]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>江苏江南农村商业银行股份有限公司,苏州银行股份有限公司</t>
+          <t>平安银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
@@ -8519,63 +8541,63 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>兴化市城市建设投资有限公司2026年度第九期定向债务融资工具</t>
+          <t>海发宝诚融资租赁有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2028-10-10</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM36" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>农产品加工</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8603,12 +8625,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ36" s="3"/>
+      <c r="AZ36" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26常城建PPN002</t>
+          <t>26广州地铁SCP015</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8618,49 +8642,49 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>032690031.IB</t>
+          <t>012682381.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>6.64</v>
+        <v>14.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>6.64</v>
+        <v>14.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.55 ~ 2.05</t>
+          <t>1.26 ~ 1.55</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>32.11</v>
+        <v>15.25</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26常城05</t>
+          <t>17广州地铁专项债01</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>4.85Y</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.8215</t>
+          <t>1.4941</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -8670,12 +8694,12 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>常州市城市建设(集团)有限公司</t>
+          <t>广州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C 29.73</t>
+          <t>C+ 32.28</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8690,28 +8714,26 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>4.2377</v>
-      </c>
-      <c r="V37" s="4" t="n">
-        <v>1.19</v>
-      </c>
+        <v>3.89</v>
+      </c>
+      <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8722,23 +8744,23 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行金额为6.64亿元,拟用于偿还发行人本部存量债务融资工具本金[21常城建MTN003,26常城建SCP001]</t>
+          <t>本期超短期融资券金额14亿元，其中5亿元用于归还发行人存量债券，9亿元用于归还发行人金融机构借款。[26广州地铁SCP001]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,江苏银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8753,63 +8775,63 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>常州市城市建设(集团)有限公司2026年度第二期定向债务融资工具</t>
+          <t>广州地铁集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2031-10-10</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM37" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8837,66 +8859,64 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ37" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ37" s="3"/>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26锡产业SCP015</t>
+          <t>26天长01</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>012682379.IB</t>
+          <t>284203.SH</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>31.25</v>
+        <v>46.84</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>25锡产业MTN005</t>
+          <t>25滁高01</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>271D</t>
+          <t>1.64Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.4940</t>
+          <t>1.6256</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -8906,12 +8926,12 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司</t>
+          <t>天长市科技工业发展有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C- 18.23</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8921,7 +8941,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8931,50 +8951,56 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>1.2333</v>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>1.82</v>
-      </c>
+        <v>4.2</v>
+      </c>
+      <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>安徽省-滁州市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额6亿元用于归还发行人本部有息债务[26锡产业SCP006]</t>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还“23天长02”公司债券本金。[23天长02]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD38" s="3"/>
+          <t>五矿证券有限公司,川财证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr">
+        <is>
+          <t>安徽省信用融资担保集团有限公司</t>
+        </is>
+      </c>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8984,70 +9010,70 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司2026年度第十五期超短期融资券</t>
+          <t>天长市科技工业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2027-07-07</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR38" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
       <c r="AU38" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9055,7 +9081,7 @@
       </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW38" s="3" t="inlineStr">
@@ -9078,59 +9104,59 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26海发宝诚SCP007</t>
+          <t>26凯建01</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>012682380.IB</t>
+          <t>284219.SH</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>0.26Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.49</t>
+          <t>2.40 ~ 3.40</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.48</v>
+        <v>2.65</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>30.32</v>
+        <v>124.11</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>25海租01</t>
+          <t>25凯建01</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>93D</t>
+          <t>4.15Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.4631</t>
+          <t>2.8084</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -9140,12 +9166,12 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>海发宝诚融资租赁有限公司</t>
+          <t>凯里正源城镇建设发展有限责任公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 16.02</t>
+          <t>B- 42.31</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9155,7 +9181,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -9169,77 +9195,83 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>2.66</v>
+      </c>
+      <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8-</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>2.79%~2.89%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>贵州省-黔东南苗族侗族自治州</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额0亿元，发行金额上限5亿元，拟全部用于偿还发行人即将到期的债务融资工具[26海发宝诚SCP006]</t>
+          <t>本期债券募集资金扣除承销费用后，拟全部用于统借统还偿还到期公司债券本金</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,上海银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD39" s="3"/>
+          <t>第一创业证券承销保荐有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr">
+        <is>
+          <t>贵州省信用增进有限公司</t>
+        </is>
+      </c>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>海发宝诚融资租赁有限公司2026年度第七期超短期融资券</t>
+          <t>凯里正源城镇建设发展有限责任公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
-        </is>
-      </c>
-      <c r="AK39" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK39" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t/>
         </is>
       </c>
       <c r="AM39" s="3" t="inlineStr">
@@ -9254,32 +9286,32 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9289,7 +9321,7 @@
       </c>
       <c r="AV39" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW39" s="3" t="inlineStr">
@@ -9307,14 +9339,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ39" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ39" s="3"/>
     </row>
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城MTN001</t>
+          <t>26兴化城投PPN009</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9324,7 +9354,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>102683877.IB</t>
+          <t>032680552.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -9333,55 +9363,55 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>6.88</v>
+        <v>4.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>6.88</v>
+        <v>4.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>36.81</v>
+        <v>39.81</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城CP001</t>
+          <t>26兴化城投PPN008</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>159D</t>
+          <t>1.88Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.5334</t>
+          <t>1.6847</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司</t>
+          <t>兴化市城市建设投资有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>B- 37.23</t>
+          <t>C- 17.15</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9396,55 +9426,55 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>4.6584</v>
+        <v>3.6</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>首期拟发行金额6.88亿元募集资金拟用于偿还发行人存量债务融资工具本金[25宿迁新城CP002]</t>
+          <t>本期定向债务融资工具发行金额4亿元,拟用于偿还发行人有息债务[26兴化城投PPN002]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,交通银行股份有限公司</t>
+          <t>江苏江南农村商业银行股份有限公司,苏州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9459,23 +9489,23 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司2026年度第一期中期票据</t>
+          <t>兴化市城市建设投资有限公司2026年度第九期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2028-10-10</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM40" s="3" t="inlineStr">
@@ -9485,37 +9515,37 @@
       </c>
       <c r="AN40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>农产品加工</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9543,9 +9573,7 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ40" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ40" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-10-09.xlsx
+++ b/data/credit_bond_all_2026-10-09.xlsx
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.3</v>
+        <v>1.3143</v>
       </c>
       <c r="V12" s="4" t="n">
         <v>1.06</v>
@@ -3732,7 +3732,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN003</t>
+          <t>26涪陵国资MTN003A(取消发行)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3742,34 +3742,28 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102690061.IB</t>
+          <t>DY102690060.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>61.36</v>
-      </c>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -3822,9 +3816,7 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U16" s="4" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
@@ -3833,7 +3825,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>2.27%~2.37%</t>
+          <t>2.21%~2.31%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3875,7 +3867,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3885,14 +3877,10 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2036-10-12</t>
-        </is>
-      </c>
-      <c r="AK16" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2033-10-12</t>
+        </is>
+      </c>
+      <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -3968,68 +3956,74 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN003A(取消发行)</t>
+          <t>26云能04</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>DY102690060.IB</t>
+          <t>246167.SH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>15.0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>15.0</v>
+      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+          <t>1.60 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>48.22</v>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN002B</t>
+          <t>25云能投MTN003</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>6.86Y</t>
+          <t>3.89Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2.0881</t>
+          <t>1.8363</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8600/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
+          <t>云南省能源集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 24.65</t>
+          <t>C- 23.68</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4039,7 +4033,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -4052,43 +4046,45 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U17" s="3"/>
+      <c r="U17" s="4" t="n">
+        <v>3.19</v>
+      </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>2.21%~2.31%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券基础发行规模为0亿元,发行金额上限为10亿元,募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN003]</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,太平洋证券股份有限公司,平安证券股份有限公司,五矿证券有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4098,12 +4094,12 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据(品种一)(取消发行)</t>
+          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4113,18 +4109,22 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2033-10-12</t>
-        </is>
-      </c>
-      <c r="AK17" s="3"/>
+          <t>2030-10-12</t>
+        </is>
+      </c>
+      <c r="AK17" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t/>
         </is>
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4134,12 +4134,12 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
@@ -4149,17 +4149,17 @@
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>食品加工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4192,7 +4192,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26云能04</t>
+          <t>26鲲鹏投资02</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4202,64 +4202,64 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>246167.SH</t>
+          <t>525030.SZ</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>1+1</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.20 ~ 2.00</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>48.22</v>
+        <v>20.81</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>25云能投MTN003</t>
+          <t>25鲲鹏02</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>3.89Y</t>
+          <t>1.07Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.8363</t>
+          <t>1.5373</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1.8600/--</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司</t>
+          <t>深圳市鲲鹏股权投资管理有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C- 23.68</t>
+          <t>C+ 33.56</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4283,17 +4283,17 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4304,17 +4304,17 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还有息债务</t>
+          <t>本期债券发行规模为不超过16亿元(含16亿元),募集资金扣除发行费用后,拟使用不超过15亿元用于偿还到期的公司债券本金,剩余募集资金用于补充流动资金。[24鲲鹏04]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,太平洋证券股份有限公司,平安证券股份有限公司,五矿证券有限公司</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4330,12 +4330,12 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>深圳市鲲鹏股权投资管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4345,14 +4345,10 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2030-10-12</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-10-12</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4370,37 +4366,33 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP18" s="3"/>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-10-12</t>
         </is>
       </c>
       <c r="AV18" s="3" t="inlineStr">
@@ -4410,7 +4402,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4428,74 +4420,74 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26鲲鹏投资02</t>
+          <t>26淮安国投MTN006</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>525030.SZ</t>
+          <t>102683878.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>1+1</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>16.0</v>
+        <v>2.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>16.0</v>
+        <v>2.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.00</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>20.81</v>
+        <v>32.81</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>25鲲鹏02</t>
+          <t>26淮安国投MTN005</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>1.07Y</t>
+          <t>1.90Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.5373</t>
+          <t>1.6140</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.5500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>深圳市鲲鹏股权投资管理有限公司</t>
+          <t>淮安市国有联合投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.56</t>
+          <t>C 25.84</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4505,12 +4497,12 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
@@ -4519,17 +4511,19 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="V19" s="3"/>
+        <v>3.8</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>2.33</v>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>1.49%~1.59%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4540,23 +4534,23 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过16亿元(含16亿元),募集资金扣除发行费用后,拟使用不超过15亿元用于偿还到期的公司债券本金,剩余募集资金用于补充流动资金。[24鲲鹏04]</t>
+          <t>本期发行金额2亿元，募集资金拟全部用于偿还发行人到期债券[25淮安国投MTN002]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
+          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4566,12 +4560,12 @@
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>深圳市鲲鹏股权投资管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4587,76 +4581,82 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM19" s="3" t="inlineStr">
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY19" s="3" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO19" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP19" s="3"/>
-      <c r="AQ19" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR19" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AS19" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
-        <is>
-          <t>2027-10-12</t>
-        </is>
-      </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW19" s="3" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AX19" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY19" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AZ19" s="3"/>
+      <c r="AZ19" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN006</t>
+          <t>26广州地铁SCP014</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4666,49 +4666,49 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>102683878.IB</t>
+          <t>012682383.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.26 ~ 1.55</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>32.81</v>
+        <v>15.25</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN005</t>
+          <t>17广州地铁专项债01</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>1.90Y</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.6140</t>
+          <t>1.4941</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>广州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C 25.84</t>
+          <t>C+ 32.28</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -4747,19 +4747,17 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V20" s="4" t="n">
-        <v>2.33</v>
-      </c>
+        <v>3.79</v>
+      </c>
+      <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.59%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4770,23 +4768,23 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额2亿元，募集资金拟全部用于偿还发行人到期债券[25淮安国投MTN002]</t>
+          <t>本期超短期融资券金额20亿元，全部用于归还发行人的债务融资工具。[26广州地铁SCP001]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4801,7 +4799,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年度第六期中期票据</t>
+          <t>广州地铁集团有限公司2026年度第十四期超短期融资券</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4811,7 +4809,7 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
@@ -4832,12 +4830,12 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
@@ -4847,17 +4845,17 @@
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4885,14 +4883,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ20" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ20" s="3"/>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26绍兴高新MTN003</t>
+          <t>26宿迁新城MTN001</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4902,49 +4898,49 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>102683883.IB</t>
+          <t>102683877.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>8.2</v>
+        <v>6.88</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>8.2</v>
+        <v>6.88</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>41.11</v>
+        <v>36.81</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26绍兴高新MTN002</t>
+          <t>26宿迁新城CP001</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>159D</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.8213</t>
+          <t>1.5334</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4954,12 +4950,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
+          <t>宿迁市新城控股集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 20.62</t>
+          <t>C+ 34.88</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4969,12 +4965,12 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -4983,9 +4979,11 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="V21" s="3"/>
+        <v>4.6584</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>1.8</v>
+      </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
           <t>6+</t>
@@ -4993,7 +4991,7 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -5004,17 +5002,17 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额人民币8.20亿元,拟全部用于偿还发行人本级2026年到期的债务融资工具本金[23绍兴高新MTN002]</t>
+          <t>首期拟发行金额6.88亿元募集资金拟用于偿还发行人存量债务融资工具本金[25宿迁新城CP002]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,宁波银行股份有限公司</t>
+          <t>南京银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
@@ -5035,7 +5033,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>绍兴高新技术产业开发区投资发展集团有限公司2026年度第三期中期票据</t>
+          <t>宿迁市新城控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5045,14 +5043,10 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK21" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-10-12</t>
+        </is>
+      </c>
+      <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -5070,12 +5064,12 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
@@ -5085,12 +5079,12 @@
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
@@ -5123,12 +5117,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ21" s="3"/>
+      <c r="AZ21" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26广州地铁SCP014</t>
+          <t>26连云港SCP004</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5138,7 +5134,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>012682383.IB</t>
+          <t>012682382.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -5147,40 +5143,40 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.55</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>15.25</v>
+        <v>30.25</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>17广州地铁专项债01</t>
+          <t>26连云港SCP003</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>248D</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.4941</t>
+          <t>1.5426</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -5190,12 +5186,12 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司</t>
+          <t>连云港港口集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.28</t>
+          <t>C- 12.75</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5219,38 +5215,40 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="V22" s="3"/>
+        <v>3.475</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.59%~1.63%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-连云港市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券金额20亿元，全部用于归还发行人的债务融资工具。[26广州地铁SCP001]</t>
+          <t>本期超短期融资券发行金额4.00亿元,募集资金全部用于偿还发行人存量有息债务。</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
+          <t>南京银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
@@ -5271,7 +5269,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司2026年度第十四期超短期融资券</t>
+          <t>连云港港口集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5302,12 +5300,12 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
@@ -5317,17 +5315,17 @@
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5355,12 +5353,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ22" s="3"/>
+      <c r="AZ22" s="4" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城MTN001</t>
+          <t>26莆田国资MTN002</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5370,49 +5370,49 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>102683877.IB</t>
+          <t>102683876.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>6.88</v>
+        <v>10.0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6.88</v>
+        <v>10.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>36.81</v>
+        <v>40.84</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城CP001</t>
+          <t>26莆田国资MTN001</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>159D</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.5334</t>
+          <t>1.6718</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司</t>
+          <t>莆田市国有资产投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.88</t>
+          <t>C- 22.97</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -5451,19 +5451,17 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>4.6584</v>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>1.8</v>
-      </c>
+        <v>5.26</v>
+      </c>
+      <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5474,17 +5472,17 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>福建省-莆田市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>首期拟发行金额6.88亿元募集资金拟用于偿还发行人存量债务融资工具本金[25宿迁新城CP002]</t>
+          <t>发行人本期中期票据发行金额为10亿元,拟用于偿还发行人本部接续债务融资工具的专项贷款。[21莆田国资PPN003]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,交通银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5505,7 +5503,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司2026年度第一期中期票据</t>
+          <t>莆田市国有资产投资集团有限责任公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5515,7 +5513,7 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
@@ -5536,27 +5534,27 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
@@ -5589,14 +5587,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ23" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ23" s="3"/>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP004</t>
+          <t>26吴中经发MTN003</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5606,64 +5602,64 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>012682382.IB</t>
+          <t>102683881.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.0</v>
+        <v>5.7</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.0</v>
+        <v>5.7</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>30.25</v>
+        <v>26.11</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP003</t>
+          <t>26吴中经发MTN002</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>248D</t>
+          <t>2.85Y+2.00Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.5426</t>
+          <t>1.6622</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司</t>
+          <t>江苏省吴中经济技术发展集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C- 12.75</t>
+          <t>C- 16.95</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5687,19 +5683,17 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.475</v>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>5.4912</v>
+      </c>
+      <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.63%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -5710,23 +5704,23 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>江苏省-连云港市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4.00亿元,募集资金全部用于偿还发行人存量有息债务。</t>
+          <t>本期中期票据发行金额5.70亿元,募集资金用于偿还债券[26吴中经发SCP001,26吴中经发SCP002,26吴中经发SCP003]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,中国银行股份有限公司</t>
+          <t>苏州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5741,7 +5735,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司2026年度第四期超短期融资券</t>
+          <t>江苏省吴中经济技术发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5751,10 +5745,14 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
-        </is>
-      </c>
-      <c r="AK24" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK24" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -5772,12 +5770,12 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
@@ -5787,22 +5785,22 @@
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AV24" s="3" t="inlineStr">
@@ -5812,7 +5810,7 @@
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
@@ -5825,14 +5823,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ24" s="4" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="AZ24" s="3"/>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26莆田国资MTN002</t>
+          <t>26阜阳投资PPN002</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5842,7 +5838,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>102683876.IB</t>
+          <t>032680548.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5851,55 +5847,55 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>10.0</v>
+        <v>4.75</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10.0</v>
+        <v>4.75</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.40 ~ 2.10</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>40.84</v>
+        <v>41.84</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26莆田国资MTN001</t>
+          <t>26阜阳投资PPN001</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.6718</t>
+          <t>1.7226</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/1.7000</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>莆田市国有资产投资集团有限责任公司</t>
+          <t>阜阳投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 22.97</t>
+          <t>C- 22.00</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5909,12 +5905,12 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -5923,9 +5919,11 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="V25" s="3"/>
+        <v>4.8632</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>22.85</v>
+      </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -5933,7 +5931,7 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5944,23 +5942,23 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>福建省-莆田市</t>
+          <t>安徽省-阜阳市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为10亿元,拟用于偿还发行人本部接续债务融资工具的专项贷款。[21莆田国资PPN003]</t>
+          <t>本次定向债务融资工具注册规模12.15亿元，本期发行规模4.75亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
+          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -5975,12 +5973,12 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>莆田市国有资产投资集团有限责任公司2026年度第二期中期票据</t>
+          <t>阜阳投资发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
@@ -6006,12 +6004,12 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
@@ -6059,12 +6057,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ25" s="3"/>
+      <c r="AZ25" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26吴中经发MTN003</t>
+          <t>26涪陵国资MTN003</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6074,64 +6074,64 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>102683881.IB</t>
+          <t>102690061.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.7</v>
+        <v>7.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.7</v>
+        <v>10.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>26.11</v>
+        <v>61.36</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26吴中经发MTN002</t>
+          <t>26涪陵国资MTN002B</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2.85Y+2.00Y</t>
+          <t>6.86Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.6622</t>
+          <t>2.0881</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>江苏省吴中经济技术发展集团有限公司</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 16.95</t>
+          <t>C- 24.65</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -6155,17 +6155,17 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>5.4912</v>
+        <v>2.7</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>2.27%~2.37%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -6176,17 +6176,17 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额5.70亿元,募集资金用于偿还债券[26吴中经发SCP001,26吴中经发SCP002,26吴中经发SCP003]</t>
+          <t>本期债券基础发行规模为0亿元,发行金额上限为10亿元,募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN003]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>苏州银行股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>江苏省吴中经济技术发展集团有限公司2026年度第三期中期票据</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
+          <t>2036-10-12</t>
         </is>
       </c>
       <c r="AK26" s="3" t="inlineStr">
@@ -6242,37 +6242,37 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>食品加工</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AV26" s="3" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="AW26" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX26" s="3" t="inlineStr">
@@ -6300,7 +6300,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN002</t>
+          <t>26杭金投MTN004</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6310,64 +6310,64 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>032680548.IB</t>
+          <t>102683873.IB</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1.5Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.75</v>
+        <v>10.0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.75</v>
+        <v>10.0</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>41.84</v>
+        <v>17.85</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN001</t>
+          <t>26杭金投MTN001</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>1.69Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.7226</t>
+          <t>1.6154</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.7500/1.7000</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司</t>
+          <t>杭州市金融投资集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 22.00</t>
+          <t>C- 19.13</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6382,55 +6382,55 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.8632</v>
+        <v>3.3</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>22.85</v>
+        <v>1.54</v>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.53%~1.63%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>安徽省-阜阳市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具注册规模12.15亿元，本期发行规模4.75亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004]</t>
+          <t>本次中期票据募集资金10亿元，拟全部用于偿还发行人即将到期的债务融资工具【26 杭金投SCP001】</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
+          <t>浙商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6445,23 +6445,23 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>杭州市金融投资集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2028-04-10</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6471,37 +6471,37 @@
       </c>
       <c r="AN27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6529,81 +6529,79 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ27" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ27" s="3"/>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26杭金投MTN004</t>
+          <t>26蜀道K9</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>102683873.IB</t>
+          <t>525034.SZ</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>17.85</v>
+        <v>21.11</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26杭金投MTN001</t>
+          <t>24蜀道05</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>1.69Y</t>
+          <t>5.01Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.6154</t>
+          <t>1.7267</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>1.6400/--</t>
+          <t>--/1.7200</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>杭州市金融投资集团有限公司</t>
+          <t>蜀道投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C- 19.13</t>
+          <t>C+ 34.43</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6613,33 +6611,31 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>1.54</v>
-      </c>
+        <v>4.26</v>
+      </c>
+      <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.63%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6650,23 +6646,23 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据募集资金10亿元，拟全部用于偿还发行人即将到期的债务融资工具【26 杭金投SCP001】</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资以及符合国家法律法规要求的其他用途。</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,天府证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
@@ -6676,12 +6672,12 @@
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>杭州市金融投资集团有限公司2026年度第四期中期票据</t>
+          <t>蜀道投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第九期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6691,28 +6687,32 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2028-04-10</t>
-        </is>
-      </c>
-      <c r="AK28" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK28" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
@@ -6722,22 +6722,22 @@
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6770,7 +6770,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26蜀道K9</t>
+          <t>26中航K5</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6780,64 +6780,62 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>525034.SZ</t>
+          <t>525028.SZ</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>25.0</v>
-      </c>
+        <v>7.0</v>
+      </c>
+      <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
           <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>21.11</v>
+        <v>24.84</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>24蜀道05</t>
+          <t>26中航K3</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>5.01Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.7267</t>
+          <t>1.6223</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/1.7200</t>
+          <t>1.6500/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司</t>
+          <t>中航科创有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.43</t>
+          <t>C+ 31.30</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6847,7 +6845,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6857,21 +6855,19 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U29" s="4" t="n">
-        <v>4.26</v>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6879,20 +6875,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z29" s="3"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资以及符合国家法律法规要求的其他用途。</t>
+          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,天府证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司</t>
+          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第九期)</t>
+          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
+          <t>2029-10-13</t>
         </is>
       </c>
       <c r="AK29" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL29" s="3" t="inlineStr">
@@ -6938,42 +6938,42 @@
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>航空装备</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -7006,7 +7006,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26中航K5</t>
+          <t>26中航K6</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>525028.SZ</t>
+          <t>525029.SZ</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
@@ -7030,38 +7030,38 @@
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>24.84</v>
+        <v>26.11</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26中航K3</t>
+          <t>26中航K4</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.6223</t>
+          <t>1.7088</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>1.6500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
+          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7159,14 +7159,10 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-13</t>
+        </is>
+      </c>
+      <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7242,7 +7238,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26中航K6</t>
+          <t>26杭钢02</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7252,47 +7248,47 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>525029.SZ</t>
+          <t>246177.SH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>26.11</v>
+        <v>31.84</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26中航K4</t>
+          <t>26杭钢01</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>2.49Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7088</t>
+          <t>1.6419</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -7302,12 +7298,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司</t>
+          <t>杭州钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.30</t>
+          <t>C- 20.59</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7317,7 +7313,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7334,12 +7330,12 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7347,24 +7343,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z31" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,剩余部分募集资金拟用于补充公司流动资金。</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
@@ -7375,17 +7367,17 @@
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
+          <t>杭州钢铁集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7395,10 +7387,14 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
-        </is>
-      </c>
-      <c r="AK31" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK31" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7406,7 +7402,7 @@
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
@@ -7421,27 +7417,27 @@
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>航空装备</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7474,57 +7470,59 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26杭钢02</t>
+          <t>26常城建PPN002</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>246177.SH</t>
+          <t>032690031.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F32" s="3"/>
+        <v>6.64</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>6.64</v>
+      </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.55 ~ 2.05</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>31.84</v>
+        <v>32.11</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26杭钢01</t>
+          <t>26常城05</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.49Y</t>
+          <t>4.85Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.6419</t>
+          <t>1.8215</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7534,12 +7532,12 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司</t>
+          <t>常州市城市建设(集团)有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 20.59</t>
+          <t>C 27.12</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7549,29 +7547,33 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>4.2377</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>1.19</v>
+      </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7582,23 +7584,23 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,剩余部分募集资金拟用于补充公司流动资金。</t>
+          <t>发行人本期定向债务融资工具发行金额为6.64亿元,拟用于偿还发行人本部存量债务融资工具本金[21常城建MTN003,26常城建SCP001]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>南京银行股份有限公司,江苏银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
@@ -7608,79 +7610,75 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>常州市城市建设(集团)有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK32" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-10</t>
+        </is>
+      </c>
+      <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>燃气</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AO32" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ32" s="3" t="inlineStr">
-        <is>
-          <t>金属和非金属矿产</t>
-        </is>
-      </c>
-      <c r="AR32" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>普钢</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7701,12 +7699,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ32" s="3"/>
+      <c r="AZ32" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26常城建PPN002</t>
+          <t>26锡产业SCP015</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7716,64 +7716,64 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>032690031.IB</t>
+          <t>012682379.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.64</v>
+        <v>6.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.64</v>
+        <v>6.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.55 ~ 2.05</t>
+          <t>1.31 ~ 1.51</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>32.11</v>
+        <v>31.25</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26常城05</t>
+          <t>25锡产业MTN005</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>4.85Y</t>
+          <t>271D</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.8215</t>
+          <t>1.4940</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4800</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>常州市城市建设(集团)有限公司</t>
+          <t>无锡产业发展集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C 27.12</t>
+          <t>C- 18.79</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>4.2377</v>
+        <v>1.2333</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>1.19</v>
+        <v>1.82</v>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7820,23 +7820,23 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行金额为6.64亿元,拟用于偿还发行人本部存量债务融资工具本金[21常城建MTN003,26常城建SCP001]</t>
+          <t>本期超短期融资券发行金额6亿元用于归还发行人本部有息债务[26锡产业SCP006]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,江苏银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7851,17 +7851,17 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>常州市城市建设(集团)有限公司2026年度第二期定向债务融资工具</t>
+          <t>无锡产业发展集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-10-10</t>
+          <t>2027-07-07</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
@@ -7882,12 +7882,12 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
@@ -7897,17 +7897,17 @@
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7935,81 +7935,79 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ33" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ33" s="3"/>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26锡产业SCP015</t>
+          <t>26古厝13</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>012682379.IB</t>
+          <t>520514.SZ</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>31.25</v>
+        <v>34.81</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>25锡产业MTN005</t>
+          <t>24古厝01</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>271D</t>
+          <t>2.63Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.4940</t>
+          <t>1.6920</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/1.4800</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司</t>
+          <t>福州古厝集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 18.79</t>
+          <t>C- 21.71</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8019,7 +8017,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -8029,15 +8027,13 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>1.2333</v>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>1.82</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -8045,7 +8041,7 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -8056,23 +8052,23 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额6亿元用于归还发行人本部有息债务[26锡产业SCP006]</t>
+          <t>本期债券发行规模不超过5.00亿元（含），募集资金在扣除发行费用后，拟用于偿还发行人到期的公司债券本金。[25古厝D6]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>兴业证券股份有限公司,中国国际金融股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -8082,68 +8078,56 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司2026年度第十五期超短期融资券</t>
+          <t>福州古厝集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2027-07-07</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AQ34" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR34" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3"/>
+      <c r="AR34" s="3"/>
+      <c r="AS34" s="3"/>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8176,22 +8160,22 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26古厝13</t>
+          <t>26海发宝诚SCP007</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>520514.SZ</t>
+          <t>012682380.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.26Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
@@ -8202,48 +8186,48 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.35 ~ 1.49</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>34.81</v>
+        <v>30.32</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>24古厝01</t>
+          <t>25海租01</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>2.63Y</t>
+          <t>93D</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.6920</t>
+          <t>1.4631</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司</t>
+          <t>海发宝诚融资租赁有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 21.71</t>
+          <t>C- 14.76</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8253,7 +8237,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8267,17 +8251,19 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V35" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8288,89 +8274,101 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过5.00亿元（含），募集资金在扣除发行费用后，拟用于偿还发行人到期的公司债券本金。[25古厝D6]</t>
+          <t>本期超短期融资券基础发行金额0亿元，发行金额上限5亿元，拟全部用于偿还发行人即将到期的债务融资工具[26海发宝诚SCP006]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,中国国际金融股份有限公司,天风证券股份有限公司</t>
+          <t>平安银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>海发宝诚融资租赁有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO35" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ35" s="3"/>
-      <c r="AR35" s="3"/>
-      <c r="AS35" s="3"/>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV35" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8391,12 +8389,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ35" s="3"/>
+      <c r="AZ35" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26海发宝诚SCP007</t>
+          <t>26广州地铁SCP015</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8406,49 +8406,49 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>012682380.IB</t>
+          <t>012682381.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>0.26Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>5.0</v>
+        <v>14.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>5.0</v>
+        <v>14.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.49</t>
+          <t>1.26 ~ 1.55</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>30.32</v>
+        <v>15.25</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>25海租01</t>
+          <t>17广州地铁专项债01</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>93D</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.4631</t>
+          <t>1.4941</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>海发宝诚融资租赁有限公司</t>
+          <t>广州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 14.76</t>
+          <t>C+ 32.28</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8487,19 +8487,17 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>3.8857</v>
+      </c>
+      <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8510,17 +8508,17 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额0亿元，发行金额上限5亿元，拟全部用于偿还发行人即将到期的债务融资工具[26海发宝诚SCP006]</t>
+          <t>本期超短期融资券金额14亿元，其中5亿元用于归还发行人存量债券，9亿元用于归还发行人金融机构借款。[26广州地铁SCP001]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,上海银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
@@ -8531,7 +8529,7 @@
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
@@ -8541,7 +8539,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>海发宝诚融资租赁有限公司2026年度第七期超短期融资券</t>
+          <t>广州地铁集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8551,7 +8549,7 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
@@ -8572,32 +8570,32 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8625,66 +8623,64 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ36" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ36" s="3"/>
     </row>
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26广州地铁SCP015</t>
+          <t>26天长01</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>012682381.IB</t>
+          <t>284203.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.55</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>15.25</v>
+        <v>46.84</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>17广州地铁专项债01</t>
+          <t>25滁高01</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>1.64Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.4941</t>
+          <t>1.6256</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -8694,12 +8690,12 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司</t>
+          <t>天长市科技工业发展有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.28</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8709,7 +8705,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8723,44 +8719,52 @@
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>3.89</v>
+        <v>4.2</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>安徽省-滁州市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券金额14亿元，其中5亿元用于归还发行人存量债券，9亿元用于归还发行人金融机构借款。[26广州地铁SCP001]</t>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还“23天长02”公司债券本金。[23天长02]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD37" s="3"/>
+          <t>五矿证券有限公司,川财证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr">
+        <is>
+          <t>安徽省信用融资担保集团有限公司</t>
+        </is>
+      </c>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8770,28 +8774,28 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司2026年度第十五期超短期融资券</t>
+          <t>天长市科技工业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t/>
         </is>
       </c>
       <c r="AM37" s="3" t="inlineStr">
@@ -8806,12 +8810,12 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
@@ -8821,17 +8825,17 @@
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8841,7 +8845,7 @@
       </c>
       <c r="AV37" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW37" s="3" t="inlineStr">
@@ -8864,7 +8868,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26天长01</t>
+          <t>26凯建01</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8874,49 +8878,49 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>284203.SH</t>
+          <t>284219.SH</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>2.40 ~ 3.40</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.75</v>
+        <v>2.65</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>46.84</v>
+        <v>124.11</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>25滁高01</t>
+          <t>25凯建01</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>1.64Y</t>
+          <t>4.15Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.6256</t>
+          <t>2.8084</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -8926,12 +8930,12 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>天长市科技工业发展有限公司</t>
+          <t>凯里正源城镇建设发展有限责任公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B- 42.31</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8955,17 +8959,17 @@
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>4.2</v>
+        <v>2.66</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>8-</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>2.79%~2.89%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -8973,29 +8977,25 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="Z38" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>安徽省-滁州市</t>
+          <t>贵州省-黔东南苗族侗族自治州</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,全部用于偿还“23天长02”公司债券本金。[23天长02]</t>
+          <t>本期债券募集资金扣除承销费用后，拟全部用于统借统还偿还到期公司债券本金</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司,川财证券有限责任公司</t>
+          <t>第一创业证券承销保荐有限责任公司</t>
         </is>
       </c>
       <c r="AD38" s="3" t="inlineStr">
         <is>
-          <t>安徽省信用融资担保集团有限公司</t>
+          <t>贵州省信用增进有限公司</t>
         </is>
       </c>
       <c r="AE38" s="3" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>天长市科技工业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>凯里正源城镇建设发展有限责任公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -9025,10 +9025,14 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK38" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK38" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9051,7 +9055,7 @@
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
@@ -9061,17 +9065,17 @@
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9104,74 +9108,74 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26凯建01</t>
+          <t>26兴化城投PPN009</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>284219.SH</t>
+          <t>032680552.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2.40 ~ 3.40</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>124.11</v>
+        <v>39.81</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>25凯建01</t>
+          <t>26兴化城投PPN008</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>4.15Y</t>
+          <t>1.88Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>2.8084</t>
+          <t>1.6847</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>凯里正源城镇建设发展有限责任公司</t>
+          <t>兴化市城市建设投资有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>B- 42.31</t>
+          <t>C- 17.15</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9181,7 +9185,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -9191,21 +9195,23 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V39" s="3"/>
+        <v>3.6</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>1.26</v>
+      </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>8-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>2.79%~2.89%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9216,27 +9222,23 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>贵州省-黔东南苗族侗族自治州</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除承销费用后，拟全部用于统借统还偿还到期公司债券本金</t>
+          <t>本期定向债务融资工具发行金额4亿元,拟用于偿还发行人有息债务[26兴化城投PPN002]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>第一创业证券承销保荐有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD39" s="3" t="inlineStr">
-        <is>
-          <t>贵州省信用增进有限公司</t>
-        </is>
-      </c>
+          <t>江苏江南农村商业银行股份有限公司,苏州银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9246,12 +9248,12 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>凯里正源城镇建设发展有限责任公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>兴化市城市建设投资有限公司2026年度第九期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9261,67 +9263,63 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK39" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-10-10</t>
+        </is>
+      </c>
+      <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>农产品加工</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO39" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="AQ39" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR39" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS39" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV39" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW39" s="3" t="inlineStr">
@@ -9344,7 +9342,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26兴化城投PPN009</t>
+          <t>26绍兴高新MTN003</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9354,64 +9352,64 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>032680552.IB</t>
+          <t>102683883.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>4.0</v>
+        <v>8.2</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>4.0</v>
+        <v>8.2</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>39.81</v>
+        <v>41.11</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26兴化城投PPN008</t>
+          <t>26绍兴高新MTN002</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>1.88Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.6847</t>
+          <t>1.8213</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>1.7100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>兴化市城市建设投资有限公司</t>
+          <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 17.15</t>
+          <t>C- 20.62</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9421,60 +9419,58 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>1.26</v>
-      </c>
+        <v>5.0366</v>
+      </c>
+      <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额4亿元,拟用于偿还发行人有息债务[26兴化城投PPN002]</t>
+          <t>发行人本期中期票据发行金额人民币8.20亿元,拟全部用于偿还发行人本级2026年到期的债务融资工具本金[23绍兴高新MTN002]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>江苏江南农村商业银行股份有限公司,苏州银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9489,38 +9485,42 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>兴化市城市建设投资有限公司2026年度第九期定向债务融资工具</t>
+          <t>绍兴高新技术产业开发区投资发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2028-10-10</t>
-        </is>
-      </c>
-      <c r="AK40" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK40" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL40" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM40" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
@@ -9530,22 +9530,22 @@
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>农产品加工</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-10-09.xlsx
+++ b/data/credit_bond_all_2026-10-09.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-13" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-14" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,9 @@
       <c r="E3" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1.40 ~ 2.40</t>
@@ -757,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.87</t>
+          <t>C+ 31.82</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -780,7 +782,9 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="U3" s="3"/>
+      <c r="U3" s="4" t="n">
+        <v>2.01</v>
+      </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
@@ -924,7 +928,7 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26安市淮阴MTN001</t>
+          <t>26镇江产投MTN008</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -934,7 +938,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>102683884.IB</t>
+          <t>102683874.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -943,55 +947,55 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>46.84</v>
+        <v>30.84</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>25安市淮阴MTN003</t>
+          <t>26镇江产投MTN007</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>1.52Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.6621</t>
+          <t>1.6876</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6900/1.6600</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>淮安市淮阴区城市资产经营有限公司</t>
+          <t>镇江产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 15.83</t>
+          <t>C- 13.67</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1006,49 +1010,49 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>1.46</v>
+        <v>3.5667</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>4.67</v>
+        <v>1.0</v>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本次发行金额5亿元,募集资金拟全部用于偿还发行人本部及下属子公司有息债务[26安市淮阴CP001]</t>
+          <t>发行人本次发行的3.00亿元中期票据全部用于偿还发行人存量有息债务[25镇江产投CP004]</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>中国民生银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
@@ -1069,7 +1073,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>淮安市淮阴区城市资产经营有限公司2026年度第一期中期票据</t>
+          <t>镇江产业投资控股集团有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1079,13 +1083,13 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2029-10-10</t>
         </is>
       </c>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
@@ -1095,17 +1099,17 @@
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
@@ -1115,17 +1119,17 @@
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
@@ -1154,23 +1158,23 @@
         </is>
       </c>
       <c r="AZ4" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26镇江产投MTN008</t>
+          <t>26苏金04</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>102683874.IB</t>
+          <t>284122.SH</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1179,55 +1183,55 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3.0</v>
+        <v>3.6</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3.0</v>
+        <v>3.6</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>30.84</v>
+        <v>46.84</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>26镇江产投MTN007</t>
+          <t>26苏金03</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.6876</t>
+          <t>1.7214</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>1.6900/1.6600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>镇江产业投资控股集团有限公司</t>
+          <t>苏州金合盛控股有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 13.22</t>
+          <t>C- 17.07</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1237,60 +1241,62 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U5" s="4" t="n">
-        <v>3.5667</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>4.34</v>
+      </c>
+      <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行的3.00亿元中期票据全部用于偿还发行人存量有息债务[25镇江产投CP004]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金。[23苏金04]</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,南京银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD5" s="3"/>
+          <t>东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>苏州苏高新集团有限公司</t>
+        </is>
+      </c>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr">
@@ -1300,70 +1306,74 @@
       </c>
       <c r="AG5" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>镇江产业投资控股集团有限公司2026年度第八期中期票据</t>
+          <t>苏州金合盛控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2029-10-10</t>
-        </is>
-      </c>
-      <c r="AK5" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ5" s="3" t="inlineStr">
         <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR5" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
       <c r="AU5" s="3" t="inlineStr">
         <is>
           <t/>
@@ -1371,7 +1381,7 @@
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW5" s="3" t="inlineStr">
@@ -1389,14 +1399,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ5" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ5" s="3"/>
     </row>
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26苏金04</t>
+          <t>26通新01</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1406,47 +1414,49 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>284122.SH</t>
+          <t>284151.SH</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>46.84</v>
+        <v>41.11</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>26苏金03</t>
+          <t>24通新03</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>3.05Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.7214</t>
+          <t>1.7098</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1456,12 +1466,12 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>苏州金合盛控股有限公司</t>
+          <t>南通高新控股集团有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C- 19.19</t>
+          <t>C- 14.35</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1484,32 +1494,34 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="U6" s="3"/>
+      <c r="U6" s="4" t="n">
+        <v>5.51</v>
+      </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金。[23苏金04]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换偿还到期公司债券本金的自有资金[21通新01]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
@@ -1517,11 +1529,7 @@
           <t>东吴证券股份有限公司</t>
         </is>
       </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>苏州苏高新集团有限公司</t>
-        </is>
-      </c>
+      <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -1539,7 +1547,7 @@
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>苏州金合盛控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>南通高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
@@ -1549,14 +1557,10 @@
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK6" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-13</t>
+        </is>
+      </c>
+      <c r="AK6" s="3"/>
       <c r="AL6" s="3" t="inlineStr">
         <is>
           <t/>
@@ -1564,7 +1568,7 @@
       </c>
       <c r="AM6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN6" s="3" t="inlineStr">
@@ -1574,32 +1578,32 @@
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1609,7 +1613,7 @@
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW6" s="3" t="inlineStr">
@@ -1632,7 +1636,7 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26通新01</t>
+          <t>26榕水02</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1642,7 +1646,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>284151.SH</t>
+          <t>525031.SZ</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1651,53 +1655,55 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>7.0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>7.0</v>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>41.11</v>
+        <v>33.11</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>24通新03</t>
+          <t>24榕水04</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>3.05Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.7098</t>
+          <t>1.7324</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>南通高新控股集团有限公司</t>
+          <t>福州水务集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C- 18.24</t>
+          <t>D+ 7.27</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1707,7 +1713,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -1720,37 +1726,39 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="U7" s="3"/>
+      <c r="U7" s="4" t="n">
+        <v>4.86</v>
+      </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换偿还到期公司债券本金的自有资金[21通新01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务。[23榕水01]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>中信证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
@@ -1766,17 +1774,17 @@
       </c>
       <c r="AG7" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>南通高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>福州水务集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="inlineStr">
@@ -1802,32 +1810,32 @@
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1860,7 +1868,7 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26榕水02</t>
+          <t>26左海02</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1870,62 +1878,64 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>525031.SZ</t>
+          <t>284143.SH</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>33.11</v>
+        <v>28.11</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>24榕水04</t>
+          <t>25左海01</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>3.26Y+5.00Y</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.7324</t>
+          <t>1.7199</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/1.7600</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>福州水务集团有限公司</t>
+          <t>福州左海控股集团有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.33</t>
+          <t>C 27.65</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1945,21 +1955,21 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U8" s="4" t="n">
-        <v>4.86</v>
+        <v>4.56</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1975,12 +1985,12 @@
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务。[23榕水01]</t>
+          <t>本期公司债券拟发行5亿元，募集资金扣除发行费用后，拟全部用于偿还公司债券本金【23左海03 】</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华福证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
@@ -1996,25 +2006,29 @@
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>福州水务集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>福州左海控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
-        </is>
-      </c>
-      <c r="AK8" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK8" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL8" s="3" t="inlineStr">
         <is>
           <t/>
@@ -2022,12 +2036,12 @@
       </c>
       <c r="AM8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO8" s="3" t="inlineStr">
@@ -2037,32 +2051,32 @@
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AV8" s="3" t="inlineStr">
@@ -2072,7 +2086,7 @@
       </c>
       <c r="AW8" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX8" s="3" t="inlineStr">
@@ -2090,74 +2104,74 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26左海02</t>
+          <t>26创星PPN002(科创债)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>284143.SH</t>
+          <t>032680550.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>2.20 ~ 2.60</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.69</v>
+        <v>2.55</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>28.11</v>
+        <v>126.84</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>25左海01</t>
+          <t>25创星PPN001(科创债)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>3.26Y+5.00Y</t>
+          <t>3.69Y+5.00Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.7199</t>
+          <t>1.7809</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>福州左海控股集团有限公司</t>
+          <t>中科创星科技投资有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C 27.65</t>
+          <t>D+ 9.13</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2167,7 +2181,7 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
@@ -2177,63 +2191,65 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="V9" s="3"/>
+        <v>1.5</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>2.45%~2.55%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券拟发行5亿元，募集资金扣除发行费用后，拟全部用于偿还公司债券本金【23左海03 】</t>
+          <t>本次定向债务融资工具发行拟募集资金1亿元,所募集资金拟用于置换前期出资、新增基金出资以及补充流动资金</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,华福证券股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>福州左海控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>中科创星科技投资有限公司2026年度第二期定向科技创新债券</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2243,64 +2259,56 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK9" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-10</t>
+        </is>
+      </c>
+      <c r="AK9" s="3"/>
       <c r="AL9" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP9" s="3"/>
+      <c r="AQ9" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO9" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ9" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR9" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>高速公路</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2308,7 +2316,7 @@
       </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX9" s="3" t="inlineStr">
@@ -2321,77 +2329,81 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ9" s="3"/>
+      <c r="AZ9" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26唐租01</t>
+          <t>26广州产投SCP008</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>246158.SH</t>
+          <t>012682378.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F10" s="3"/>
+        <v>10.5</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>10.5</v>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>39.84</v>
+        <v>24.25</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>25大唐租赁MTN002B(绿色)</t>
+          <t>26广州产投SCP007</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>1.63Y</t>
+          <t>259D</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.6333</t>
+          <t>1.4923</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/1.4900</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司</t>
+          <t>广州产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.38</t>
+          <t>C- 23.54</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2401,7 +2413,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -2411,19 +2423,23 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>1.3143</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>1.06</v>
+      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2434,38 +2450,38 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金10.00亿元拟用于偿还发行人到期公司债券本金[24唐租04]</t>
+          <t>本期超短期融资券的发行规模为10.5亿元，募集资金全部用于偿还到期债务融资工具[26 广州产投SCP002 ]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,招商证券股份有限公司</t>
+          <t>平安银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>广州产业投资控股集团有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2475,17 +2491,13 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK10" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-07-07</t>
+        </is>
+      </c>
+      <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM10" s="3" t="inlineStr">
@@ -2495,37 +2507,37 @@
       </c>
       <c r="AN10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2558,7 +2570,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26创星PPN002(科创债)</t>
+          <t>26鲁高速SCP004</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2568,64 +2580,64 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>032680550.IB</t>
+          <t>012682377.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.66Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.0</v>
+        <v>20.0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.0</v>
+        <v>30.0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.60</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.55</v>
+        <v>1.37</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>126.84</v>
+        <v>17.25</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>25创星PPN001(科创债)</t>
+          <t>24鲁高K3</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>3.69Y+5.00Y</t>
+          <t>290D</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.7809</t>
+          <t>1.4600</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/1.7600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>中科创星科技投资有限公司</t>
+          <t>山东高速集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.13</t>
+          <t>B- 43.92</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2635,12 +2647,12 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 10:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2649,51 +2661,51 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.5</v>
+        <v>1.5667</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>2.45%~2.55%</t>
+          <t>1.43%~1.47%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具发行拟募集资金1亿元,所募集资金拟用于置换前期出资、新增基金出资以及补充流动资金</t>
+          <t>本期超短期融资券基础发行金额20亿元，发行金额上限30亿元，募集资金用于偿还发行人本部及子公司有息负债及补充流动资金</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司</t>
+          <t>广发银行股份有限公司,北京银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
@@ -2703,17 +2715,17 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>中科创星科技投资有限公司2026年度第二期定向科技创新债券</t>
+          <t>山东高速集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2029-10-10</t>
+          <t>2027-06-07</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
@@ -2724,7 +2736,7 @@
       </c>
       <c r="AM11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN11" s="3" t="inlineStr">
@@ -2734,28 +2746,32 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP11" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2783,14 +2799,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ11" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ11" s="3"/>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP008</t>
+          <t>26南京公路MTN003</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2800,64 +2814,64 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>012682378.IB</t>
+          <t>102683875.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>10.5</v>
+        <v>2.0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10.5</v>
+        <v>2.0</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>24.25</v>
+        <v>24.11</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP007</t>
+          <t>25南京公路MTN001</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>259D</t>
+          <t>3.83Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.4923</t>
+          <t>1.6928</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1.5000/1.4900</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司</t>
+          <t>南京公路发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 23.54</t>
+          <t>C- 11.53</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2872,7 +2886,7 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
@@ -2881,19 +2895,19 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.3143</v>
+        <v>2.5</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.06</v>
+        <v>1.0</v>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2904,23 +2918,27 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券的发行规模为10.5亿元，募集资金全部用于偿还到期债务融资工具[26 广州产投SCP002 ]</t>
+          <t>本期中期票据发行金额2亿元,募集资金用于偿还发行人本级及下属子公司有息债务</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,中信银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3"/>
+          <t>南京银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+        </is>
+      </c>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2935,7 +2953,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司2026年度第八期超短期融资券</t>
+          <t>南京公路发展(集团)有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2945,7 +2963,7 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2027-07-07</t>
+          <t>2031-10-10</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
@@ -2966,32 +2984,32 @@
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -3001,7 +3019,7 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
@@ -3019,12 +3037,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ12" s="3"/>
+      <c r="AZ12" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26鲁高速SCP004</t>
+          <t>26涪陵国资MTN003A(取消发行)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3034,49 +3054,43 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>012682377.IB</t>
+          <t>DY102690060.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>0.66Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>30.0</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>17.25</v>
-      </c>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>24鲁高K3</t>
+          <t>26涪陵国资MTN002B</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>290D</t>
+          <t>6.86Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.4600</t>
+          <t>2.0881</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3086,12 +3100,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B- 43.18</t>
+          <t>C- 24.33</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3101,60 +3115,56 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>10-09 10:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>1.5667</v>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>9.0</v>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.43%~1.47%</t>
+          <t>2.21%~2.31%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额20亿元，发行金额上限30亿元，募集资金用于偿还发行人本部及子公司有息负债及补充流动资金</t>
+          <t>本期债券基础发行规模为0亿元,发行金额上限为10亿元,募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN003]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司,北京银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3169,7 +3179,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司2026年度第四期超短期融资券</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3179,25 +3189,25 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2027-06-07</t>
+          <t>2033-10-12</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>类城投</t>
@@ -3205,27 +3215,27 @@
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>食品加工</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3258,74 +3268,74 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26南京公路MTN003</t>
+          <t>26云能04</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>102683875.IB</t>
+          <t>246167.SH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>24.11</v>
+        <v>48.22</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>25南京公路MTN001</t>
+          <t>25云能投MTN003</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>3.83Y</t>
+          <t>3.89Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.6928</t>
+          <t>1.8363</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.7100/--</t>
+          <t>1.8600/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司</t>
+          <t>云南省能源集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 11.53</t>
+          <t>C- 23.77</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3335,64 +3345,58 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>3.19</v>
+      </c>
+      <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额2亿元,募集资金用于偿还发行人本级及下属子公司有息债务</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,太平洋证券股份有限公司,平安证券股份有限公司,五矿证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3402,12 +3406,12 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司2026年度第三期中期票据</t>
+          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3417,53 +3421,57 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-10-10</t>
-        </is>
-      </c>
-      <c r="AK14" s="3"/>
+          <t>2030-10-12</t>
+        </is>
+      </c>
+      <c r="AK14" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL14" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3473,7 +3481,7 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW14" s="3" t="inlineStr">
@@ -3491,81 +3499,79 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ14" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ14" s="3"/>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26皖投集MTN006</t>
+          <t>26鲲鹏投资02</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102683882.IB</t>
+          <t>525030.SZ</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1+1</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.20 ~ 2.00</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>22.84</v>
+        <v>20.81</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>24皖投03</t>
+          <t>25鲲鹏02</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>1.07Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.6119</t>
+          <t>1.5373</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/1.5900</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司</t>
+          <t>深圳市鲲鹏股权投资管理有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 16.85</t>
+          <t>C+ 34.97</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3575,12 +3581,12 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -3589,19 +3595,17 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="V15" s="4" t="n">
-        <v>3.08</v>
-      </c>
+        <v>3.06</v>
+      </c>
+      <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3612,23 +3616,23 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金5亿元人民币，全部用于偿还发行人即将到期的债券[25皖投集CP003]</t>
+          <t>本期债券发行规模为不超过16亿元(含16亿元),募集资金扣除发行费用后,拟使用不超过15亿元用于偿还到期的公司债券本金,剩余募集资金用于补充流动资金。[24鲲鹏04]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,国家开发银行</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3638,12 +3642,12 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司2026年度第六期中期票据</t>
+          <t>深圳市鲲鹏股权投资管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3653,18 +3657,18 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t/>
         </is>
       </c>
       <c r="AM15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN15" s="3" t="inlineStr">
@@ -3674,37 +3678,33 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP15" s="3"/>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-10-12</t>
         </is>
       </c>
       <c r="AV15" s="3" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN003A(取消发行)</t>
+          <t>26淮安国投MTN006</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3742,43 +3742,49 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>DY102690060.IB</t>
+          <t>102683878.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F16" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+          <t>1.30 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>32.81</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN002B</t>
+          <t>26淮安国投MTN005</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>6.86Y</t>
+          <t>1.90Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>2.0881</t>
+          <t>1.6140</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3788,12 +3794,12 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
+          <t>淮安市国有联合投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 24.65</t>
+          <t>C 26.00</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3803,12 +3809,12 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -3816,8 +3822,12 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
+      <c r="U16" s="4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>2.33</v>
+      </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -3825,28 +3835,28 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>2.21%~2.31%</t>
+          <t>1.49%~1.59%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债券基础发行规模为0亿元,发行金额上限为10亿元,募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN003]</t>
+          <t>本期发行金额2亿元，募集资金拟全部用于偿还发行人到期债券[25淮安国投MTN002]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
@@ -3867,7 +3877,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据(品种一)(取消发行)</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3877,7 +3887,7 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2033-10-12</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
@@ -3898,32 +3908,32 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>食品加工</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3951,79 +3961,81 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26云能04</t>
+          <t>26广州地铁SCP014</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>246167.SH</t>
+          <t>012682383.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.26 ~ 1.55</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.82</v>
+        <v>1.35</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>48.22</v>
+        <v>15.25</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>25云能投MTN003</t>
+          <t>17广州地铁专项债01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>3.89Y</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.8363</t>
+          <t>1.4941</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.8600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司</t>
+          <t>广州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 23.68</t>
+          <t>C+ 32.05</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4033,7 +4045,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -4047,17 +4059,17 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>3.19</v>
+        <v>3.79</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4068,23 +4080,23 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还有息债务</t>
+          <t>本期超短期融资券金额20亿元，全部用于归还发行人的债务融资工具。[26广州地铁SCP001]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,太平洋证券股份有限公司,平安证券股份有限公司,五矿证券有限公司</t>
+          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4094,12 +4106,12 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>广州地铁集团有限公司2026年度第十四期超短期融资券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4109,22 +4121,18 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2030-10-12</t>
-        </is>
-      </c>
-      <c r="AK17" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-07-09</t>
+        </is>
+      </c>
+      <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4134,32 +4142,32 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4192,74 +4200,74 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26鲲鹏投资02</t>
+          <t>26宿迁新城MTN001</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>525030.SZ</t>
+          <t>102683877.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>1+1</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>16.0</v>
+        <v>6.88</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>16.0</v>
+        <v>6.88</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.00</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>20.81</v>
+        <v>36.81</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>25鲲鹏02</t>
+          <t>26宿迁新城CP001</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>1.07Y</t>
+          <t>159D</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.5373</t>
+          <t>1.5334</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1.5500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>深圳市鲲鹏股权投资管理有限公司</t>
+          <t>宿迁市新城控股集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.56</t>
+          <t>B- 39.08</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4269,12 +4277,12 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -4283,44 +4291,46 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="V18" s="3"/>
+        <v>4.6584</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>1.8</v>
+      </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过16亿元(含16亿元),募集资金扣除发行费用后,拟使用不超过15亿元用于偿还到期的公司债券本金,剩余募集资金用于补充流动资金。[24鲲鹏04]</t>
+          <t>首期拟发行金额6.88亿元募集资金拟用于偿还发行人存量债务融资工具本金[25宿迁新城CP002]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
+          <t>南京银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4330,12 +4340,12 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>深圳市鲲鹏股权投资管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>宿迁市新城控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4351,76 +4361,82 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM18" s="3" t="inlineStr">
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY18" s="3" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO18" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP18" s="3"/>
-      <c r="AQ18" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR18" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t>2027-10-12</t>
-        </is>
-      </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW18" s="3" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AX18" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AZ18" s="3"/>
+      <c r="AZ18" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN006</t>
+          <t>26连云港SCP004</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4430,49 +4446,49 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683878.IB</t>
+          <t>012682382.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>32.81</v>
+        <v>30.25</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN005</t>
+          <t>26连云港SCP003</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>1.90Y</t>
+          <t>248D</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.6140</t>
+          <t>1.5426</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4482,12 +4498,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>连云港港口集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C 25.84</t>
+          <t>C- 13.51</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4502,7 +4518,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
@@ -4511,10 +4527,10 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>3.8</v>
+        <v>3.475</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.33</v>
+        <v>1.0</v>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
@@ -4523,34 +4539,34 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.59%</t>
+          <t>1.59%~1.63%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>江苏省-连云港市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额2亿元，募集资金拟全部用于偿还发行人到期债券[25淮安国投MTN002]</t>
+          <t>本期超短期融资券发行金额4.00亿元,募集资金全部用于偿还发行人存量有息债务。</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
+          <t>南京银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4565,7 +4581,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年度第六期中期票据</t>
+          <t>连云港港口集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4575,7 +4591,7 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK19" s="3"/>
@@ -4596,7 +4612,7 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
@@ -4611,17 +4627,17 @@
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4650,13 +4666,13 @@
         </is>
       </c>
       <c r="AZ19" s="4" t="n">
-        <v>0.0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26广州地铁SCP014</t>
+          <t>26莆田国资MTN002</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4666,49 +4682,49 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>012682383.IB</t>
+          <t>102683876.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.55</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>15.25</v>
+        <v>40.84</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>17广州地铁专项债01</t>
+          <t>26莆田国资MTN001</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.4941</t>
+          <t>1.6718</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4718,12 +4734,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司</t>
+          <t>莆田市国有资产投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.28</t>
+          <t>C 28.26</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4733,12 +4749,12 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -4747,44 +4763,44 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>3.79</v>
+        <v>5.26</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>福建省-莆田市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券金额20亿元，全部用于归还发行人的债务融资工具。[26广州地铁SCP001]</t>
+          <t>发行人本期中期票据发行金额为10亿元,拟用于偿还发行人本部接续债务融资工具的专项贷款。[21莆田国资PPN003]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4799,7 +4815,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司2026年度第十四期超短期融资券</t>
+          <t>莆田市国有资产投资集团有限责任公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4809,7 +4825,7 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
@@ -4835,27 +4851,27 @@
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4888,7 +4904,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城MTN001</t>
+          <t>26吴中经发MTN003</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4898,64 +4914,64 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>102683877.IB</t>
+          <t>102683881.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>6.88</v>
+        <v>5.7</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6.88</v>
+        <v>5.7</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>36.81</v>
+        <v>26.11</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城CP001</t>
+          <t>26吴中经发MTN002</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>159D</t>
+          <t>2.85Y+2.00Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.5334</t>
+          <t>1.6622</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司</t>
+          <t>江苏省吴中经济技术发展集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.88</t>
+          <t>C- 19.51</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4970,7 +4986,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -4979,19 +4995,17 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>4.6584</v>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>1.8</v>
-      </c>
+        <v>5.4912</v>
+      </c>
+      <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -5002,17 +5016,17 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>首期拟发行金额6.88亿元募集资金拟用于偿还发行人存量债务融资工具本金[25宿迁新城CP002]</t>
+          <t>本期中期票据发行金额5.70亿元,募集资金用于偿还债券[26吴中经发SCP001,26吴中经发SCP002,26吴中经发SCP003]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,交通银行股份有限公司</t>
+          <t>苏州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
@@ -5033,7 +5047,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司2026年度第一期中期票据</t>
+          <t>江苏省吴中经济技术发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5043,10 +5057,14 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
-        </is>
-      </c>
-      <c r="AK21" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK21" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL21" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -5069,7 +5087,7 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
@@ -5079,22 +5097,22 @@
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AV21" s="3" t="inlineStr">
@@ -5104,7 +5122,7 @@
       </c>
       <c r="AW21" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX21" s="3" t="inlineStr">
@@ -5117,14 +5135,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ21" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ21" s="3"/>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP004</t>
+          <t>26阜阳投资PPN002</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5134,64 +5150,64 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>012682382.IB</t>
+          <t>032680548.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.0</v>
+        <v>4.75</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4.0</v>
+        <v>4.75</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.40 ~ 2.10</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>30.25</v>
+        <v>41.84</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP003</t>
+          <t>26阜阳投资PPN001</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>248D</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.5426</t>
+          <t>1.7226</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/1.7000</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司</t>
+          <t>阜阳投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C- 12.75</t>
+          <t>C- 24.91</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5206,7 +5222,7 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
@@ -5215,19 +5231,19 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>3.475</v>
+        <v>4.8632</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.0</v>
+        <v>22.85</v>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.63%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5238,23 +5254,23 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>江苏省-连云港市</t>
+          <t>安徽省-阜阳市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4.00亿元,募集资金全部用于偿还发行人存量有息债务。</t>
+          <t>本次定向债务融资工具注册规模12.15亿元，本期发行规模4.75亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,中国银行股份有限公司</t>
+          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -5269,17 +5285,17 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司2026年度第四期超短期融资券</t>
+          <t>阜阳投资发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
@@ -5300,32 +5316,32 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5354,13 +5370,13 @@
         </is>
       </c>
       <c r="AZ22" s="4" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26莆田国资MTN002</t>
+          <t>26涪陵国资MTN003</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5370,49 +5386,49 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>102683876.IB</t>
+          <t>102690061.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>10.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>40.84</v>
+        <v>61.36</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26莆田国资MTN001</t>
+          <t>26涪陵国资MTN002B</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>6.86Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.6718</t>
+          <t>2.0881</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -5422,12 +5438,12 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>莆田市国有资产投资集团有限责任公司</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 22.97</t>
+          <t>C- 24.33</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5437,12 +5453,12 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -5451,17 +5467,17 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>5.26</v>
+        <v>2.7</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>2.27%~2.37%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5472,17 +5488,17 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>福建省-莆田市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为10亿元,拟用于偿还发行人本部接续债务融资工具的专项贷款。[21莆田国资PPN003]</t>
+          <t>本期债券基础发行规模为0亿元,发行金额上限为10亿元,募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN003]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5503,7 +5519,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>莆田市国有资产投资集团有限责任公司2026年度第二期中期票据</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5513,10 +5529,14 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK23" s="3"/>
+          <t>2036-10-12</t>
+        </is>
+      </c>
+      <c r="AK23" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL23" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -5539,7 +5559,7 @@
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
@@ -5559,7 +5579,7 @@
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>食品加工</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5592,7 +5612,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26吴中经发MTN003</t>
+          <t>26安市淮阴MTN001</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5602,64 +5622,64 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102683881.IB</t>
+          <t>102683884.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.7</v>
+        <v>5.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.7</v>
+        <v>5.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>26.11</v>
+        <v>46.84</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26吴中经发MTN002</t>
+          <t>25安市淮阴MTN003</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2.85Y+2.00Y</t>
+          <t>1.52Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.6622</t>
+          <t>1.6621</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>江苏省吴中经济技术发展集团有限公司</t>
+          <t>淮安市淮阴区城市资产经营有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C- 16.95</t>
+          <t>C- 19.88</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5674,7 +5694,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -5683,17 +5703,19 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>5.4912</v>
-      </c>
-      <c r="V24" s="3"/>
+        <v>1.66</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>4.67</v>
+      </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -5704,17 +5726,17 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额5.70亿元,募集资金用于偿还债券[26吴中经发SCP001,26吴中经发SCP002,26吴中经发SCP003]</t>
+          <t>本次发行金额5亿元,募集资金拟全部用于偿还发行人本部及下属子公司有息债务[26安市淮阴CP001]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>苏州银行股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
@@ -5735,7 +5757,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>江苏省吴中经济技术发展集团有限公司2026年度第三期中期票据</t>
+          <t>淮安市淮阴区城市资产经营有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5745,14 +5767,10 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK24" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-12</t>
+        </is>
+      </c>
+      <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -5780,27 +5798,27 @@
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AV24" s="3" t="inlineStr">
@@ -5810,7 +5828,7 @@
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
@@ -5823,22 +5841,24 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ24" s="3"/>
+      <c r="AZ24" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN002</t>
+          <t>26中航K5</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>032680548.IB</t>
+          <t>525028.SZ</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5847,55 +5867,55 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.75</v>
+        <v>7.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.75</v>
+        <v>9.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>41.84</v>
+        <v>24.84</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN001</t>
+          <t>26中航K3</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7226</t>
+          <t>1.6223</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.7500/1.7000</t>
+          <t>1.6500/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司</t>
+          <t>中航科创有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 22.00</t>
+          <t>C+ 30.66</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5905,111 +5925,117 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>4.8632</v>
-      </c>
-      <c r="V25" s="4" t="n">
-        <v>22.85</v>
-      </c>
+        <v>2.47</v>
+      </c>
+      <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z25" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>安徽省-阜阳市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具注册规模12.15亿元，本期发行规模4.75亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004]</t>
+          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK25" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK25" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL25" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AM25" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
@@ -6019,17 +6045,17 @@
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>航空装备</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -6057,66 +6083,64 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ25" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ25" s="3"/>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN003</t>
+          <t>26中航K6</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>102690061.IB</t>
+          <t>525029.SZ</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
         <v>7.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>61.36</v>
+        <v>26.11</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN002B</t>
+          <t>26中航K4</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>6.86Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>2.0881</t>
+          <t>1.7088</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -6126,12 +6150,12 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
+          <t>中航科创有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 24.65</t>
+          <t>C+ 30.66</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6151,63 +6175,67 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>2.27%~2.37%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z26" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券基础发行规模为0亿元,发行金额上限为10亿元,募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN003]</t>
+          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据</t>
+          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6217,37 +6245,33 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2036-10-12</t>
-        </is>
-      </c>
-      <c r="AK26" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-13</t>
+        </is>
+      </c>
+      <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AM26" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
@@ -6257,17 +6281,17 @@
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>食品加工</t>
+          <t>航空装备</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6300,22 +6324,22 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26杭金投MTN004</t>
+          <t>26杭钢02</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>102683873.IB</t>
+          <t>246177.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
@@ -6326,48 +6350,48 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>17.85</v>
+        <v>31.84</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26杭金投MTN001</t>
+          <t>26杭钢01</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>1.69Y</t>
+          <t>2.49Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.6154</t>
+          <t>1.6419</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.6400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>杭州市金融投资集团有限公司</t>
+          <t>杭州钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 19.13</t>
+          <t>C- 21.84</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6377,33 +6401,31 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>1.54</v>
-      </c>
+        <v>2.88</v>
+      </c>
+      <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.63%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6419,18 +6441,18 @@
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据募集资金10亿元，拟全部用于偿还发行人即将到期的债务融资工具【26 杭金投SCP001】</t>
+          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,剩余部分募集资金拟用于补充公司流动资金。</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6440,12 +6462,12 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>杭州市金融投资集团有限公司2026年度第四期中期票据</t>
+          <t>杭州钢铁集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6455,13 +6477,17 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2028-04-10</t>
-        </is>
-      </c>
-      <c r="AK27" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6471,37 +6497,37 @@
       </c>
       <c r="AN27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6534,74 +6560,74 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26蜀道K9</t>
+          <t>26杭金投MTN004</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>525034.SZ</t>
+          <t>102683873.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1.5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>21.11</v>
+        <v>17.85</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>24蜀道05</t>
+          <t>26杭金投MTN001</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>5.01Y</t>
+          <t>1.69Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.7267</t>
+          <t>1.6154</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/1.7200</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司</t>
+          <t>杭州市金融投资集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.43</t>
+          <t>C- 20.01</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6611,31 +6637,33 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="V28" s="3"/>
+        <v>3.3</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>1.54</v>
+      </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.53%~1.63%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6646,23 +6674,23 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资以及符合国家法律法规要求的其他用途。</t>
+          <t>本次中期票据募集资金10亿元，拟全部用于偿还发行人即将到期的债务融资工具【26 杭金投SCP001】</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,天府证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司</t>
+          <t>浙商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
@@ -6672,12 +6700,12 @@
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第九期)</t>
+          <t>杭州市金融投资集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6687,17 +6715,13 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK28" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-04-10</t>
+        </is>
+      </c>
+      <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM28" s="3" t="inlineStr">
@@ -6707,12 +6731,12 @@
       </c>
       <c r="AN28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
@@ -6722,22 +6746,22 @@
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6770,7 +6794,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26中航K5</t>
+          <t>26蜀道K9</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6780,62 +6804,64 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>525028.SZ</t>
+          <t>525034.SZ</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F29" s="3"/>
+        <v>25.0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>25.0</v>
+      </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
           <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>24.84</v>
+        <v>21.11</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26中航K3</t>
+          <t>24蜀道05</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>5.01Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.6223</t>
+          <t>1.7267</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.6500/--</t>
+          <t>--/1.7200</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司</t>
+          <t>蜀道投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.30</t>
+          <t>C+ 34.46</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6845,7 +6871,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6855,19 +6881,21 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U29" s="3"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>4.26</v>
+      </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6875,24 +6903,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z29" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资以及符合国家法律法规要求的其他用途。</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,天府证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6903,7 +6927,7 @@
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
@@ -6913,7 +6937,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
+          <t>蜀道投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第九期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6923,12 +6947,12 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
+          <t>2031-10-12</t>
         </is>
       </c>
       <c r="AK29" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL29" s="3" t="inlineStr">
@@ -6938,42 +6962,42 @@
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
-        </is>
-      </c>
-      <c r="AR29" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS29" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>航空装备</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -7006,17 +7030,17 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26中航K6</t>
+          <t>26常城建PPN002</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>525029.SZ</t>
+          <t>032690031.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -7025,38 +7049,40 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F30" s="3"/>
+        <v>6.64</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>6.64</v>
+      </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.55 ~ 2.05</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>26.11</v>
+        <v>32.11</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26中航K4</t>
+          <t>26常城05</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>4.85Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.7088</t>
+          <t>1.8215</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -7066,12 +7092,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司</t>
+          <t>常州市城市建设(集团)有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.30</t>
+          <t>C- 24.32</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7081,21 +7107,25 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>4.2377</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>1.19</v>
+      </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -7111,199 +7141,199 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z30" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
+          <t>发行人本期定向债务融资工具发行金额为6.64亿元,拟用于偿还发行人本部存量债务融资工具本金[21常城建MTN003,26常城建SCP001]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>南京银行股份有限公司,江苏银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
+          <t>常州市城市建设(集团)有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
+          <t>2031-10-10</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>燃气</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM30" s="3" t="inlineStr">
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY30" s="3" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AO30" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="AQ30" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR30" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS30" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT30" s="3" t="inlineStr">
-        <is>
-          <t>航空装备</t>
-        </is>
-      </c>
-      <c r="AU30" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV30" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW30" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX30" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY30" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AZ30" s="3"/>
+      <c r="AZ30" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26杭钢02</t>
+          <t>26锡产业SCP015</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>246177.SH</t>
+          <t>012682379.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F31" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.31 ~ 1.51</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>31.84</v>
+        <v>31.25</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26杭钢01</t>
+          <t>25锡产业MTN005</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2.49Y</t>
+          <t>271D</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.6419</t>
+          <t>1.4940</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4800</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司</t>
+          <t>无锡产业发展集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 20.59</t>
+          <t>C- 18.84</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7313,7 +7343,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7323,19 +7353,23 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>1.2333</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>1.82</v>
+      </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7346,23 +7380,23 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,剩余部分募集资金拟用于补充公司流动资金。</t>
+          <t>本期超短期融资券发行金额6亿元用于归还发行人本部有息债务[26锡产业SCP006]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7372,12 +7406,12 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>无锡产业发展集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7387,17 +7421,13 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK31" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-07-07</t>
+        </is>
+      </c>
+      <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
@@ -7407,7 +7437,7 @@
       </c>
       <c r="AN31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO31" s="3" t="inlineStr">
@@ -7417,27 +7447,27 @@
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7470,74 +7500,74 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26常城建PPN002</t>
+          <t>26古厝13</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>032690031.IB</t>
+          <t>520514.SZ</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.64</v>
+        <v>5.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.64</v>
+        <v>5.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.55 ~ 2.05</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>32.11</v>
+        <v>34.81</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26常城05</t>
+          <t>24古厝01</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>4.85Y</t>
+          <t>2.63Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.8215</t>
+          <t>1.6920</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>常州市城市建设(集团)有限公司</t>
+          <t>福州古厝集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C 27.12</t>
+          <t>C- 21.58</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7547,25 +7577,23 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>4.2377</v>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>1.19</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -7573,7 +7601,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7584,23 +7612,23 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行金额为6.64亿元,拟用于偿还发行人本部存量债务融资工具本金[21常城建MTN003,26常城建SCP001]</t>
+          <t>本期债券发行规模不超过5.00亿元（含），募集资金在扣除发行费用后，拟用于偿还发行人到期的公司债券本金。[25古厝D6]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,江苏银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>兴业证券股份有限公司,中国国际金融股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
@@ -7610,12 +7638,12 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>常州市城市建设(集团)有限公司2026年度第二期定向债务融资工具</t>
+          <t>福州古厝集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7625,25 +7653,25 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2031-10-10</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>城投</t>
@@ -7651,27 +7679,15 @@
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ32" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR32" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3"/>
+      <c r="AR32" s="3"/>
+      <c r="AS32" s="3"/>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7699,14 +7715,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ32" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ32" s="3"/>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26锡产业SCP015</t>
+          <t>26海发宝诚SCP007</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7716,64 +7730,64 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>012682379.IB</t>
+          <t>012682380.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>0.26Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
+          <t>1.35 ~ 1.49</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>31.25</v>
+        <v>30.32</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>25锡产业MTN005</t>
+          <t>25海租01</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>271D</t>
+          <t>93D</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.4940</t>
+          <t>1.4631</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/1.4800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司</t>
+          <t>海发宝诚融资租赁有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 18.79</t>
+          <t>C- 14.11</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7793,23 +7807,23 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1.2333</v>
+        <v>1.0</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>1.82</v>
+        <v>1.0</v>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7820,17 +7834,17 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额6亿元用于归还发行人本部有息债务[26锡产业SCP006]</t>
+          <t>本期超短期融资券基础发行金额0亿元，发行金额上限5亿元，拟全部用于偿还发行人即将到期的债务融资工具[26海发宝诚SCP006]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>平安银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7841,7 +7855,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
@@ -7851,7 +7865,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司2026年度第十五期超短期融资券</t>
+          <t>海发宝诚融资租赁有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7861,53 +7875,53 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2027-07-07</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7935,79 +7949,81 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ33" s="3"/>
+      <c r="AZ33" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26古厝13</t>
+          <t>26广州地铁SCP015</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>520514.SZ</t>
+          <t>012682381.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.0</v>
+        <v>14.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.0</v>
+        <v>14.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.26 ~ 1.55</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>34.81</v>
+        <v>15.25</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>24古厝01</t>
+          <t>17广州地铁专项债01</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.63Y</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.6920</t>
+          <t>1.4941</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司</t>
+          <t>广州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 21.71</t>
+          <t>C+ 32.05</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8017,7 +8033,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -8031,17 +8047,17 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.2</v>
+        <v>3.8857</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -8052,23 +8068,23 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过5.00亿元（含），募集资金在扣除发行费用后，拟用于偿还发行人到期的公司债券本金。[25古厝D6]</t>
+          <t>本期超短期融资券金额14亿元，其中5亿元用于归还发行人存量债券，9亿元用于归还发行人金融机构借款。[26广州地铁SCP001]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,中国国际金融股份有限公司,天风证券股份有限公司</t>
+          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -8078,28 +8094,28 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>广州地铁集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
@@ -8114,20 +8130,32 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ34" s="3"/>
-      <c r="AR34" s="3"/>
-      <c r="AS34" s="3"/>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8160,59 +8188,59 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26海发宝诚SCP007</t>
+          <t>26天长01</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>012682380.IB</t>
+          <t>284203.SH</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>0.26Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.49</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>30.32</v>
+        <v>46.84</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>25海租01</t>
+          <t>25滁高01</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>93D</t>
+          <t>1.64Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.4631</t>
+          <t>1.6256</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -8222,12 +8250,12 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>海发宝诚融资租赁有限公司</t>
+          <t>天长市科技工业发展有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 14.76</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8237,7 +8265,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8251,77 +8279,83 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="V35" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>4.2</v>
+      </c>
+      <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>安徽省-滁州市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额0亿元，发行金额上限5亿元，拟全部用于偿还发行人即将到期的债务融资工具[26海发宝诚SCP006]</t>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还“23天长02”公司债券本金。[23天长02]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,上海银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD35" s="3"/>
+          <t>五矿证券有限公司,川财证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr">
+        <is>
+          <t>安徽省信用融资担保集团有限公司</t>
+        </is>
+      </c>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>海发宝诚融资租赁有限公司2026年度第七期超短期融资券</t>
+          <t>天长市科技工业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
@@ -8336,32 +8370,32 @@
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8371,7 +8405,7 @@
       </c>
       <c r="AV35" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW35" s="3" t="inlineStr">
@@ -8389,66 +8423,64 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ35" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ35" s="3"/>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26广州地铁SCP015</t>
+          <t>26凯建01</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>012682381.IB</t>
+          <t>284219.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.55</t>
+          <t>2.40 ~ 3.40</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.35</v>
+        <v>2.65</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>15.25</v>
+        <v>124.11</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>17广州地铁专项债01</t>
+          <t>25凯建01</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>4.15Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.4941</t>
+          <t>2.8084</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -8458,12 +8490,12 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司</t>
+          <t>凯里正源城镇建设发展有限责任公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.28</t>
+          <t>B- 42.31</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8473,7 +8505,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8487,44 +8519,48 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>3.8857</v>
+        <v>2.66</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8-</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>2.79%~2.89%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>贵州省-黔东南苗族侗族自治州</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券金额14亿元，其中5亿元用于归还发行人存量债券，9亿元用于归还发行人金融机构借款。[26广州地铁SCP001]</t>
+          <t>本期债券募集资金扣除承销费用后，拟全部用于统借统还偿还到期公司债券本金</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD36" s="3"/>
+          <t>第一创业证券承销保荐有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr">
+        <is>
+          <t>贵州省信用增进有限公司</t>
+        </is>
+      </c>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8534,28 +8570,32 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司2026年度第十五期超短期融资券</t>
+          <t>凯里正源城镇建设发展有限责任公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
-        </is>
-      </c>
-      <c r="AK36" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK36" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
@@ -8570,12 +8610,12 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
@@ -8585,17 +8625,17 @@
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8605,7 +8645,7 @@
       </c>
       <c r="AV36" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW36" s="3" t="inlineStr">
@@ -8628,74 +8668,74 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26天长01</t>
+          <t>26兴化城投PPN009</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>284203.SH</t>
+          <t>032680552.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>46.84</v>
+        <v>39.81</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>25滁高01</t>
+          <t>26兴化城投PPN008</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>1.64Y</t>
+          <t>1.88Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.6256</t>
+          <t>1.6847</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>天长市科技工业发展有限公司</t>
+          <t>兴化市城市建设投资有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 16.51</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8705,7 +8745,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8715,21 +8755,23 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V37" s="3"/>
+        <v>3.6</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>1.26</v>
+      </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8737,34 +8779,26 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="Z37" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>安徽省-滁州市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,全部用于偿还“23天长02”公司债券本金。[23天长02]</t>
+          <t>本期定向债务融资工具发行金额4亿元,拟用于偿还发行人有息债务[26兴化城投PPN002]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司,川财证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD37" s="3" t="inlineStr">
-        <is>
-          <t>安徽省信用融资担保集团有限公司</t>
-        </is>
-      </c>
+          <t>江苏江南农村商业银行股份有限公司,苏州银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8774,12 +8808,12 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>天长市科技工业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>兴化市城市建设投资有限公司2026年度第九期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8789,63 +8823,63 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2028-10-10</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>农产品加工</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM37" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO37" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ37" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR37" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV37" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW37" s="3" t="inlineStr">
@@ -8868,17 +8902,17 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26凯建01</t>
+          <t>26绍兴高新MTN003</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>284219.SH</t>
+          <t>102683883.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -8887,40 +8921,40 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>3.0</v>
+        <v>8.2</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3.0</v>
+        <v>8.2</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2.40 ~ 3.40</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>124.11</v>
+        <v>41.11</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>25凯建01</t>
+          <t>26绍兴高新MTN002</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>4.15Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2.8084</t>
+          <t>1.8213</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -8930,12 +8964,12 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>凯里正源城镇建设发展有限责任公司</t>
+          <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B- 42.31</t>
+          <t>C- 22.73</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8945,12 +8979,12 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
@@ -8959,48 +8993,44 @@
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>2.66</v>
+        <v>5.0366</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>8-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>2.79%~2.89%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>贵州省-黔东南苗族侗族自治州</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除承销费用后，拟全部用于统借统还偿还到期公司债券本金</t>
+          <t>发行人本期中期票据发行金额人民币8.20亿元,拟全部用于偿还发行人本级2026年到期的债务融资工具本金[23绍兴高新MTN002]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>第一创业证券承销保荐有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD38" s="3" t="inlineStr">
-        <is>
-          <t>贵州省信用增进有限公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,宁波银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -9010,17 +9040,17 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>凯里正源城镇建设发展有限责任公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>绍兴高新技术产业开发区投资发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
@@ -9035,57 +9065,57 @@
       </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO38" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="AQ38" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR38" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW38" s="3" t="inlineStr">
@@ -9108,7 +9138,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26兴化城投PPN009</t>
+          <t>26皖投集MTN006</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -9118,64 +9148,64 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>032680552.IB</t>
+          <t>102683882.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>39.81</v>
+        <v>22.84</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26兴化城投PPN008</t>
+          <t>24皖投03</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>1.88Y</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.6847</t>
+          <t>1.6119</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.7100/--</t>
+          <t>--/1.5900</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>兴化市城市建设投资有限公司</t>
+          <t>安徽省投资集团控股有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 17.15</t>
+          <t>C- 18.28</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9190,55 +9220,55 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>3.6</v>
+        <v>5.16</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>1.26</v>
+        <v>3.08</v>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额4亿元,拟用于偿还发行人有息债务[26兴化城投PPN002]</t>
+          <t>本期中期票据募集资金5亿元人民币，全部用于偿还发行人即将到期的债券[25皖投集CP003]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>江苏江南农村商业银行股份有限公司,苏州银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,国家开发银行</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9253,43 +9283,43 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>兴化市城市建设投资有限公司2026年度第九期定向债务融资工具</t>
+          <t>安徽省投资集团控股有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2028-10-10</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
@@ -9309,7 +9339,7 @@
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>农产品加工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9342,59 +9372,59 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26绍兴高新MTN003</t>
+          <t>26唐租01</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>102683883.IB</t>
+          <t>246158.SH</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>8.2</v>
+        <v>10.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>8.2</v>
+        <v>10.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>41.11</v>
+        <v>39.84</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26绍兴高新MTN002</t>
+          <t>25大唐租赁MTN002B(绿色)</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>1.63Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.8213</t>
+          <t>1.6333</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -9404,12 +9434,12 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
+          <t>大唐融资租赁有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 20.62</t>
+          <t>B- 35.39</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9419,21 +9449,21 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>5.0366</v>
+        <v>2.34</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
@@ -9443,49 +9473,49 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额人民币8.20亿元,拟全部用于偿还发行人本级2026年到期的债务融资工具本金[23绍兴高新MTN002]</t>
+          <t>本期债券募集资金10.00亿元拟用于偿还发行人到期公司债券本金[24唐租04]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,宁波银行股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>绍兴高新技术产业开发区投资发展集团有限公司2026年度第三期中期票据</t>
+          <t>大唐融资租赁有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9495,57 +9525,57 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
+          <t>2029-10-13</t>
         </is>
       </c>
       <c r="AK40" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL40" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AM40" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-10-09.xlsx
+++ b/data/credit_bond_all_2026-10-09.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-14" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-15" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.82</t>
+          <t>C+ 32.26</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 13.67</t>
+          <t>C- 15.21</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 17.07</t>
+          <t>C- 14.81</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C- 14.35</t>
+          <t>C- 13.68</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1563,7 +1563,7 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C 27.65</t>
+          <t>C 27.97</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 23.54</t>
+          <t>C- 23.75</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>B- 43.92</t>
+          <t>B- 43.00</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 11.53</t>
+          <t>C- 10.38</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C- 24.33</t>
+          <t>C- 23.93</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 23.77</t>
+          <t>C- 24.00</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C 26.00</t>
+          <t>C- 24.58</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.05</t>
+          <t>C+ 32.85</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 39.08</t>
+          <t>B- 41.57</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 13.51</t>
+          <t>C- 13.72</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C 28.26</t>
+          <t>C+ 33.54</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 19.51</t>
+          <t>C- 21.11</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C- 24.91</t>
+          <t>C+ 30.33</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 24.33</t>
+          <t>C- 23.93</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.66</t>
+          <t>C+ 31.28</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.66</t>
+          <t>C+ 31.28</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.46</t>
+          <t>B- 36.63</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 24.32</t>
+          <t>C 25.80</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 18.84</t>
+          <t>C- 17.06</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 14.11</t>
+          <t>C- 15.93</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.05</t>
+          <t>C+ 32.85</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C- 22.73</t>
+          <t>C- 22.07</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 18.28</t>
+          <t>C- 17.65</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>B- 35.39</t>
+          <t>B- 35.40</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-10-09.xlsx
+++ b/data/credit_bond_all_2026-10-09.xlsx
@@ -692,74 +692,74 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26联投Y5</t>
+          <t>26镇江产投MTN008</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>246172.SH</t>
+          <t>102683874.IB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>49.84</v>
+        <v>30.84</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>26鄂联投MTN002</t>
+          <t>26镇江产投MTN007</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2.92Y+N</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>1.7641</t>
+          <t>1.6876</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.7600/--</t>
+          <t>1.6900/1.6600</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>湖北省联合发展投资集团有限公司</t>
+          <t>镇江产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.26</t>
+          <t>C- 15.21</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -769,31 +769,33 @@
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U3" s="4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="V3" s="3"/>
+        <v>3.5667</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -804,23 +806,23 @@
       <c r="Z3" s="3"/>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>湖北省</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于生产性支出,包括但不限于补充流动资金、偿还有息债务、项目建设、权益投资等符合国家法律法规及政策要求的企业生产经营活动。</t>
+          <t>发行人本次发行的3.00亿元中期票据全部用于偿还发行人存量有息债务[25镇江产投CP004]</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,平安证券股份有限公司,中国银河证券股份有限公司,广发证券股份有限公司</t>
+          <t>中国民生银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -830,12 +832,12 @@
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>湖北省联合发展投资集团有限公司2026年面向专业投资者公开发行可续期公司债券(第五期)</t>
+          <t>镇江产业投资控股集团有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
@@ -845,100 +847,98 @@
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK3" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2029-10-10</t>
+        </is>
+      </c>
+      <c r="AK3" s="3"/>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY3" s="3" t="inlineStr">
+        <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ3" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>永续</t>
-        </is>
-      </c>
-      <c r="AX3" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AZ3" s="3"/>
+      <c r="AZ3" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26镇江产投MTN008</t>
+          <t>26苏金04</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>102683874.IB</t>
+          <t>284122.SH</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -947,55 +947,55 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3.0</v>
+        <v>3.6</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>3.0</v>
+        <v>3.6</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>30.84</v>
+        <v>46.84</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26镇江产投MTN007</t>
+          <t>26苏金03</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.6876</t>
+          <t>1.7214</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.6900/1.6600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>镇江产业投资控股集团有限公司</t>
+          <t>苏州金合盛控股有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 15.21</t>
+          <t>C- 14.81</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1005,60 +1005,62 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>3.5667</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>4.34</v>
+      </c>
+      <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行的3.00亿元中期票据全部用于偿还发行人存量有息债务[25镇江产投CP004]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金。[23苏金04]</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,南京银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD4" s="3"/>
+          <t>东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>苏州苏高新集团有限公司</t>
+        </is>
+      </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1068,70 +1070,74 @@
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>镇江产业投资控股集团有限公司2026年度第八期中期票据</t>
+          <t>苏州金合盛控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2029-10-10</t>
-        </is>
-      </c>
-      <c r="AK4" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
       <c r="AU4" s="3" t="inlineStr">
         <is>
           <t/>
@@ -1139,7 +1145,7 @@
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW4" s="3" t="inlineStr">
@@ -1157,14 +1163,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ4" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ4" s="3"/>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26苏金04</t>
+          <t>26通新01</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1174,49 +1178,49 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>284122.SH</t>
+          <t>284151.SH</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3.6</v>
+        <v>5.0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3.6</v>
+        <v>5.0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>46.84</v>
+        <v>41.11</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>26苏金03</t>
+          <t>24通新03</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>3.05Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.7214</t>
+          <t>1.7098</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1226,12 +1230,12 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>苏州金合盛控股有限公司</t>
+          <t>南通高新控股集团有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 14.81</t>
+          <t>C- 13.68</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1255,33 +1259,33 @@
         </is>
       </c>
       <c r="U5" s="4" t="n">
-        <v>4.34</v>
+        <v>5.51</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金。[23苏金04]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换偿还到期公司债券本金的自有资金[21通新01]</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
@@ -1289,11 +1293,7 @@
           <t>东吴证券股份有限公司</t>
         </is>
       </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>苏州苏高新集团有限公司</t>
-        </is>
-      </c>
+      <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>苏州金合盛控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>南通高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
@@ -1321,14 +1321,10 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK5" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-13</t>
+        </is>
+      </c>
+      <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1336,7 +1332,7 @@
       </c>
       <c r="AM5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN5" s="3" t="inlineStr">
@@ -1346,32 +1342,32 @@
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ5" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr">
@@ -1381,7 +1377,7 @@
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW5" s="3" t="inlineStr">
@@ -1404,7 +1400,7 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26通新01</t>
+          <t>26榕水02</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1414,7 +1410,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>284151.SH</t>
+          <t>525031.SZ</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1423,55 +1419,55 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>41.11</v>
+        <v>33.11</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>24通新03</t>
+          <t>24榕水04</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>3.05Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.7098</t>
+          <t>1.7324</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>南通高新控股集团有限公司</t>
+          <t>福州水务集团有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C- 13.68</t>
+          <t>D+ 7.27</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1481,7 +1477,7 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
@@ -1495,38 +1491,38 @@
         </is>
       </c>
       <c r="U6" s="4" t="n">
-        <v>5.51</v>
+        <v>4.86</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换偿还到期公司债券本金的自有资金[21通新01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务。[23榕水01]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>中信证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
@@ -1542,17 +1538,17 @@
       </c>
       <c r="AG6" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>南通高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>福州水务集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="inlineStr">
@@ -1563,7 +1559,7 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t/>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr">
@@ -1578,32 +1574,32 @@
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1636,7 +1632,7 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26榕水02</t>
+          <t>26左海02</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1646,64 +1642,64 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>525031.SZ</t>
+          <t>284143.SH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>33.11</v>
+        <v>28.11</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>24榕水04</t>
+          <t>25左海01</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>3.26Y+5.00Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.7324</t>
+          <t>1.7199</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/1.7600</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>福州水务集团有限公司</t>
+          <t>福州左海控股集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.27</t>
+          <t>C 27.97</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1723,21 +1719,21 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U7" s="4" t="n">
-        <v>4.86</v>
+        <v>4.56</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1753,12 +1749,12 @@
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务。[23榕水01]</t>
+          <t>本期公司债券拟发行5亿元，募集资金扣除发行费用后，拟全部用于偿还公司债券本金【23左海03 】</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华福证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
@@ -1774,25 +1770,29 @@
       </c>
       <c r="AG7" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>福州水务集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>福州左海控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
-        </is>
-      </c>
-      <c r="AK7" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL7" s="3" t="inlineStr">
         <is>
           <t/>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="AM7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO7" s="3" t="inlineStr">
@@ -1815,32 +1815,32 @@
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AV7" s="3" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AW7" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX7" s="3" t="inlineStr">
@@ -1868,74 +1868,74 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26左海02</t>
+          <t>26创星PPN002(科创债)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>284143.SH</t>
+          <t>032680550.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>2.20 ~ 2.60</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.69</v>
+        <v>2.55</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>28.11</v>
+        <v>126.84</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>25左海01</t>
+          <t>25创星PPN001(科创债)</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>3.26Y+5.00Y</t>
+          <t>3.69Y+5.00Y</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.7199</t>
+          <t>1.7809</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>福州左海控股集团有限公司</t>
+          <t>中科创星科技投资有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C 27.97</t>
+          <t>D+ 9.13</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -1955,63 +1955,65 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U8" s="4" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="V8" s="3"/>
+        <v>1.5</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>2.45%~2.55%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券拟发行5亿元，募集资金扣除发行费用后，拟全部用于偿还公司债券本金【23左海03 】</t>
+          <t>本次定向债务融资工具发行拟募集资金1亿元,所募集资金拟用于置换前期出资、新增基金出资以及补充流动资金</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,华福证券股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>福州左海控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>中科创星科技投资有限公司2026年度第二期定向科技创新债券</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -2021,64 +2023,56 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK8" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-10</t>
+        </is>
+      </c>
+      <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP8" s="3"/>
+      <c r="AQ8" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ8" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR8" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>高速公路</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
-        <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2086,7 +2080,7 @@
       </c>
       <c r="AW8" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX8" s="3" t="inlineStr">
@@ -2099,12 +2093,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ8" s="3"/>
+      <c r="AZ8" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26创星PPN002(科创债)</t>
+          <t>26广州产投SCP008</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2114,64 +2110,64 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>032680550.IB</t>
+          <t>012682378.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.0</v>
+        <v>10.5</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.0</v>
+        <v>10.5</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.60</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.55</v>
+        <v>1.44</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>126.84</v>
+        <v>24.25</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>25创星PPN001(科创债)</t>
+          <t>26广州产投SCP007</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>3.69Y+5.00Y</t>
+          <t>259D</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.7809</t>
+          <t>1.4923</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/1.7600</t>
+          <t>1.5000/1.4900</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>中科创星科技投资有限公司</t>
+          <t>广州产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.13</t>
+          <t>C- 23.75</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2195,51 +2191,51 @@
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.5</v>
+        <v>1.3143</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.0</v>
+        <v>1.06</v>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>2.45%~2.55%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具发行拟募集资金1亿元,所募集资金拟用于置换前期出资、新增基金出资以及补充流动资金</t>
+          <t>本期超短期融资券的发行规模为10.5亿元，募集资金全部用于偿还到期债务融资工具[26 广州产投SCP002 ]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司</t>
+          <t>平安银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr">
@@ -2249,17 +2245,17 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>中科创星科技投资有限公司2026年度第二期定向科技创新债券</t>
+          <t>广州产业投资控股集团有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2029-10-10</t>
+          <t>2027-07-07</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
@@ -2270,7 +2266,7 @@
       </c>
       <c r="AM9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN9" s="3" t="inlineStr">
@@ -2280,28 +2276,32 @@
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP9" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2329,14 +2329,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ9" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ9" s="3"/>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP008</t>
+          <t>26鲁高速SCP004</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2346,19 +2344,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>012682378.IB</t>
+          <t>012682377.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>0.66Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10.5</v>
+        <v>20.0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.5</v>
+        <v>30.0</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -2366,44 +2364,44 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>24.25</v>
+        <v>17.25</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP007</t>
+          <t>24鲁高K3</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>259D</t>
+          <t>290D</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.4923</t>
+          <t>1.4600</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>1.5000/1.4900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司</t>
+          <t>山东高速集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 23.75</t>
+          <t>B- 43.00</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2413,12 +2411,12 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 10:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2427,19 +2425,19 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.3143</v>
+        <v>1.5667</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.06</v>
+        <v>9.0</v>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.43%~1.47%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2450,17 +2448,17 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券的发行规模为10.5亿元，募集资金全部用于偿还到期债务融资工具[26 广州产投SCP002 ]</t>
+          <t>本期超短期融资券基础发行金额20亿元，发行金额上限30亿元，募集资金用于偿还发行人本部及子公司有息负债及补充流动资金</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,中信银行股份有限公司</t>
+          <t>广发银行股份有限公司,北京银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
@@ -2481,7 +2479,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司2026年度第八期超短期融资券</t>
+          <t>山东高速集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2491,7 +2489,7 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2027-07-07</t>
+          <t>2027-06-07</t>
         </is>
       </c>
       <c r="AK10" s="3"/>
@@ -2512,32 +2510,32 @@
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2570,7 +2568,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26鲁高速SCP004</t>
+          <t>26南京公路MTN003</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2580,64 +2578,64 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>012682377.IB</t>
+          <t>102683875.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0.66Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>20.0</v>
+        <v>2.0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>30.0</v>
+        <v>2.0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>17.25</v>
+        <v>24.11</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>24鲁高K3</t>
+          <t>25南京公路MTN001</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>290D</t>
+          <t>3.83Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.4600</t>
+          <t>1.6928</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司</t>
+          <t>南京公路发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>B- 43.00</t>
+          <t>C- 10.38</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2647,12 +2645,12 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>10-09 10:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2661,19 +2659,19 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.5667</v>
+        <v>2.5</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.43%~1.47%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -2684,23 +2682,27 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额20亿元，发行金额上限30亿元，募集资金用于偿还发行人本部及子公司有息负债及补充流动资金</t>
+          <t>本期中期票据发行金额2亿元,募集资金用于偿还发行人本级及下属子公司有息债务</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司,北京银行股份有限公司,中国建设银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD11" s="3"/>
+          <t>南京银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+        </is>
+      </c>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -2715,7 +2717,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司2026年度第四期超短期融资券</t>
+          <t>南京公路发展(集团)有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2725,7 +2727,7 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2027-06-07</t>
+          <t>2031-10-10</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
@@ -2746,12 +2748,12 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
@@ -2781,7 +2783,7 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW11" s="3" t="inlineStr">
@@ -2799,12 +2801,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ11" s="3"/>
+      <c r="AZ11" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26南京公路MTN003</t>
+          <t>26涪陵国资MTN003A(取消发行)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2814,64 +2818,58 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>102683875.IB</t>
+          <t>DY102690060.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>24.11</v>
-      </c>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>25南京公路MTN001</t>
+          <t>26涪陵国资MTN002B</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>3.83Y</t>
+          <t>6.86Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.6928</t>
+          <t>2.0881</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1.7100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 10.38</t>
+          <t>C- 23.93</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2881,61 +2879,53 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>1.0</v>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>2.21%~2.31%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额2亿元,募集资金用于偿还发行人本级及下属子公司有息债务</t>
+          <t>本期债券基础发行规模为0亿元,发行金额上限为10亿元,募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN003]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -2953,7 +2943,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司2026年度第三期中期票据</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2963,53 +2953,53 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2031-10-10</t>
+          <t>2033-10-12</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>食品加工</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -3019,7 +3009,7 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
@@ -3037,75 +3027,79 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ12" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ12" s="3"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN003A(取消发行)</t>
+          <t>26云能04</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>DY102690060.IB</t>
+          <t>246167.SH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F13" s="3"/>
+        <v>15.0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>15.0</v>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+          <t>1.60 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>48.22</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN002B</t>
+          <t>25云能投MTN003</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>6.86Y</t>
+          <t>3.89Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>2.0881</t>
+          <t>1.8363</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8600/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
+          <t>云南省能源集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C- 23.93</t>
+          <t>C- 24.00</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3115,7 +3109,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3128,43 +3122,45 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U13" s="3"/>
+      <c r="U13" s="4" t="n">
+        <v>3.19</v>
+      </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>2.21%~2.31%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期债券基础发行规模为0亿元,发行金额上限为10亿元,募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN003]</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,太平洋证券股份有限公司,平安证券股份有限公司,五矿证券有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3174,12 +3170,12 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据(品种一)(取消发行)</t>
+          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3189,18 +3185,22 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2033-10-12</t>
-        </is>
-      </c>
-      <c r="AK13" s="3"/>
+          <t>2030-10-12</t>
+        </is>
+      </c>
+      <c r="AK13" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t/>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN13" s="3" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
@@ -3225,17 +3225,17 @@
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>食品加工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3268,7 +3268,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26云能04</t>
+          <t>26鲲鹏投资02</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3278,64 +3278,64 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>246167.SH</t>
+          <t>525030.SZ</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>1+1</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.20 ~ 2.00</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>48.22</v>
+        <v>20.81</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>25云能投MTN003</t>
+          <t>25鲲鹏02</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>3.89Y</t>
+          <t>1.07Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.8363</t>
+          <t>1.5373</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.8600/--</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司</t>
+          <t>深圳市鲲鹏股权投资管理有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 24.00</t>
+          <t>C+ 34.97</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3359,17 +3359,17 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3380,17 +3380,17 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还有息债务</t>
+          <t>本期债券发行规模为不超过16亿元(含16亿元),募集资金扣除发行费用后,拟使用不超过15亿元用于偿还到期的公司债券本金,剩余募集资金用于补充流动资金。[24鲲鹏04]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,太平洋证券股份有限公司,平安证券股份有限公司,五矿证券有限公司</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3406,12 +3406,12 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>深圳市鲲鹏股权投资管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3421,14 +3421,10 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2030-10-12</t>
-        </is>
-      </c>
-      <c r="AK14" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-10-12</t>
+        </is>
+      </c>
+      <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
           <t/>
@@ -3446,37 +3442,33 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP14" s="3"/>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-10-12</t>
         </is>
       </c>
       <c r="AV14" s="3" t="inlineStr">
@@ -3486,7 +3478,7 @@
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr">
@@ -3504,74 +3496,74 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26鲲鹏投资02</t>
+          <t>26淮安国投MTN006</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>525030.SZ</t>
+          <t>102683878.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1+1</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>16.0</v>
+        <v>2.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>16.0</v>
+        <v>2.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.00</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>20.81</v>
+        <v>32.81</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>25鲲鹏02</t>
+          <t>26淮安国投MTN005</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>1.07Y</t>
+          <t>1.90Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.5373</t>
+          <t>1.6140</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.5500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>深圳市鲲鹏股权投资管理有限公司</t>
+          <t>淮安市国有联合投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.97</t>
+          <t>C- 24.58</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3581,12 +3573,12 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -3595,17 +3587,19 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="V15" s="3"/>
+        <v>4.7</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>2.33</v>
+      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>1.49%~1.59%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3616,23 +3610,23 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过16亿元(含16亿元),募集资金扣除发行费用后,拟使用不超过15亿元用于偿还到期的公司债券本金,剩余募集资金用于补充流动资金。[24鲲鹏04]</t>
+          <t>本期发行金额2亿元，募集资金拟全部用于偿还发行人到期债券[25淮安国投MTN002]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
+          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3642,12 +3636,12 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>深圳市鲲鹏股权投资管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3663,76 +3657,82 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM15" s="3" t="inlineStr">
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY15" s="3" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO15" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP15" s="3"/>
-      <c r="AQ15" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR15" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t>2027-10-12</t>
-        </is>
-      </c>
-      <c r="AV15" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW15" s="3" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AX15" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AZ15" s="3"/>
+      <c r="AZ15" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN006</t>
+          <t>26广州地铁SCP014</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3742,49 +3742,49 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683878.IB</t>
+          <t>012682383.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.26 ~ 1.55</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>32.81</v>
+        <v>15.25</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN005</t>
+          <t>17广州地铁专项债01</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>1.90Y</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.6140</t>
+          <t>1.4941</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>广州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 24.58</t>
+          <t>C+ 32.85</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -3823,19 +3823,17 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>2.33</v>
-      </c>
+        <v>3.79</v>
+      </c>
+      <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.59%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3846,23 +3844,23 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额2亿元，募集资金拟全部用于偿还发行人到期债券[25淮安国投MTN002]</t>
+          <t>本期超短期融资券金额20亿元，全部用于归还发行人的债务融资工具。[26广州地铁SCP001]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3877,7 +3875,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年度第六期中期票据</t>
+          <t>广州地铁集团有限公司2026年度第十四期超短期融资券</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3887,7 +3885,7 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
@@ -3908,12 +3906,12 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
@@ -3923,17 +3921,17 @@
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3961,14 +3959,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ16" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ16" s="3"/>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26广州地铁SCP014</t>
+          <t>26宿迁新城MTN001</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3978,49 +3974,49 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>012682383.IB</t>
+          <t>102683877.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>20.0</v>
+        <v>6.88</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>20.0</v>
+        <v>6.88</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.55</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>15.25</v>
+        <v>36.81</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>17广州地铁专项债01</t>
+          <t>26宿迁新城CP001</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>159D</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.4941</t>
+          <t>1.5334</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -4030,12 +4026,12 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司</t>
+          <t>宿迁市新城控股集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.85</t>
+          <t>B- 41.57</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4050,7 +4046,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
@@ -4059,44 +4055,46 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="V17" s="3"/>
+        <v>4.6584</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>1.8</v>
+      </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券金额20亿元，全部用于归还发行人的债务融资工具。[26广州地铁SCP001]</t>
+          <t>首期拟发行金额6.88亿元募集资金拟用于偿还发行人存量债务融资工具本金[25宿迁新城CP002]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
+          <t>南京银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4111,7 +4109,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司2026年度第十四期超短期融资券</t>
+          <t>宿迁市新城控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4121,7 +4119,7 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
@@ -4142,12 +4140,12 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
@@ -4157,17 +4155,17 @@
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4195,12 +4193,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ17" s="3"/>
+      <c r="AZ17" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城MTN001</t>
+          <t>26连云港SCP004</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4210,49 +4210,49 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683877.IB</t>
+          <t>012682382.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>6.88</v>
+        <v>4.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6.88</v>
+        <v>4.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>36.81</v>
+        <v>30.25</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城CP001</t>
+          <t>26连云港SCP003</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>159D</t>
+          <t>248D</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.5334</t>
+          <t>1.5426</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司</t>
+          <t>连云港港口集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 41.57</t>
+          <t>C- 13.72</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -4291,19 +4291,19 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>4.6584</v>
+        <v>3.475</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.8</v>
+        <v>1.0</v>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.59%~1.63%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4314,23 +4314,23 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>江苏省-连云港市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>首期拟发行金额6.88亿元募集资金拟用于偿还发行人存量债务融资工具本金[25宿迁新城CP002]</t>
+          <t>本期超短期融资券发行金额4.00亿元,募集资金全部用于偿还发行人存量有息债务。</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,交通银行股份有限公司</t>
+          <t>南京银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司2026年度第一期中期票据</t>
+          <t>连云港港口集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
@@ -4376,12 +4376,12 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4430,13 +4430,13 @@
         </is>
       </c>
       <c r="AZ18" s="4" t="n">
-        <v>0.0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP004</t>
+          <t>26莆田国资MTN002</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4446,49 +4446,49 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>012682382.IB</t>
+          <t>102683876.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>30.25</v>
+        <v>40.84</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP003</t>
+          <t>26莆田国资MTN001</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>248D</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.5426</t>
+          <t>1.6718</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司</t>
+          <t>莆田市国有资产投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 13.72</t>
+          <t>C+ 33.54</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
@@ -4527,19 +4527,17 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>3.475</v>
-      </c>
-      <c r="V19" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>5.26</v>
+      </c>
+      <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.63%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4550,23 +4548,23 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>江苏省-连云港市</t>
+          <t>福建省-莆田市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4.00亿元,募集资金全部用于偿还发行人存量有息债务。</t>
+          <t>发行人本期中期票据发行金额为10亿元,拟用于偿还发行人本部接续债务融资工具的专项贷款。[21莆田国资PPN003]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,中国银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4581,7 +4579,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司2026年度第四期超短期融资券</t>
+          <t>莆田市国有资产投资集团有限责任公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4591,7 +4589,7 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK19" s="3"/>
@@ -4612,7 +4610,7 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
@@ -4622,22 +4620,22 @@
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4665,14 +4663,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ19" s="4" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="AZ19" s="3"/>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26莆田国资MTN002</t>
+          <t>26吴中经发MTN003</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4682,64 +4678,64 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>102683876.IB</t>
+          <t>102683881.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>10.0</v>
+        <v>5.7</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.0</v>
+        <v>5.7</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>40.84</v>
+        <v>26.11</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26莆田国资MTN001</t>
+          <t>26吴中经发MTN002</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>2.85Y+2.00Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.6718</t>
+          <t>1.6622</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>莆田市国有资产投资集团有限责任公司</t>
+          <t>江苏省吴中经济技术发展集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.54</t>
+          <t>C- 21.11</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4749,12 +4745,12 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -4763,17 +4759,17 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>5.26</v>
+        <v>5.4912</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4784,17 +4780,17 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>福建省-莆田市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为10亿元,拟用于偿还发行人本部接续债务融资工具的专项贷款。[21莆田国资PPN003]</t>
+          <t>本期中期票据发行金额5.70亿元,募集资金用于偿还债券[26吴中经发SCP001,26吴中经发SCP002,26吴中经发SCP003]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
+          <t>苏州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
@@ -4815,7 +4811,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>莆田市国有资产投资集团有限责任公司2026年度第二期中期票据</t>
+          <t>江苏省吴中经济技术发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4825,60 +4821,64 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK20" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
           <t>2029-10-12</t>
         </is>
       </c>
-      <c r="AK20" s="3"/>
-      <c r="AL20" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AM20" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO20" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ20" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR20" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS20" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX20" s="3" t="inlineStr">
@@ -4904,7 +4904,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26吴中经发MTN003</t>
+          <t>26阜阳投资PPN002</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4914,64 +4914,64 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>102683881.IB</t>
+          <t>032680548.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.7</v>
+        <v>4.75</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5.7</v>
+        <v>4.75</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.40 ~ 2.10</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>26.11</v>
+        <v>41.84</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26吴中经发MTN002</t>
+          <t>26阜阳投资PPN001</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2.85Y+2.00Y</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.6622</t>
+          <t>1.7226</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>1.7500/1.7000</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>江苏省吴中经济技术发展集团有限公司</t>
+          <t>阜阳投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 21.11</t>
+          <t>C+ 30.33</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -4995,17 +4995,19 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>5.4912</v>
-      </c>
-      <c r="V21" s="3"/>
+        <v>4.8632</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>22.85</v>
+      </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -5016,23 +5018,23 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>安徽省-阜阳市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额5.70亿元,募集资金用于偿还债券[26吴中经发SCP001,26吴中经发SCP002,26吴中经发SCP003]</t>
+          <t>本次定向债务融资工具注册规模12.15亿元，本期发行规模4.75亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>苏州银行股份有限公司</t>
+          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -5047,24 +5049,20 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>江苏省吴中经济技术发展集团有限公司2026年度第三期中期票据</t>
+          <t>阜阳投资发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK21" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-12</t>
+        </is>
+      </c>
+      <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -5087,32 +5085,32 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t/>
         </is>
       </c>
       <c r="AV21" s="3" t="inlineStr">
@@ -5122,7 +5120,7 @@
       </c>
       <c r="AW21" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX21" s="3" t="inlineStr">
@@ -5135,12 +5133,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ21" s="3"/>
+      <c r="AZ21" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN002</t>
+          <t>26涪陵国资MTN003</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5150,64 +5150,64 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>032680548.IB</t>
+          <t>102690061.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.75</v>
+        <v>7.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4.75</v>
+        <v>10.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>41.84</v>
+        <v>61.36</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN001</t>
+          <t>26涪陵国资MTN002B</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>6.86Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.7226</t>
+          <t>2.0881</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1.7500/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.33</t>
+          <t>C- 23.93</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
@@ -5231,19 +5231,17 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>4.8632</v>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>22.85</v>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>2.27%~2.37%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5254,23 +5252,23 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>安徽省-阜阳市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具注册规模12.15亿元，本期发行规模4.75亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004]</t>
+          <t>本期债券基础发行规模为0亿元,发行金额上限为10亿元,募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN003]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -5285,20 +5283,24 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK22" s="3"/>
+          <t>2036-10-12</t>
+        </is>
+      </c>
+      <c r="AK22" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL22" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -5316,7 +5318,7 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
@@ -5341,7 +5343,7 @@
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>食品加工</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5369,14 +5371,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ22" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ22" s="3"/>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN003</t>
+          <t>26安市淮阴MTN001</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5386,49 +5386,49 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>102690061.IB</t>
+          <t>102683884.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>61.36</v>
+        <v>46.84</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26涪陵国资MTN002B</t>
+          <t>25安市淮阴MTN003</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>6.86Y</t>
+          <t>1.52Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>2.0881</t>
+          <t>1.6621</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
+          <t>淮安市淮阴区城市资产经营有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 23.93</t>
+          <t>C- 19.88</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -5467,17 +5467,19 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V23" s="3"/>
+        <v>1.66</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>4.67</v>
+      </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>2.27%~2.37%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5488,17 +5490,17 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期债券基础发行规模为0亿元,发行金额上限为10亿元,募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN003]</t>
+          <t>本次发行金额5亿元,募集资金拟全部用于偿还发行人本部及下属子公司有息债务[26安市淮阴CP001]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5519,7 +5521,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第三期中期票据</t>
+          <t>淮安市淮阴区城市资产经营有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5529,14 +5531,10 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2036-10-12</t>
-        </is>
-      </c>
-      <c r="AK23" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-12</t>
+        </is>
+      </c>
+      <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -5554,12 +5552,12 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
@@ -5579,7 +5577,7 @@
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>食品加工</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5607,22 +5605,24 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ23" s="3"/>
+      <c r="AZ23" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26安市淮阴MTN001</t>
+          <t>26中航K5</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102683884.IB</t>
+          <t>525028.SZ</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -5631,55 +5631,55 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>46.84</v>
+        <v>24.84</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>25安市淮阴MTN003</t>
+          <t>26中航K3</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>1.52Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.6621</t>
+          <t>1.6223</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6500/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>淮安市淮阴区城市资产经营有限公司</t>
+          <t>中航科创有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C- 19.88</t>
+          <t>C+ 31.28</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5689,75 +5689,77 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>4.67</v>
-      </c>
+        <v>2.47</v>
+      </c>
+      <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z24" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本次发行金额5亿元,募集资金拟全部用于偿还发行人本部及下属子公司有息债务[26安市淮阴CP001]</t>
+          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>淮安市淮阴区城市资产经营有限公司2026年度第一期中期票据</t>
+          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5767,33 +5769,37 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK24" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK24" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AM24" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
@@ -5803,17 +5809,17 @@
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>航空装备</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5841,14 +5847,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ24" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ24" s="3"/>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26中航K5</t>
+          <t>26中航K6</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5858,54 +5862,54 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>525028.SZ</t>
+          <t>525029.SZ</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
         <v>7.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>24.84</v>
+        <v>26.11</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26中航K3</t>
+          <t>26中航K4</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.6223</t>
+          <t>1.7088</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.6500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -5939,7 +5943,7 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
@@ -5949,7 +5953,7 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5995,7 +5999,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
+          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -6005,14 +6009,10 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK25" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-13</t>
+        </is>
+      </c>
+      <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6088,7 +6088,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26中航K6</t>
+          <t>26杭钢02</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6098,49 +6098,49 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>525029.SZ</t>
+          <t>246177.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>26.11</v>
+        <v>31.84</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26中航K4</t>
+          <t>26杭钢01</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>2.49Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.7088</t>
+          <t>1.6419</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司</t>
+          <t>杭州钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.28</t>
+          <t>C- 21.84</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -6179,17 +6179,17 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -6197,24 +6197,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟将不低于90%用于偿还银行借款、公司债券(含到期的可续期公司债)等公司债务,偿还债务后剩余部分募集资金拟用于补充公司日常生产经营所需的流动资金。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,剩余部分募集资金拟用于补充公司流动资金。</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中航证券有限公司,中信证券股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
@@ -6225,17 +6221,17 @@
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>中航科创有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
+          <t>杭州钢铁集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6245,10 +6241,14 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
-        </is>
-      </c>
-      <c r="AK26" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK26" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL26" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="AM26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN26" s="3" t="inlineStr">
@@ -6271,27 +6271,27 @@
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>航空装备</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6324,22 +6324,22 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26杭钢02</t>
+          <t>26杭金投MTN004</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>246177.SH</t>
+          <t>102683873.IB</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1.5Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
@@ -6350,48 +6350,48 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>31.84</v>
+        <v>17.85</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26杭钢01</t>
+          <t>26杭金投MTN001</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2.49Y</t>
+          <t>1.69Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.6419</t>
+          <t>1.6154</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司</t>
+          <t>杭州市金融投资集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 21.84</t>
+          <t>C- 20.01</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6401,31 +6401,33 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V27" s="3"/>
+        <v>3.3</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>1.54</v>
+      </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.53%~1.63%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6441,18 +6443,18 @@
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,剩余部分募集资金拟用于补充公司流动资金。</t>
+          <t>本次中期票据募集资金10亿元，拟全部用于偿还发行人即将到期的债务融资工具【26 杭金投SCP001】</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>浙商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6462,12 +6464,12 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>杭州市金融投资集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6477,17 +6479,13 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK27" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-04-10</t>
+        </is>
+      </c>
+      <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6497,37 +6495,37 @@
       </c>
       <c r="AN27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6560,74 +6558,74 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26杭金投MTN004</t>
+          <t>26蜀道K9</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>102683873.IB</t>
+          <t>525034.SZ</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>17.85</v>
+        <v>21.11</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26杭金投MTN001</t>
+          <t>24蜀道05</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>1.69Y</t>
+          <t>5.01Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.6154</t>
+          <t>1.7267</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>1.6400/--</t>
+          <t>--/1.7200</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>杭州市金融投资集团有限公司</t>
+          <t>蜀道投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C- 20.01</t>
+          <t>B- 36.63</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6637,33 +6635,31 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>1.54</v>
-      </c>
+        <v>4.26</v>
+      </c>
+      <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.63%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6674,23 +6670,23 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据募集资金10亿元，拟全部用于偿还发行人即将到期的债务融资工具【26 杭金投SCP001】</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资以及符合国家法律法规要求的其他用途。</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,天府证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
@@ -6700,12 +6696,12 @@
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>杭州市金融投资集团有限公司2026年度第四期中期票据</t>
+          <t>蜀道投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第九期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6715,28 +6711,32 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2028-04-10</t>
-        </is>
-      </c>
-      <c r="AK28" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK28" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
@@ -6746,22 +6746,22 @@
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6794,17 +6794,17 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26蜀道K9</t>
+          <t>26常城建PPN002</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>525034.SZ</t>
+          <t>032690031.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -6813,55 +6813,55 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>25.0</v>
+        <v>6.64</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>25.0</v>
+        <v>6.64</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.55 ~ 2.05</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>21.11</v>
+        <v>32.11</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>24蜀道05</t>
+          <t>26常城05</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>5.01Y</t>
+          <t>4.85Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.7267</t>
+          <t>1.8215</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/1.7200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司</t>
+          <t>常州市城市建设(集团)有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>B- 36.63</t>
+          <t>C 25.80</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6871,31 +6871,33 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="V29" s="3"/>
+        <v>4.2377</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>1.19</v>
+      </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6906,23 +6908,23 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资以及符合国家法律法规要求的其他用途。</t>
+          <t>发行人本期定向债务融资工具发行金额为6.64亿元,拟用于偿还发行人本部存量债务融资工具本金[21常城建MTN003,26常城建SCP001]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,天府证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司</t>
+          <t>南京银行股份有限公司,江苏银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6932,79 +6934,75 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>蜀道投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第九期)</t>
+          <t>常州市城市建设(集团)有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK29" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-10</t>
+        </is>
+      </c>
+      <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>燃气</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM29" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO29" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ29" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR29" s="3" t="inlineStr">
-        <is>
-          <t>轨道交通</t>
-        </is>
-      </c>
-      <c r="AS29" s="3" t="inlineStr">
-        <is>
-          <t>轨道交通</t>
-        </is>
-      </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU29" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV29" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7025,12 +7023,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ29" s="3"/>
+      <c r="AZ29" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26常城建PPN002</t>
+          <t>26锡产业SCP015</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -7040,64 +7040,64 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>032690031.IB</t>
+          <t>012682379.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.64</v>
+        <v>6.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.64</v>
+        <v>6.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.55 ~ 2.05</t>
+          <t>1.31 ~ 1.51</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>32.11</v>
+        <v>31.25</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26常城05</t>
+          <t>25锡产业MTN005</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>4.85Y</t>
+          <t>271D</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.8215</t>
+          <t>1.4940</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4800</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>常州市城市建设(集团)有限公司</t>
+          <t>无锡产业发展集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C 25.80</t>
+          <t>C- 17.06</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.2377</v>
+        <v>1.2333</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>1.19</v>
+        <v>1.82</v>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -7144,23 +7144,23 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行金额为6.64亿元,拟用于偿还发行人本部存量债务融资工具本金[21常城建MTN003,26常城建SCP001]</t>
+          <t>本期超短期融资券发行金额6亿元用于归还发行人本部有息债务[26锡产业SCP006]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,江苏银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -7175,17 +7175,17 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>常州市城市建设(集团)有限公司2026年度第二期定向债务融资工具</t>
+          <t>无锡产业发展集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-10-10</t>
+          <t>2027-07-07</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
@@ -7206,12 +7206,12 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7259,81 +7259,79 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ30" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ30" s="3"/>
     </row>
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26锡产业SCP015</t>
+          <t>26古厝13</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>012682379.IB</t>
+          <t>520514.SZ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>31.25</v>
+        <v>34.81</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>25锡产业MTN005</t>
+          <t>24古厝01</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>271D</t>
+          <t>2.63Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.4940</t>
+          <t>1.6920</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/1.4800</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司</t>
+          <t>福州古厝集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 17.06</t>
+          <t>C- 21.58</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7343,7 +7341,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7353,15 +7351,13 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>1.2333</v>
-      </c>
-      <c r="V31" s="4" t="n">
-        <v>1.82</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -7369,7 +7365,7 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7380,23 +7376,23 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额6亿元用于归还发行人本部有息债务[26锡产业SCP006]</t>
+          <t>本期债券发行规模不超过5.00亿元（含），募集资金在扣除发行费用后，拟用于偿还发行人到期的公司债券本金。[25古厝D6]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>兴业证券股份有限公司,中国国际金融股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7406,68 +7402,56 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司2026年度第十五期超短期融资券</t>
+          <t>福州古厝集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2027-07-07</t>
+          <t>2028-10-12</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM31" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AQ31" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR31" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3"/>
+      <c r="AR31" s="3"/>
+      <c r="AS31" s="3"/>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7500,22 +7484,22 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26古厝13</t>
+          <t>26海发宝诚SCP007</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>520514.SZ</t>
+          <t>012682380.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.26Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -7526,48 +7510,48 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.35 ~ 1.49</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>34.81</v>
+        <v>30.32</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>24古厝01</t>
+          <t>25海租01</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.63Y</t>
+          <t>93D</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.6920</t>
+          <t>1.4631</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司</t>
+          <t>海发宝诚融资租赁有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 21.58</t>
+          <t>C- 15.93</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7577,7 +7561,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7591,17 +7575,19 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V32" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7612,89 +7598,101 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过5.00亿元（含），募集资金在扣除发行费用后，拟用于偿还发行人到期的公司债券本金。[25古厝D6]</t>
+          <t>本期超短期融资券基础发行金额0亿元，发行金额上限5亿元，拟全部用于偿还发行人即将到期的债务融资工具[26海发宝诚SCP006]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,中国国际金融股份有限公司,天风证券股份有限公司</t>
+          <t>平安银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>海发宝诚融资租赁有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2028-10-12</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO32" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ32" s="3"/>
-      <c r="AR32" s="3"/>
-      <c r="AS32" s="3"/>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7715,12 +7713,14 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ32" s="3"/>
+      <c r="AZ32" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26海发宝诚SCP007</t>
+          <t>26广州地铁SCP015</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7730,49 +7730,49 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>012682380.IB</t>
+          <t>012682381.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>0.26Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.0</v>
+        <v>14.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.0</v>
+        <v>14.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.49</t>
+          <t>1.26 ~ 1.55</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>30.32</v>
+        <v>15.25</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>25海租01</t>
+          <t>17广州地铁专项债01</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>93D</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.4631</t>
+          <t>1.4941</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>海发宝诚融资租赁有限公司</t>
+          <t>广州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 15.93</t>
+          <t>C+ 32.85</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7811,19 +7811,17 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="V33" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>3.8857</v>
+      </c>
+      <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7834,17 +7832,17 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额0亿元，发行金额上限5亿元，拟全部用于偿还发行人即将到期的债务融资工具[26海发宝诚SCP006]</t>
+          <t>本期超短期融资券金额14亿元，其中5亿元用于归还发行人存量债券，9亿元用于归还发行人金融机构借款。[26广州地铁SCP001]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,上海银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7855,7 +7853,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
@@ -7865,7 +7863,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>海发宝诚融资租赁有限公司2026年度第七期超短期融资券</t>
+          <t>广州地铁集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7875,7 +7873,7 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
@@ -7896,32 +7894,32 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7949,66 +7947,64 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AZ33" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ33" s="3"/>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26广州地铁SCP015</t>
+          <t>26天长01</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>012682381.IB</t>
+          <t>284203.SH</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.55</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>15.25</v>
+        <v>46.84</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>17广州地铁专项债01</t>
+          <t>25滁高01</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>1.64Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.4941</t>
+          <t>1.6256</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -8018,12 +8014,12 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司</t>
+          <t>天长市科技工业发展有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.85</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8033,7 +8029,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -8047,44 +8043,52 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.8857</v>
+        <v>4.2</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>安徽省-滁州市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券金额14亿元，其中5亿元用于归还发行人存量债券，9亿元用于归还发行人金融机构借款。[26广州地铁SCP001]</t>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还“23天长02”公司债券本金。[23天长02]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,广发银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD34" s="3"/>
+          <t>五矿证券有限公司,川财证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr">
+        <is>
+          <t>安徽省信用融资担保集团有限公司</t>
+        </is>
+      </c>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -8094,28 +8098,28 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>广州地铁集团有限公司2026年度第十五期超短期融资券</t>
+          <t>天长市科技工业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
@@ -8130,12 +8134,12 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
@@ -8145,17 +8149,17 @@
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8165,7 +8169,7 @@
       </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW34" s="3" t="inlineStr">
@@ -8188,7 +8192,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26天长01</t>
+          <t>26凯建01</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8198,49 +8202,49 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>284203.SH</t>
+          <t>284219.SH</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>2.40 ~ 3.40</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.75</v>
+        <v>2.65</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>46.84</v>
+        <v>124.11</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>25滁高01</t>
+          <t>25凯建01</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>1.64Y</t>
+          <t>4.15Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.6256</t>
+          <t>2.8084</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -8250,12 +8254,12 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>天长市科技工业发展有限公司</t>
+          <t>凯里正源城镇建设发展有限责任公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B- 42.31</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8279,17 +8283,17 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>4.2</v>
+        <v>2.66</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>8-</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>2.79%~2.89%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8297,29 +8301,25 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>安徽省-滁州市</t>
+          <t>贵州省-黔东南苗族侗族自治州</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,全部用于偿还“23天长02”公司债券本金。[23天长02]</t>
+          <t>本期债券募集资金扣除承销费用后，拟全部用于统借统还偿还到期公司债券本金</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司,川财证券有限责任公司</t>
+          <t>第一创业证券承销保荐有限责任公司</t>
         </is>
       </c>
       <c r="AD35" s="3" t="inlineStr">
         <is>
-          <t>安徽省信用融资担保集团有限公司</t>
+          <t>贵州省信用增进有限公司</t>
         </is>
       </c>
       <c r="AE35" s="3" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>天长市科技工业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>凯里正源城镇建设发展有限责任公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8349,10 +8349,14 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK35" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK35" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL35" s="3" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -8375,7 +8379,7 @@
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
@@ -8385,17 +8389,17 @@
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8428,74 +8432,74 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26凯建01</t>
+          <t>26兴化城投PPN009</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>10-09 19:00</t>
+          <t>10-09 18:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>284219.SH</t>
+          <t>032680552.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2.40 ~ 3.40</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>124.11</v>
+        <v>39.81</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>25凯建01</t>
+          <t>26兴化城投PPN008</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>4.15Y</t>
+          <t>1.88Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2.8084</t>
+          <t>1.6847</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>凯里正源城镇建设发展有限责任公司</t>
+          <t>兴化市城市建设投资有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>B- 42.31</t>
+          <t>C- 16.51</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8505,7 +8509,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>10-09 15:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8515,21 +8519,23 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V36" s="3"/>
+        <v>3.6</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>1.26</v>
+      </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>8-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>2.79%~2.89%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8540,27 +8546,23 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>贵州省-黔东南苗族侗族自治州</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除承销费用后，拟全部用于统借统还偿还到期公司债券本金</t>
+          <t>本期定向债务融资工具发行金额4亿元,拟用于偿还发行人有息债务[26兴化城投PPN002]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>第一创业证券承销保荐有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD36" s="3" t="inlineStr">
-        <is>
-          <t>贵州省信用增进有限公司</t>
-        </is>
-      </c>
+          <t>江苏江南农村商业银行股份有限公司,苏州银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8570,12 +8572,12 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>凯里正源城镇建设发展有限责任公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>兴化市城市建设投资有限公司2026年度第九期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8585,17 +8587,13 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK36" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-10-10</t>
+        </is>
+      </c>
+      <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
@@ -8605,37 +8603,37 @@
       </c>
       <c r="AN36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>农产品加工</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8645,7 +8643,7 @@
       </c>
       <c r="AV36" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW36" s="3" t="inlineStr">
@@ -8668,7 +8666,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26兴化城投PPN009</t>
+          <t>26绍兴高新MTN003</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8678,64 +8676,64 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>032680552.IB</t>
+          <t>102683883.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>4.0</v>
+        <v>8.2</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>4.0</v>
+        <v>8.2</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>39.81</v>
+        <v>41.11</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26兴化城投PPN008</t>
+          <t>26绍兴高新MTN002</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>1.88Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.6847</t>
+          <t>1.8213</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>1.7100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>兴化市城市建设投资有限公司</t>
+          <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C- 16.51</t>
+          <t>C- 22.07</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8745,60 +8743,58 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 14:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V37" s="4" t="n">
-        <v>1.26</v>
-      </c>
+        <v>5.0366</v>
+      </c>
+      <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额4亿元,拟用于偿还发行人有息债务[26兴化城投PPN002]</t>
+          <t>发行人本期中期票据发行金额人民币8.20亿元,拟全部用于偿还发行人本级2026年到期的债务融资工具本金[23绍兴高新MTN002]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>江苏江南农村商业银行股份有限公司,苏州银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8813,38 +8809,42 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>兴化市城市建设投资有限公司2026年度第九期定向债务融资工具</t>
+          <t>绍兴高新技术产业开发区投资发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2028-10-10</t>
-        </is>
-      </c>
-      <c r="AK37" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK37" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL37" s="3" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AM37" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
@@ -8854,22 +8854,22 @@
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>农产品加工</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8902,7 +8902,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26绍兴高新MTN003</t>
+          <t>26皖投集MTN006</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8912,64 +8912,64 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>102683883.IB</t>
+          <t>102683882.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>8.2</v>
+        <v>5.0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>8.2</v>
+        <v>5.0</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.82</v>
+        <v>1.51</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>41.11</v>
+        <v>22.84</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26绍兴高新MTN002</t>
+          <t>24皖投03</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.8213</t>
+          <t>1.6119</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5900</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
+          <t>安徽省投资集团控股有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C- 22.07</t>
+          <t>C- 17.65</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8979,12 +8979,12 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>10-09 14:00</t>
+          <t>10-09 09:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
@@ -8993,38 +8993,40 @@
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>5.0366</v>
-      </c>
-      <c r="V38" s="3"/>
+        <v>5.16</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>3.08</v>
+      </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额人民币8.20亿元,拟全部用于偿还发行人本级2026年到期的债务融资工具本金[23绍兴高新MTN002]</t>
+          <t>本期中期票据募集资金5亿元人民币，全部用于偿还发行人即将到期的债券[25皖投集CP003]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,宁波银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,国家开发银行</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
@@ -9045,7 +9047,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>绍兴高新技术产业开发区投资发展集团有限公司2026年度第三期中期票据</t>
+          <t>安徽省投资集团控股有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -9055,14 +9057,10 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK38" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-12</t>
+        </is>
+      </c>
+      <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -9085,27 +9083,27 @@
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9138,17 +9136,17 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26皖投集MTN006</t>
+          <t>26唐租01</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>10-09 18:00</t>
+          <t>10-09 19:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>102683882.IB</t>
+          <t>246158.SH</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -9157,55 +9155,55 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>22.84</v>
+        <v>39.84</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>24皖投03</t>
+          <t>25大唐租赁MTN002B(绿色)</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>1.63Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.6119</t>
+          <t>1.6333</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/1.5900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司</t>
+          <t>大唐融资租赁有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 17.65</t>
+          <t>B- 35.40</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9215,33 +9213,31 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>10-09 09:00</t>
+          <t>10-09 16:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>3.08</v>
-      </c>
+        <v>2.34</v>
+      </c>
+      <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9252,38 +9248,38 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金5亿元人民币，全部用于偿还发行人即将到期的债券[25皖投集CP003]</t>
+          <t>本期债券募集资金10.00亿元拟用于偿还发行人到期公司债券本金[24唐租04]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,国家开发银行</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司2026年度第六期中期票据</t>
+          <t>大唐融资租赁有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9293,53 +9289,57 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK39" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK39" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9372,7 +9372,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26唐租01</t>
+          <t>26联投Y5</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9382,12 +9382,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>246158.SH</t>
+          <t>246172.SH</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
@@ -9398,33 +9398,33 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>39.84</v>
+        <v>49.84</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>25大唐租赁MTN002B(绿色)</t>
+          <t>26鄂联投MTN002</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>1.63Y</t>
+          <t>2.92Y+N</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.6333</t>
+          <t>1.7641</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -9434,12 +9434,12 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司</t>
+          <t>湖北省联合发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>B- 35.40</t>
+          <t>C+ 32.26</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>10-09 16:00</t>
+          <t>10-09 15:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -9463,17 +9463,17 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>2.34</v>
+        <v>2.01</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -9484,17 +9484,17 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>湖北省</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金10.00亿元拟用于偿还发行人到期公司债券本金[24唐租04]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于生产性支出,包括但不限于补充流动资金、偿还有息债务、项目建设、权益投资等符合国家法律法规及政策要求的企业生产经营活动。</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,招商证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,平安证券股份有限公司,中国银河证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>大唐融资租赁有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>湖北省联合发展投资集团有限公司2026年面向专业投资者公开发行可续期公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9535,54 +9535,54 @@
       </c>
       <c r="AL40" s="3" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM40" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AO40" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ40" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR40" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AS40" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AT40" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU40" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV40" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
